--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clusters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_Fases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conflictos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallazgos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Léeme" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Clusters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Plan_Fases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Conflictos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Hallazgos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallazgos'!$A$1:$L$235</definedName>
@@ -2768,11 +2768,19 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K17" s="6" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1)</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>d33a38a</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2872,11 +2880,19 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K19" s="6" t="inlineStr"/>
-      <c r="L19" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1)</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>d33a38a</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -9000,11 +9016,19 @@
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K141" s="6" t="inlineStr"/>
-      <c r="L141" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1)</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>d33a38a</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -9204,11 +9228,19 @@
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K145" s="6" t="inlineStr"/>
-      <c r="L145" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1)</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>d33a38a</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -11020,11 +11052,19 @@
       <c r="I183" s="6" t="inlineStr"/>
       <c r="J183" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K183" s="6" t="inlineStr"/>
-      <c r="L183" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K183" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1)</t>
+        </is>
+      </c>
+      <c r="L183" s="6" t="inlineStr">
+        <is>
+          <t>59440a9 + 8b033b6</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -11070,11 +11110,19 @@
       <c r="I184" s="6" t="inlineStr"/>
       <c r="J184" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K184" s="6" t="inlineStr"/>
-      <c r="L184" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K184" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1)</t>
+        </is>
+      </c>
+      <c r="L184" s="6" t="inlineStr">
+        <is>
+          <t>08ba613</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -12758,11 +12806,19 @@
       <c r="I218" s="6" t="inlineStr"/>
       <c r="J218" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K218" s="6" t="inlineStr"/>
-      <c r="L218" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K218" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1)</t>
+        </is>
+      </c>
+      <c r="L218" s="6" t="inlineStr">
+        <is>
+          <t>219f584</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -13108,11 +13164,19 @@
       <c r="I225" s="6" t="inlineStr"/>
       <c r="J225" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K225" s="6" t="inlineStr"/>
-      <c r="L225" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K225" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1)</t>
+        </is>
+      </c>
+      <c r="L225" s="6" t="inlineStr">
+        <is>
+          <t>3c526b4</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -13218,10 +13218,14 @@
       <c r="I226" s="6" t="inlineStr"/>
       <c r="J226" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K226" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K226" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L226" s="6" t="inlineStr"/>
     </row>
     <row r="227">
@@ -13264,10 +13268,14 @@
       <c r="I227" s="6" t="inlineStr"/>
       <c r="J227" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K227" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K227" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L227" s="6" t="inlineStr"/>
     </row>
     <row r="228">
@@ -13310,10 +13318,14 @@
       <c r="I228" s="6" t="inlineStr"/>
       <c r="J228" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K228" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K228" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L228" s="6" t="inlineStr"/>
     </row>
     <row r="229">
@@ -13356,10 +13368,14 @@
       <c r="I229" s="6" t="inlineStr"/>
       <c r="J229" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K229" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K229" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L229" s="6" t="inlineStr"/>
     </row>
     <row r="230">
@@ -13402,10 +13418,14 @@
       <c r="I230" s="6" t="inlineStr"/>
       <c r="J230" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K230" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K230" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L230" s="6" t="inlineStr"/>
     </row>
     <row r="231">
@@ -13448,10 +13468,14 @@
       <c r="I231" s="6" t="inlineStr"/>
       <c r="J231" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K231" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K231" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L231" s="6" t="inlineStr"/>
     </row>
     <row r="232">
@@ -13494,10 +13518,14 @@
       <c r="I232" s="6" t="inlineStr"/>
       <c r="J232" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K232" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K232" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L232" s="6" t="inlineStr"/>
     </row>
     <row r="233">
@@ -13540,10 +13568,14 @@
       <c r="I233" s="6" t="inlineStr"/>
       <c r="J233" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K233" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K233" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L233" s="6" t="inlineStr"/>
     </row>
     <row r="234">
@@ -13586,10 +13618,14 @@
       <c r="I234" s="6" t="inlineStr"/>
       <c r="J234" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K234" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K234" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L234" s="6" t="inlineStr"/>
     </row>
     <row r="235">
@@ -13632,10 +13668,14 @@
       <c r="I235" s="6" t="inlineStr"/>
       <c r="J235" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K235" s="6" t="inlineStr"/>
+          <t>N/A (sin trabajo)</t>
+        </is>
+      </c>
+      <c r="K235" s="6" t="inlineStr">
+        <is>
+          <t>Auditoría normativa</t>
+        </is>
+      </c>
       <c r="L235" s="6" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -1990,11 +1990,19 @@
       <c r="I2" s="6" t="inlineStr"/>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr"/>
-      <c r="L2" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -2606,11 +2614,19 @@
       <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr"/>
-      <c r="L14" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -3242,11 +3258,19 @@
       <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr"/>
-      <c r="L26" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3288,11 +3312,19 @@
       <c r="I27" s="6" t="inlineStr"/>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr"/>
-      <c r="L27" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -4160,11 +4192,19 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -4206,11 +4246,19 @@
       <c r="I46" s="6" t="inlineStr"/>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K46" s="6" t="inlineStr"/>
-      <c r="L46" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -4252,11 +4300,19 @@
       <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K47" s="6" t="inlineStr"/>
-      <c r="L47" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -4782,11 +4838,19 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K58" s="6" t="inlineStr"/>
-      <c r="L58" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c — Docstrings resincronizados (v_max_*, conteo de M2, ejemplo de MD). El VALOR de h_relleno_min_concreto_tmc queda en el paquete del conflicto #5 (C01: MAT-D3/D4, NOR-VAC-01): aqui solo se describe su estado, no se cierra el vacio.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -5152,11 +5216,19 @@
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K65" s="6" t="inlineStr"/>
-      <c r="L65" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -5344,11 +5416,19 @@
       <c r="I69" s="6" t="inlineStr"/>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K69" s="6" t="inlineStr"/>
-      <c r="L69" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6834,11 +6914,19 @@
       <c r="I98" s="6" t="inlineStr"/>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K98" s="6" t="inlineStr"/>
-      <c r="L98" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -7034,11 +7122,19 @@
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr"/>
-      <c r="L102" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -7138,11 +7234,19 @@
       <c r="I104" s="6" t="inlineStr"/>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K104" s="6" t="inlineStr"/>
-      <c r="L104" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -7238,11 +7342,19 @@
       <c r="I106" s="6" t="inlineStr"/>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K106" s="6" t="inlineStr"/>
-      <c r="L106" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -7288,11 +7400,19 @@
       <c r="I107" s="6" t="inlineStr"/>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K107" s="6" t="inlineStr"/>
-      <c r="L107" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -7338,11 +7458,19 @@
       <c r="I108" s="6" t="inlineStr"/>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K108" s="6" t="inlineStr"/>
-      <c r="L108" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -7388,11 +7516,19 @@
       <c r="I109" s="6" t="inlineStr"/>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K109" s="6" t="inlineStr"/>
-      <c r="L109" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -7604,11 +7740,19 @@
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K113" s="6" t="inlineStr"/>
-      <c r="L113" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -7754,11 +7898,19 @@
       <c r="I116" s="6" t="inlineStr"/>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K116" s="6" t="inlineStr"/>
-      <c r="L116" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L116" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -7908,11 +8060,19 @@
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K119" s="6" t="inlineStr"/>
-      <c r="L119" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -10368,11 +10528,19 @@
       <c r="I169" s="6" t="inlineStr"/>
       <c r="J169" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K169" s="6" t="inlineStr"/>
-      <c r="L169" s="6" t="inlineStr"/>
+          <t>Verificado (sin correccion)</t>
+        </is>
+      </c>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c — Ficha de cobertura (CONFIRMA). Reverificado sobre las dos memorias generadas tras el cambio: sin citas truncadas, plantillas sin numerales, analogia [N-&gt;] declarada, adopcion de Clase F impresa, avisos de trazabilidad y "(proyecto no declarado)".</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -10702,11 +10870,19 @@
       <c r="I176" s="6" t="inlineStr"/>
       <c r="J176" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K176" s="6" t="inlineStr"/>
-      <c r="L176" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K176" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L176" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -11268,11 +11444,19 @@
       <c r="I187" s="6" t="inlineStr"/>
       <c r="J187" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K187" s="6" t="inlineStr"/>
-      <c r="L187" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L187" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -11318,11 +11502,19 @@
       <c r="I188" s="6" t="inlineStr"/>
       <c r="J188" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K188" s="6" t="inlineStr"/>
-      <c r="L188" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K188" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L188" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -11418,11 +11610,19 @@
       <c r="I190" s="6" t="inlineStr"/>
       <c r="J190" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K190" s="6" t="inlineStr"/>
-      <c r="L190" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K190" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L190" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -12056,11 +12256,19 @@
       <c r="I203" s="6" t="inlineStr"/>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K203" s="6" t="inlineStr"/>
-      <c r="L203" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L203" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -12356,11 +12564,19 @@
       <c r="I209" s="6" t="inlineStr"/>
       <c r="J209" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K209" s="6" t="inlineStr"/>
-      <c r="L209" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K209" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L209" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -12406,11 +12622,19 @@
       <c r="I210" s="6" t="inlineStr"/>
       <c r="J210" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K210" s="6" t="inlineStr"/>
-      <c r="L210" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L210" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
@@ -12506,11 +12730,19 @@
       <c r="I212" s="6" t="inlineStr"/>
       <c r="J212" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K212" s="6" t="inlineStr"/>
-      <c r="L212" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K212" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L212" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -12556,11 +12788,19 @@
       <c r="I213" s="6" t="inlineStr"/>
       <c r="J213" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K213" s="6" t="inlineStr"/>
-      <c r="L213" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K213" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L213" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -12606,11 +12846,19 @@
       <c r="I214" s="6" t="inlineStr"/>
       <c r="J214" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K214" s="6" t="inlineStr"/>
-      <c r="L214" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K214" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L214" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -12914,11 +13162,19 @@
       <c r="I220" s="6" t="inlineStr"/>
       <c r="J220" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K220" s="6" t="inlineStr"/>
-      <c r="L220" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K220" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S2)</t>
+        </is>
+      </c>
+      <c r="L220" s="6" t="inlineStr">
+        <is>
+          <t>3ea627c</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2000,7 +2000,7 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>3ea627c — Docstrings resincronizados (v_max_*, conteo de M2, ejemplo de MD). El VALOR de h_relleno_min_concreto_tmc queda en el paquete del conflicto #5 (C01: MAT-D3/D4, NOR-VAC-01): aqui solo se describe su estado, no se cierra el vacio.</t>
+          <t>3ea627c + 7266bfe — Docstrings resincronizados (v_max_*, conteo de M2, ejemplo de MD). El VALOR de h_relleno_min_concreto_tmc queda en el paquete del conflicto #5 (C01: MAT-D3/D4, NOR-VAC-01): aqui solo se describe su estado, no se cierra el vacio.</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
       </c>
       <c r="L98" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="L102" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="L104" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -7352,7 +7352,7 @@
       </c>
       <c r="L106" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="L107" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L108" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L109" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="L113" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="L116" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="L169" s="6" t="inlineStr">
         <is>
-          <t>3ea627c — Ficha de cobertura (CONFIRMA). Reverificado sobre las dos memorias generadas tras el cambio: sin citas truncadas, plantillas sin numerales, analogia [N-&gt;] declarada, adopcion de Clase F impresa, avisos de trazabilidad y "(proyecto no declarado)".</t>
+          <t>3ea627c + 7266bfe — Ficha de cobertura (CONFIRMA). Reverificado sobre las dos memorias generadas tras el cambio: sin citas truncadas, plantillas sin numerales, analogia [N-&gt;] declarada, adopcion de Clase F impresa, avisos de trazabilidad y "(proyecto no declarado)".</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="L176" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="L187" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="L188" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="L190" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="L203" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -12574,7 +12574,7 @@
       </c>
       <c r="L209" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -12632,7 +12632,7 @@
       </c>
       <c r="L210" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="L212" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="L213" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="L214" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="L220" s="6" t="inlineStr">
         <is>
-          <t>3ea627c</t>
+          <t>3ea627c + 7266bfe</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2048,11 +2048,19 @@
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K3" s="6" t="inlineStr"/>
-      <c r="L3" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — verificado leyendo el PDF: ASTM A760/A760M-10, Tabla 1 'Tamaños de tuberia', pag. 3, tabula de 100 a 3600 mm; 2100 mm es una fila mas. El tope se reetiqueta como de catalogo ('D_max_catalogo' [A]) y V9 y el motivo de descarte de MD lo dicen asi.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2098,11 +2106,19 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr"/>
-      <c r="L4" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — idem para concreto: M 170M-04 Tablas 1-5 van de 300 a 3600 mm y §7.2 preve diseños especiales por encima. El 2.70 se conserva como tope de catalogo, no como tope normativo.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2198,11 +2214,19 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="inlineStr"/>
-      <c r="L6" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — el vacio no era un vacio. Se transcribe la Tabla 12.6.6.3-1 de AASHTO LRFD (Art. 12.6.6.3, pag. 12-22) en el criterio 'cobertura_minima_aashto' [C] y h_rec pasa a calcularse como el mayor entre el minimo de EG-2013 (solo HDPE) y esa cobertura. Se RETIRA 'h_relleno_min_concreto_tmc'. Que fila aplica lo decide 'condicion_pavimento' [A], sin valor, que bloquea; el Bc del concreto necesita 'espesor_pared_conducto' [A], sin valor, que tambien bloquea.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2356,11 +2380,19 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr"/>
-      <c r="L9" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — U y EV de V7 pasan al diametro EXTERIOR (M8.empuje_flotacion_kn_m / peso_relleno_kn_m reciben D_exterior, que M2.diametro_exterior calcula como D + 2t). Se retira del docstring la afirmacion de que usar el interior era conservador: es la direccion contraria. Con D=0.90 y t=0.10 en concreto, U pasa de 6.24 a 9.32 kN/m.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2410,11 +2442,19 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr"/>
-      <c r="L10" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — la cota de clave es la FISICA: M5.cota_clave = cota_entrada + D_interior + espesor_pared. Se unifica en M5 la formula que estaba duplicada (M7.cota_clave y una linea suelta dentro de v7_flotacion), con el mismo defecto en las dos copias.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -4504,11 +4544,19 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr"/>
-      <c r="L51" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — atribucion corregida en el codigo (comentario de H_RELLENO_MIN y fuente de 'cobertura_minima_aashto') y en docs/manifiesto_citas.md §9 y §14.a: la formula 'manufacturing and purchase specification only' es la Nota 1 de M 170M y solo de ella; en M 36 la exclusion esta en §1.3 y en A760 en §1.4.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -4838,17 +4886,17 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S2)</t>
+          <t>Claude Code (fase1, S4)</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe — Docstrings resincronizados (v_max_*, conteo de M2, ejemplo de MD). El VALOR de h_relleno_min_concreto_tmc queda en el paquete del conflicto #5 (C01: MAT-D3/D4, NOR-VAC-01): aqui solo se describe su estado, no se cierra el vacio.</t>
+          <t>3ea627c + 7266bfe — Docstrings resincronizados (v_max_*, conteo de M2, ejemplo de MD). El VALOR de h_relleno_min_concreto_tmc queda en el paquete del conflicto #5 (C01: MAT-D3/D4, NOR-VAC-01): aqui solo se describe su estado, no se cierra el vacio. || 3d59da0 — cierra el resto que S2 dejo abierto (era 'Cerrado parcial'): el VALOR de 'h_relleno_min_concreto_tmc' quedaba en el paquete del conflicto #5. El criterio se retiro y los docstrings que describian su estado (M2, M5, M7, modelos, M11, constantes_normativas) estan al dia.</t>
         </is>
       </c>
     </row>
@@ -5694,11 +5742,19 @@
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K74" s="6" t="inlineStr"/>
-      <c r="L74" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — los topes salen de constantes_normativas.py al criterio 'D_max_catalogo' [A], con el campo nuevo Criterio.de_catalogo. La marca VERIFICAR desaparece porque el problema no era confirmar el numero: era que no es [N]. El paso 0.15 y el conservadurismo del 0.90 se conservan en 'diametros_normalizados' [C], con la serie de A760/M170M como fuente.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -6372,11 +6428,19 @@
       <c r="I87" s="6" t="inlineStr"/>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K87" s="6" t="inlineStr"/>
-      <c r="L87" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — la ATRIBUCION queda cerrada: 'clases_producto_por_relleno' y el docstring de M8 dejan de difierir a ASTM A-807 (que no aparece en M 170M, M 36 ni A760) y difieren a ASTM A796/A796M, con A798/A798M para instalacion; se anota que la remision del EG-2013 507.05/.06/.08 a A-807 si es correcta pero es de materiales. QUEDA ABIERTO lo que la ficha dice que se puede cerrar hoy: transcribir la relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36. Es trabajo de la tabla de clases (C01 no la transcribe) y sigue en el vacio declarado 'clases_producto_por_relleno'.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -6668,11 +6732,19 @@
       <c r="I93" s="6" t="inlineStr"/>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K93" s="6" t="inlineStr"/>
-      <c r="L93" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — la divergencia queda ESCRITA, que es lo que faltaba: M6_proteccion declara en su docstring y en una tercera advertencia del resultado que HDS-5 3a ed. (FHWA-HIF-12-026), Sec. 5.3.2 'Scour at Outlets', pag. 5.11 -- verificada leyendo el PDF -- dimensiona el apron por HEC-14 Sec. 10.2 (funcion de Q, D y TW), y por que el proyecto aplica el d50 de Laushey del Manual MTC: es norma peruana [N] y HEC-14 no esta en normas/. Sin contradiccion numerica demostrable.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -6822,11 +6894,19 @@
       <c r="I96" s="6" t="inlineStr"/>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K96" s="6" t="inlineStr"/>
-      <c r="L96" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — el argumento apoyado en WSDOT M 23-03.12 Tabla 8-6 desaparece con el criterio que lo alojaba. La direccion que sostenia queda respaldada por una fuente que SI esta en normas/ (la propia Tabla 12.6.6.3-1: bajo pavimento el termoplastico pide ID/2 &gt;= 24 in, el valor mas alto de la tabla) y la magnitud ya no depende de la analogia.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -6868,11 +6948,19 @@
       <c r="I97" s="6" t="inlineStr"/>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K97" s="6" t="inlineStr"/>
-      <c r="L97" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — la comparacion que la ficha reclama queda DECLARADA: 'hds5_embocadura_hdpe' lleva ahora la fila alternativa ('Circular CM / Headwall') en `sensibilidad` y su verificacion_pendiente dice con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila: la adopcion se sostiene en el perfil de pared en la boca (argumento fisico que la ficha no refuta), no en un margen de seguridad, y elegir la del metal por su resultado seria sustituir una analogia por otra. Lo que cierra el punto es el detalle constructivo, y eso sigue abierto.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -9884,11 +9972,19 @@
       <c r="I155" s="6" t="inlineStr"/>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K155" s="6" t="inlineStr"/>
-      <c r="L155" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S4)</t>
+        </is>
+      </c>
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>3d59da0 — la ficha CONFIRMA la analogia y su etiqueta; lo que se corrige es lo unico que la fuente no sostenia. Se retira de 'resguardo_HW_subrasante' la frase 'la analogia es conservadora' y se declara que la equivalencia entre saturacion permanente (mecanismo del num. 4.5.4) y mojado transitorio por avenida es plausible, no demostrada, con verificacion_pendiente propia.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2058,7 +2058,7 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — verificado leyendo el PDF: ASTM A760/A760M-10, Tabla 1 'Tamaños de tuberia', pag. 3, tabula de 100 a 3600 mm; 2100 mm es una fila mas. El tope se reetiqueta como de catalogo ('D_max_catalogo' [A]) y V9 y el motivo de descarte de MD lo dicen asi.</t>
+          <t>3d59da0 — verificado leyendo el PDF: ASTM A760/A760M-10, Tabla 1 'Tamaños de tuberia', pag. 3, tabula de 100 a 3600 mm; 2100 mm es una fila mas. El tope se reetiqueta como de catalogo ('D_max_catalogo' [A]) y V9 y el motivo de descarte de MD lo dicen asi. || dbaa501 — A760 Tabla 1 arranca en 100 mm (4 in), no en 150; corregido en 'diametros_normalizados'.</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — el vacio no era un vacio. Se transcribe la Tabla 12.6.6.3-1 de AASHTO LRFD (Art. 12.6.6.3, pag. 12-22) en el criterio 'cobertura_minima_aashto' [C] y h_rec pasa a calcularse como el mayor entre el minimo de EG-2013 (solo HDPE) y esa cobertura. Se RETIRA 'h_relleno_min_concreto_tmc'. Que fila aplica lo decide 'condicion_pavimento' [A], sin valor, que bloquea; el Bc del concreto necesita 'espesor_pared_conducto' [A], sin valor, que tambien bloquea.</t>
+          <t>3d59da0 — el vacio no era un vacio. Se transcribe la Tabla 12.6.6.3-1 de AASHTO LRFD (Art. 12.6.6.3, pag. 12-22) en el criterio 'cobertura_minima_aashto' [C] y h_rec pasa a calcularse como el mayor entre el minimo de EG-2013 (solo HDPE) y esa cobertura. Se RETIRA 'h_relleno_min_concreto_tmc'. Que fila aplica lo decide 'condicion_pavimento' [A], sin valor, que bloquea; el Bc del concreto necesita 'espesor_pared_conducto' [A], sin valor, que tambien bloquea. || dbaa501 — la transcripcion de la Tabla 12.6.6.3-1 se rehizo sobre la celda RENDERIZADA tras la auditoria adversarial: la fila del concreto dice "Bc/8 or B'c/8, whichever is greater, &gt;= 12.0 in.", no "sqrt(Bc)/8" como transcribe la propia ficha NOR-VAC-01 (la prima de B'c es un glifo de SymbolMT que la extraccion de texto rompe). B'c es la "out-to-out vertical rise of pipe", que en conducto circular es Bc, de modo que el maximo se reduce a Bc/8. Cae con la lectura falsa la rama sqrt y el factor pie-metro que se habian introducido. NOTA CONTRA LA FICHA: su transcripcion del segundo termino es erronea.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2272,11 +2272,19 @@
       <c r="I7" s="6" t="inlineStr"/>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr"/>
-      <c r="L7" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — V2 deja de leer la rama n_min. `modelos.TiranteNormal` y `modelos.ResultadoHidraulico` retiran el campo `V` y llevan dos: `V_erosion` (n_min, estimacion ALTA) y `V_sedimentacion` (n_max, estimacion BAJA), las dos sobre la MISMA geometria de Brent. `M5.v2_velocidad_minima` consume `V_sedimentacion`; `v3_velocidad_maxima` y Laushey (cli._fase_6 -&gt; M6) consumen `V_erosion`. No hay campo neutro que permita elegir mal en silencio. Recomputado a mano: D=0.90, y/D=0.75 (theta=4pi/3), S=5e-5, concreto -&gt; A=0.511800 m2, R=0.271518 m, V(n_max)=0.228073 m/s y V(n_min)=0.296495 m/s con Q=0.116728 m3/s: V2 pasa de 'cumple' a 'NO cumple', que es lo correcto. `Material.n_para_velocidad` se renombra `n_para_velocidad_maxima` (los terminos de la Sec. 4.1 de la hoja de ruta) y se agrega `n_para_velocidad_minima`.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -4136,11 +4144,19 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K43" s="6" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — `DIAMETRO_MIN` lleva ahora el texto literal del num. 4.1.1.3.4 a) (`DIAMETRO_MIN_TEXTO`, pag. impresa 72) y su ambito (`DIAMETRO_MIN_AMBITO`), con las dos condiciones: 'carreteras de alto volumen de transito' -- que el proyecto NO puede afirmar porque la clase de via no esta cerrada, y aplicar el piso igual queda declarado como adopcion conservadora -- y 'salvo en cruces de canales de riego', que es la Familia C de este expediente. El codigo ya no le aplicaba el piso a la Familia C (`M2.materiales_candidatos` devuelve tupla vacia), pero la razon escrita era solo la forma de la seccion; ahora la excepcion normativa esta en el docstring del modulo, en la funcion y en la `fuente` de 'diametros_normalizados'. Se cierra el defecto de CITA; el piso nunca llegaba a la Familia C por la via de calculo. || 76791d0 -- la auditoria adversarial mostro que estaba cerrado solo en `DIAMETRO_MIN`, que no tiene consumidor: la cadena viva conservaba la formula que la ficha cita como defecto. Corregidos `D_INICIO` ('minimo normativo MTC' a secas), el docstring 'Sec. 3.2 - Catalogo de diametros' de M2 y la fila del manifiesto. Y se retira una afirmacion FALSA que este mismo cluster habia introducido en DIAMETRO_MIN_AMBITO -- que aplicar el piso 'exige mas seccion, nunca menos' y por eso es conservador --: con concreto, S=0.001 y Q=0.0035 m3/s, D=0.75 cumple V2 con 0.2554 m/s y D=0.90 NO cumple con 0.2488. Mas diametro favorece a V1 y perjudica a V2.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4182,11 +4198,19 @@
       <c r="I44" s="6" t="inlineStr"/>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K44" s="6" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — La frase 'el rango recorre la calidad del revestimiento' sale de la cita y pasa a declararse como INTERPRETACION DEL PROYECTISTA en `constantes_normativas.TABLA_10_INTERPRETACION_PROYECTO`, que M11 imprime separada, en su propio aviso. La `fuente` de 'v_max_concreto_eleccion', `M5.NUMERAL_V3` y la nota de la §1 del manifiesto separan ahora lo que la fuente sostiene (los dos numeros son maximos: lo dice el titulo y el rotulo 'VELOCIDAD (M/S)') de lo que pone el proyecto, y citan los dos hechos que juegan en contra de la lectura de acabados: la frase que introduce la tabla ('un rango, cuyos limites se describen a continuacion') y la fila de mamposteria con un solo valor.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4448,11 +4472,19 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K49" s="6" t="inlineStr"/>
-      <c r="L49" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — Cerrado sobre el PRODUCTO, que era donde fallaba. El matiz viajaba solo dentro de `M5.NUMERAL_V2`, o sea dentro de la tabla de verificaciones del punto, que no se imprime si el punto no llego a evaluarse -- y no llega, porque 'homogeneidad_serie_fen' bloquea el Q de la Familia A. Se agrega `constantes_normativas.UMBRALES_DE_VERIFICACION` (V1, V2, V3, TR y D_min con numeral, caracter, texto literal y lo que el proyecto hace con cada uno), `M11.bloque_umbrales()` y el marcador %%bloque_umbrales en las dos plantillas, en la seccion nueva '0-ter. Umbrales normativos y su caracter', que se imprime siempre. Medido sobre la memoria generada con tests/ejemplo_puntos.csv en los dos alcances: 'recomend' pasa de 0 a 7 apariciones y 'sedimentaci' de 0 a 3. || 76791d0 -- ademas, la memoria imprimia 'num. MC-HHD (...), num. 3.6' porque M11 anteponia 'num.' a un NUMERAL_TR que ya lo trae; y NUMERAL_V3 remitia a un simbolo de codigo que un revisor con el PDF no puede resolver.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5318,11 +5350,19 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K66" s="6" t="inlineStr"/>
-      <c r="L66" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — La Tabla N 02 se transcribe COMPLETA (seis filas) con su titulo literal 'VALORES MAXIMOS RECOMENDADOS de riesgo admisible de obras de drenaje', el texto que la introduce ('se recomienda utilizar como maximo') y las dos notas al pie, incluida la que asigna la decision al Propietario. El caracter viaja al punto de uso: `M1.NUMERAL_TR` y el `fundamento` de `PeriodoRetorno` declaran que son maximos recomendados adoptados por el proyecto y que adoptarlos es -- al reves que en V1 y V2 -- el extremo MENOS conservador del margen concedido. NO se reetiqueta [N]-&gt;[A]: por la regla de CLAUDE.md la TABLA es [N] y lo que es [A] es la eleccion, que para la Familia A ya vive en 'umbral_area_quebrada_importante_ha' (sin valor, bloquea) y para la Familia B la fija la Sec. 2.3. Lo que faltaba era el caracter declarado, y es lo que se cierra. || 76791d0 -- cerrado en parte hasta la auditoria adversarial: `NUMERAL_TR` imprimia 'mientras el Propietario no declare otros' y no habia via para declararlos. Entra 'riesgo_admisible_propietario' [A] opcional (no bloquea; sin declarar rigen los maximos de la tabla), leido por `M1._riesgo_del_propietario`, que solo admite ENDURECER el techo: R por encima del maximo recomendado o n por debajo del de la nota al pie es DatoInvalidoError. Verificado: R=0.20 con n=25 lleva el TR de 71 a 113 anios.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -5368,11 +5408,19 @@
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K67" s="6" t="inlineStr"/>
-      <c r="L67" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — Mismo cierre que MAT-O13: V1 y V2 salen del mismo tipo de frase ('se recomienda') y ahora los dos numerales lo dicen. Ademas el caracter de los dos viaja a la memoria por una via que no depende de que el punto se evalue (`UMBRALES_DE_VERIFICACION`).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -5414,11 +5462,19 @@
       <c r="I68" s="6" t="inlineStr"/>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K68" s="6" t="inlineStr"/>
-      <c r="L68" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — `TABLA_09_FILAS` transcribe las TRES columnas (MINIMO / NORMAL / MAXIMO) y las DOS subfilas de metal corrugado con su nombre literal; `MANNING` pasa a ser vista derivada (n_min, n_max), no una copia. Las claves declaran la subfila: 'metal_corrugado_dren_aguas_lluvias' y 'metal_corrugado_subdren', 'concreto_tubo_recto', 'madera_duelas'. `M2._MANNING_CLAVE` declara que material toma que subfila y por que (una alcantarilla es dren de aguas lluvias, no sub-dren; el concreto es tubo recto y libre de basuras, no tubo de alcantarillado con camaras). Por que el calculo no usa la columna NORMAL queda escrito: la regla de doble n pide los dos extremos, no el valor corriente. `Material.fila_manning` lleva la fila literal a la memoria.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6070,11 +6126,19 @@
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K80" s="6" t="inlineStr"/>
-      <c r="L80" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — `M5.NUMERAL_V1` deja de ser el numeral pelado: lleva RD, pag. impresa 79, el texto literal del 4.1.1.3.7 b) y el matiz de RECOMENDACION, igual que NUMERAL_V2, mas la declaracion de que el proyecto lo aplica como umbral duro. El comportamiento no cambia. Verificado contra el PDF: 'Se recomienda que el diseño hidraulico considere como minimo el 25 % de la altura, diametro o flecha de la estructura' (pag. impresa 79).</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -6124,11 +6188,19 @@
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K81" s="6" t="inlineStr"/>
-      <c r="L81" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — 'v_max_tmc' y 'v_max_hdpe' pasan de 4.6 a 4.572 m/s: 15 ft x 0.3048 = 4.572 exactos, y 4.6 quedaba 0.6 % POR ENCIMA de un techo que el propio criterio declara duro. Los dos criterios declaran ademas que la Tabla 8-4 de WSDOT NO esta en normas/ y que la cita no es auditable contra el repositorio. DEFECTO REPORTADO CONTRA LA HOJA DE RUTA, no corregido aqui: la fila V3 de la tabla de la Fase 5 de docs/hoja_de_ruta_alcantarillas_v8.md sigue diciendo 'TMC y HDPE: PPI/FHWA, valor por extraer' -- el criterio esta cerrado y la fuente que lo cerro es WSDOT, no PPI/FHWA. || 76791d0 -- tres referencias cruzadas se quedaron en 4.6 (el modo de fallo de SIS-A-20): docstring de M2, `verificacion_pendiente` de 'clases_producto_por_relleno' y un docstring de test.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -10486,11 +10558,19 @@
       <c r="I166" s="6" t="inlineStr"/>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K166" s="6" t="inlineStr"/>
-      <c r="L166" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L166" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — El titulo de la Tabla N 10 se transcribe con la unidad -- 'Velocidades maximas admisibles (m/s) en conductos revestidos' -- en los tres sitios que lo citaban sin ella: `constantes_normativas.TABLA_10_TITULO`, `M5.NUMERAL_V3` y la `fuente` de 'v_max_concreto_eleccion'. Verificado contra el PDF, pag. impresa 76. || 76791d0 -- `bloque_umbrales` reintrodujo el mismo defecto que cerraba: rotulaba 'Texto literal' dos composiciones que no lo eran (prosa del proyecto en TR, la tabla reformateada en V3) y el titulo de la Tabla N 02 no iba verbatim. `texto` pasa a ser tupla de citas verbatim impresas por separado; lo que no es cita va en `transcripcion`.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -10532,11 +10612,19 @@
       <c r="I167" s="6" t="inlineStr"/>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K167" s="6" t="inlineStr"/>
-      <c r="L167" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L167" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — Los nombres de fila se transcriben completos y literales. Tabla N 02 (`TABLA_02_FILAS`): 'Alcantarillas de paso de quebradas importantes y badenes' y 'Alcantarillas de paso quebradas menores y descarga de agua de cunetas', ademas de las otras cuatro filas de la tabla. Tabla N 10 (`TABLA_10_FILAS`): 'Mamposteria de piedra y concreto', y su valor deja de escribirse (2.0, 2.0) -- un par que la fuente no imprime -- para quedar en (2.0,). `M5.v3_velocidad_maxima` toma `max()` de la fila en vez de desempaquetar dos valores. || 76791d0 -- la transcripcion se anunciaba completa y dejaba la fila 'Puentes (*)' con su marcador y sin la nota. Se agregan TABLA_02_NOTA_PUENTES y TABLA_02_NOTA_IMPORTANCIA, y TABLA_02_NOTAS reune las cuatro.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -10916,11 +11004,19 @@
       <c r="I175" s="6" t="inlineStr"/>
       <c r="J175" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K175" s="6" t="inlineStr"/>
-      <c r="L175" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K175" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L175" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — `Material.v_max_rango: Optional[Tuple[float,float]]` se parte en dos campos que no se confunden: `v_max_tabla10: Optional[Tuple[float, ...]]` (la fila literal de la Tabla N 10; None si el material no tiene fila) y `v_max_adoptado: Optional[float]` (el techo escalar del criterio [C] de TMC y HDPE). Ya no hay un campo anotado como par que transporte un escalar. El docstring de `v_max_definida` deja de decir 'False para TMC y HDPE' -- hoy devuelve True para los tres -- y explica cuando vuelve a False.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -12106,11 +12202,19 @@
       <c r="I198" s="6" t="inlineStr"/>
       <c r="J198" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K198" s="6" t="inlineStr"/>
-      <c r="L198" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S5)</t>
+        </is>
+      </c>
+      <c r="L198" s="6" t="inlineStr">
+        <is>
+          <t>00da460 — `DIAMETRO_MIN_SELVA_ALTA` se renombra `DIAMETRO_MIN_TMC_SELVA_ALTA_RECOMENDADO` -- dos de las tres restricciones en el nombre -- y se acompaña del texto literal (`..._TEXTO`: 'Se recomienda utilizar... como diametro minimo alcantarillas TMC Ø 48"') y de las cuatro caracteristicas geomorfologicas que el numeral exige (`..._CONDICIONES`), verificadas sobre el PDF, pag. impresa 79. Sigue sin consumidor de calculo y sigue declarado en CONSTANTES_DE_REFERENCIA.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2334,11 +2334,19 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K8" s="6" t="inlineStr"/>
-      <c r="L8" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — cierra la mitad documental y la etiqueta: 'HW_D_max' pasa de [C] a [A] con la cita verificada contra el PDF (num. 2.2.5 d) 'Agency Constraints', pag. impresa 2.10; la v8 citaba la 2.14, que trata de espolones de escombros y seguridad vial), y los DOS docstrings que afirmaban que M5 verifica V4b (M4_control, modelos.ControlEntrada) dejan de afirmarlo. QUEDA ABIERTO el cableado del chequeo, que el conflicto #1 prohibe hacer antes de cerrar la etiqueta y que la tabla maestra asigna a S14.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2612,11 +2620,19 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K13" s="6" t="inlineStr"/>
-      <c r="L13" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — mismo paquete que MAT-D2. Los dos docstrings corregidos; la constancia de la fila V4b en M5.verificaciones_no_evaluadas() se actualiza (la procedencia del umbral ya no esta en revision abierta: esta cerrada) y pasa a LEER del criterio su valor, etiqueta y sensibilidad con ca.criterio_efectivo, que no registra uso -- es la unica via por la que 'HW_D_max' llega a la memoria, porque no lo consume nadie. QUEDA ABIERTO que siga sin consumidor, diferido a S14 por el conflicto #1.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2890,11 +2906,19 @@
       <c r="I18" s="6" t="inlineStr"/>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr"/>
-      <c r="L18" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — M4.control_entrada() ya no puede devolver HW negativo: _exigir_hw_no_negativo() lanza DisenoNoFactibleError cuando HWi/D &lt;= 0, en las tres ramas. Es un rechazo, no un piso: adoptar una carga en su lugar (H_c, cero) seria rellenar un vacio en silencio. Caso de la ficha recomputado a mano y reproducido: D=0.90, Q=0.05, S=0.40 -&gt; H_c=0.1694795575, q*=0.1500349023, HW/D=-0.011469, HW=-0.010322 m, umbral de signo S*=0.3770624442. QUE NO CIERRA, y queda escrito en el codigo y en la hoja de ruta: el rechazo elimina el SIGNO, no el error. A S=0.37706 el diseño se sigue aceptando con HW=+1e-6 m y V4/7.A evaluados 0.1695 m del lado no conservador; de los 0.1798 m de error de la ficha retira 0.0103, el 5.7 %. En el corredor real (S_cauce=0.006-0.008) no se dispara nunca. Acotar el rango de validez entero de la correccion exige una pendiente maxima que ninguna fuente escribe. La excepcion se cambio de DatoInvalidoError a DisenoNoFactibleError tras la auditoria adversarial: una S de 0.40 es del tipo correcto, cae dentro de dominios.S_CAUCE_MAX y no contradice a nadie -- no hay dato que el revisor deba corregir.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -3622,11 +3646,19 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr"/>
-      <c r="L32" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — la discrepancia declarada deja de existir: el codigo mantiene 19.63 y la hoja de ruta se corrige a 19.63. El comentario de constantes_normativas ya no anuncia una discrepancia abierta. Hallazgo de C11 cerrado de paso por el conflicto #6.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3952,11 +3984,19 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K39" s="6" t="inlineStr"/>
-      <c r="L39" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — 'ke_entrada': la pagina pasa de C.2 (que es el numero de la TABLA leido como pagina; la pag. impresa C.2 es el indice de cartas del Apendice C) a C.6, verificada contra el PDF, y se retira el rotulo CITA CERRADA que la sostenia. Se transcribe ademas la fila tal como se imprime -- 'Square-edge 0.5' sangrada bajo 'Headwall or headwall and wingwalls' --, porque ninguna fila dice literalmente 'square edge with headwall'. Hallazgo de C11 cerrado de paso: C06 reescribia ese mismo campo por NOR-HDS-04.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4002,11 +4042,19 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr"/>
-      <c r="L40" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — reetiquetado [C]-&gt;[A]: HDS-5 no cubre el vacio porque no prescribe HW/D; su num. 2.2.5 d) DESCRIBE lo que imponen las agencias viales de EE. UU. Cita corregida (2.14 -&gt; 2.10) y transcrita literal, con la salvedad de que el pasaje no existe en la copia de 1985 de normas/. Se declara de donde sale el 1.5: el extremo superior, el menos restrictivo, de una banda ajena. Hoja de ruta v8 corregida en sus cuatro filas de HW/D. Tras la auditoria adversarial, la constancia de M5 imprime el valor, la etiqueta y la sensibilidad leidos del propio criterio, para que la reetiqueta llegue a la memoria y no se quede en el archivo.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -4048,11 +4096,19 @@
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K41" s="6" t="inlineStr"/>
-      <c r="L41" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — h_o deja de ser una formula 'sin numeral' y sin limite: num. 3.3.3 'Outlet Control', pag. impresa 3.24, con sus TRES condiciones transcritas verbatim y cada una atribuida a su sitio de la pagina (H_O_NUMERAL, H_O_CONDICION_TEXTO, H_O_FORMA_MAXIMO_TEXTO, H_O_CONDICION_APLICACION). DOS de las tres SE EVALUAN punto por punto: los limites HW/D &lt; 0.75 ('should not be used') y HW/D &lt; 1.2 ('caution'), como constantes [N] H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculados en control_salida(), filtrados por si el control de salida gobierna -- que es como la fuente los escribe -- e impresos EN LA MEMORIA DEL PUNTO junto a su HW. Es lo que la auditoria adversarial refuto de la primera version, que los declaraba sin evaluarlos pudiendo: el punto A-02 del CSV de ejemplo da HW/D=0.675 con el control de salida gobernando, y la memoria no lo decia. La condicion llega ademas siempre por UMBRALES_DE_VERIFICACION, tambien en la corrida bloqueada. QUEDA ABIERTO lo unico que no se puede evaluar sin un perfil de la lamina de agua: que el barril fluya lleno en la mayor parte de su longitud. Lo cerraria el procedimiento de barril parcialmente lleno del Cap. III.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -5142,11 +5198,19 @@
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K62" s="6" t="inlineStr"/>
-      <c r="L62" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — la contradiccion entre las dos ediciones queda escrita en constantes_normativas, en M4_control y en el fixture, resuelta a favor de la 3a ed. (conflicto #6). Se retira la afirmacion falsa de la 'coincidencia numerica': K = 2g/phi^2 es exacto (2*32.2/1.486^2 = 29.16; 2*9.81456 = 19.629) y lo unico que separa 19.63 de 19.62 es cual g. La hoja de ruta v8 corregida a 19.63 en sus cuatro menciones; con eso cierra tambien la discrepancia abierta que el codigo declaraba.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5250,11 +5314,19 @@
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K64" s="6" t="inlineStr"/>
-      <c r="L64" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — conflicto #6, cerrado junto con MAT-X5 y MAT-O12 (C06). La hoja de ruta v8 escribe 19.63 en sus cuatro menciones (Sec. 4.3, nota de unidades, Anexo C y notas criticas), con la cita verificada: 3a ed., num. 3.1.4, ec. (3.4b), pag. impresa 3.10. Hallazgo de C11 cerrado de paso.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -5964,11 +6036,19 @@
       <c r="I77" s="6" t="inlineStr"/>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K77" s="6" t="inlineStr"/>
-      <c r="L77" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — corregido en la hoja de ruta v8, que es donde estaba el defecto: la linea 'Transicion: interpolar linealmente' presentaba la recta como si fuera el metodo del HDS-5. Ahora dice que HDS-5 empalma con una curva tangente sin ecuacion publicada, que la recta la prescribe la hoja de ruta y que es la simplificacion adoptada 'metodo_transicion_hds5' [C]. El codigo ya lo declaraba bien.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -6072,11 +6152,19 @@
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K79" s="6" t="inlineStr"/>
-      <c r="L79" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — la frase del fixture 'el propio HDS-5 declara' queda acotada a la edicion que lo declara: CP-8 nombra ahora las dos copias de normas/ (hif12026, 3a ed., num. 3.1.4 ec. (3.4b) pag. impresa 3.10, que imprime 19.63; y la de 1985, cuyas ecs. (4b) y (5) imprimen 29 con rotulos duales 'ft (m)' en la pag. 54 del PDF y g = 32.2 ft/s/s (9.8 m/s/s) en la 53). Verificado contra los dos PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -6304,11 +6392,19 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr"/>
-      <c r="L83" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — el comentario ya no cita renglones de la hoja de ruta, ni los corregidos: al corregirse la hoja no queda discrepancia que localizar, y citar numeros de linea de un documento vivo es lo que produjo este hallazgo. Hallazgo de C11 cerrado de paso.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -7344,11 +7440,19 @@
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K103" s="6" t="inlineStr"/>
-      <c r="L103" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — el docstring de ControlEntrada.HW_sobre_D deja de decir que es 'lo que compara V4b': esa comparacion no existe. Se dice lo que se sostiene (hoy solo lo leen los tests) y por que el campo se conserva. QUEDA ABIERTO que no tenga lector de produccion, hasta el cableado de V4b (S14).</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -10466,11 +10570,19 @@
       <c r="I164" s="6" t="inlineStr"/>
       <c r="J164" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K164" s="6" t="inlineStr"/>
-      <c r="L164" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L164" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — KU_METRICO, los dos Q_LIM y las ecuaciones dejan de atribuirse a la Tabla A.1: estan en el texto del num. A.2, pags. impresas A.1-A.2 (KU en la lista de variables de A.2.1, pag. A.2, verificado contra el PDF). De la Tabla A.1 (pag. A.8) salen solo K, M, c e Y. Se anota tambien por que los limites son los ingleses (3.5/4.0) y no los del parentesis SI. El docstring de M4 que decia 'ecuaciones literales de la Tabla A.1' queda corregido. Hallazgo de C11 cerrado de paso.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -12156,11 +12268,19 @@
       <c r="I197" s="6" t="inlineStr"/>
       <c r="J197" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K197" s="6" t="inlineStr"/>
-      <c r="L197" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S6)</t>
+        </is>
+      </c>
+      <c r="L197" s="6" t="inlineStr">
+        <is>
+          <t>3ed6b22 + 4f32683 — anotado donde vive el primero de los dos 0.7: junto a HDS5_INLET (Ks = +0.7, correccion por pendiente del control de ENTRADA, num. A.2.1 pag. impresa A.2) y en el criterio 'ke_entrada' (ke = 0.7 'Mitered to conform to fill slope', perdida de entrada del control de SALIDA, Tabla C.2 pag. impresa C.6). Se dice que coinciden en valor y en condicion y en nada mas, y que con la embocadura adoptada (a ras del muro) no coinciden.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — M4.control_entrada() ya no puede devolver HW negativo: _exigir_hw_no_negativo() lanza DisenoNoFactibleError cuando HWi/D &lt;= 0, en las tres ramas. Es un rechazo, no un piso: adoptar una carga en su lugar (H_c, cero) seria rellenar un vacio en silencio. Caso de la ficha recomputado a mano y reproducido: D=0.90, Q=0.05, S=0.40 -&gt; H_c=0.1694795575, q*=0.1500349023, HW/D=-0.011469, HW=-0.010322 m, umbral de signo S*=0.3770624442. QUE NO CIERRA, y queda escrito en el codigo y en la hoja de ruta: el rechazo elimina el SIGNO, no el error. A S=0.37706 el diseño se sigue aceptando con HW=+1e-6 m y V4/7.A evaluados 0.1695 m del lado no conservador; de los 0.1798 m de error de la ficha retira 0.0103, el 5.7 %. En el corredor real (S_cauce=0.006-0.008) no se dispara nunca. Acotar el rango de validez entero de la correccion exige una pendiente maxima que ninguna fuente escribe. La excepcion se cambio de DatoInvalidoError a DisenoNoFactibleError tras la auditoria adversarial: una S de 0.40 es del tipo correcto, cae dentro de dominios.S_CAUCE_MAX y no contradice a nadie -- no hay dato que el revisor deba corregir.</t>
+          <t>3ed6b22 + 4f32683 — M4.control_entrada() ya no puede devolver HW negativo: _exigir_hw_no_negativo() lanza DisenoNoFactibleError cuando HWi/D &lt;= 0, en las tres ramas. Es un rechazo, no un piso: adoptar una carga en su lugar (H_c, cero) seria rellenar un vacio en silencio. Caso de la ficha recomputado a mano y reproducido: D=0.90, Q=0.05, S=0.40 -&gt; H_c=0.169480, q*=0.150035, HW/D=-0.011469, HW=-0.010322 m, umbral de signo S*=0.377062. QUE NO CIERRA, y queda escrito en el codigo y en la hoja de ruta: el rechazo elimina el SIGNO, no el error. A S=0.37706 el diseño se sigue aceptando con HW=+1e-6 m y V4/7.A evaluados 0.1695 m del lado no conservador; de los 0.1798 m de error de la ficha retira 0.0103, el 5.7 %. En el corredor real (S_cauce=0.006-0.008) no se dispara nunca. Acotar el rango de validez entero de la correccion exige una pendiente maxima que ninguna fuente escribe. La excepcion se cambio de DatoInvalidoError a DisenoNoFactibleError tras la auditoria adversarial: una S de 0.40 es del tipo correcto, cae dentro de dominios.S_CAUCE_MAX y no contradice a nadie -- no hay dato que el revisor deba corregir.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -3084,11 +3084,19 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="inlineStr"/>
-      <c r="L21" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S7)</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>0f3cf28 + 0f63edd — la pendiente deja de elegirse dos veces. `modelos.ResultadoHidraulico` gana el campo obligatorio `S` -- la pendiente CON QUE corrio el diseño --, que `M4.resolver_control` llena con la que recibio, y `M7.compatibilidad_geometrica` PIERDE su parametro `S`: la lee de `resultado.S`. `cli._fase_7` ya no puede omitirla ni discrepar. Caso recomputado a mano: punto con cota de entrada 42.10 msnm, L = 20.0 m, cota de fondo del receptor 41.30 y S_cauce 0.006; con S_conducto declarada 0.045 la caida es 0.900 m, la cota de salida 41.200 y G2 INCUMPLE. Antes esa misma corrida daba caida 0.120 y salida 41.980 con G2 cumplida, o sea el conducto entregando 0.10 m BAJO el fondo del receptor sin que nada lo dijera. La MEMORIA lo imprime ahora, que es donde el hallazgo hacia dano: `M11_reporte._tabla_diseno` saca S en la fila de Hidraulica, al lado de Q, y la CLI en el bloque de Fase 4 (texto y JSON). Antes la unica pendiente del entregable era la columna S_cauce de los datos de partida, que en ese punto NO es la del diseño: la memoria traia 'Pendiente del cauce 0.010 m/m' junto a 'caida 0.900 m' y la caida no se podia recomputar. Verificado sobre la memoria generada.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -5708,11 +5716,19 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K71" s="6" t="inlineStr"/>
-      <c r="L71" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S7)</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>0f3cf28 + 0f63edd — defecto documental de la hoja de ruta v8, corregido en la hoja. La fila V4 de la tabla de Fase 5 pasa de «HW &lt;= cota de subrasante - resguardo(CBR)» a «cota de entrada + HW &lt;= cota de subrasante - resguardo(CBR)», con una NOTA DE DATUM en la Sec. 5.1. El codigo nunca lo escribio mal (`M5.v4_carga_entrada` suma `cota_entrada_supuesta`) y ahora su docstring lo dice con el sumando explicito. La forma nivel-contra-nivel se verifico contra el PDF primario (Manual de Suelos, num. 4.5.4, pag. impresa 42): «El nivel superior de la sub rasante debe quedar encima del nivel de la napa freatica como minimo a 0.60 m ...». Los dos terminos que el numeral compara son del mismo tipo.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -5762,11 +5778,19 @@
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K72" s="6" t="inlineStr"/>
-      <c r="L72" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S7)</t>
+        </is>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>0f3cf28 + 0f63edd — misma correccion documental en la Sec. 7.A: la segunda condicion del max{} pasa de «HW + resguardo + e_paq» a «cota entrada + HW + resguardo + e_paq», con la equivalencia con V4 escrita en la propia hoja. El algebra se verifico: con e_paq = cota rasante - cota subrasante, «cota rasante &gt;= cota entrada + HW + resguardo + e_paq» es exactamente «cota entrada + HW &lt;= cota subrasante - resguardo». `M7.tamizado_rasante` ya calculaba `por_resguardo = entrada + HW + resguardo + e_paq`. Las cuatro copias de la formula incoherente en docstrings del codigo (`M7` cabecera y `tamizado_rasante`, `modelos.CondicionRasante` y `modelos.TamizadoRasante`) tambien se corrigieron.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -12634,11 +12658,19 @@
       <c r="I204" s="6" t="inlineStr"/>
       <c r="J204" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K204" s="6" t="inlineStr"/>
-      <c r="L204" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S7)</t>
+        </is>
+      </c>
+      <c r="L204" s="6" t="inlineStr">
+        <is>
+          <t>0f3cf28 + 0f63edd — la resta se escribe una sola vez, con su guarda. Nueva funcion publica `M5_verificaciones.altura_relleno_sobre_clave(punto, material, D)`, que calcula subrasante menos clave fisica y lanza `DatoInvalidoError` sobre 'cota_subrasante' cuando la clave queda al nivel de la subrasante o por encima. La usan `v7_flotacion` y `cli._fase_8`, que antes repetia la resta sin guarda. El hallazgo decia «hoy sin efecto porque M8 se detiene antes», y esa es la razon de cerrarlo ahora: el dia en que 'clases_producto_por_relleno' se declare, la Fase 8 entraria a la tabla de la norma de producto con una altura negativa.</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2164,11 +2164,19 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr"/>
-      <c r="L5" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S8)</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>9ec09d6 + 65dbebe — el cabezal deja de heredar el minimo del conducto. M9.factores_de_carga('Resistencia I')['EV'] pasa de {max 1.35, min 0.90} a {max 1.35, min 1.00}: la fila 'Muros y estribos de retencion', que es la que la tabla da a un muro de contencion con zapata. El 0.90 rebajaba un 10 % el peso de tierra que estabiliza E2 (volteo), E3 (deslizamiento) y la flotacion. Hoy ningun modulo de produccion consume ese numero -- la estabilidad automatica sigue bloqueada por 'predimensionamiento_cabezal' --, de modo que no cambia ningun resultado impreso; lo que cierra es que el numero que se consumira cuando se desbloquee ya es el correcto y esta atado a su fila CONTRADICE A LA FICHA EN UN PUNTO, y hay que decirlo (regla 3): la ficha sostiene que usar 0.90 rebaja el peso estabilizante de tierra en E2, E3 y V7 y que esa es la direccion INSEGURA. Es al reves. Minorar lo que ESTABILIZA es la direccion conservadora -- es lo que el marco LRFD hace a proposito y la razon por la que V7 minora DC y EV --, de modo que subir el minimo del cabezal de 0.90 a 1.00 RELAJA volteo y deslizamiento alrededor de un 8 %. El hallazgo se cierra igual y con el valor que pide, porque el defecto real es de conformidad normativa (el par no era ninguna fila) y porque AASHTO C3.4.1, pag. impresa 3-15, prescribe ese 1.00 literalmente para el empuje vertical sobre el talon de un muro en voladizo al evaluar deslizamiento. Lo que no se sostiene es el argumento de seguridad de la ficha, y queda escrito en el criterio, en M9 y en el test para que nadie lea la correccion como un endurecimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -3030,11 +3038,19 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr"/>
-      <c r="L20" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S8)</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>9ec09d6 + 65dbebe — el par unico de EV desaparece. La Tabla 2.4.5.3.1-2 del Manual de Puentes (= 3.4.1-2 AASHTO) se transcribe COMPLETA, sus dieciocho filas, como [N] en constantes_normativas.TABLA_GAMMA_P_FILAS, y 'factores_carga_aashto' pasa de [C] a [A] guardando SOLO strings: que fila de gamma_p describe a cada estructura. concreto -&gt; 'Estructura rigida enterrada'; hdpe -&gt; 'Alcantarillas termoplasticas'; tmc -&gt; la subfila flexible 'Entre otros'; cabezal -&gt; 'Muros y estribos de retencion'. M8.factores_carga_flotacion recibe ahora el material y M5.v7_flotacion se lo pasa; modelos.FactoresFlotacion lleva el campo fila_gamma_EV, de modo que el resultado de V7 dice de que fila salio su gamma. Ya no se puede escribir un par que no sea una fila: la eleccion se contrasta contra la tabla y un nombre inventado es DatoInvalidoError. Recomputado a mano y reproducido: concreto D=0.90, t=0.10 -&gt; D_ext=1.10; cota entrada 42.10, subrasante 44.05 -&gt; clave 43.10, relleno 0.95 m; con gamma_relleno 18.0, U = 9.81*(pi/4)*1.10^2 = 9.322755 kN/m y EV = 18.81 kN/m; estabilizante 0.90*18.81 = 16.929 kN/m contra 1.00*U. V7 NO cambia de valor para ninguno de los tres materiales -- las tres filas enterradas tienen minimo 0.90 --, que era la condicion del conflicto #2</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -3292,11 +3308,19 @@
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S8)</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>9ec09d6 + 65dbebe — el vacio se retira porque no existia. Verificado leyendo el PDF del Manual de Puentes por el encabezado impreso de cada pagina, no por aritmetica de desfase: las Tablas 2.4.5.3.1-1 'Combinaciones de Carga y Factores de Carga' y 2.4.5.3.1-2 'Factores de carga para cargas permanentes, gamma_p' estan las DOS en la pagina impresa 143, completas y con sus valores, dentro del rango de paginas que el propio repositorio citaba al declarar el vacio. Las dos estan hoy transcritas como [N] en constantes_normativas y la afirmacion negativa se retira de los cinco sitios donde vivia: el comentario de COMBINACIONES_AASHTO, la justificacion del criterio, el docstring de modelos.CombinacionCarga, el de M9.combinaciones y la fila del manifiesto (Sec. 3, Sec. 8 y Sec. 12). Corregidas ademas tres paginas mal citadas por el criterio: la Tabla 3.4.1-1 no esta en la 3-14 de AASHTO sino en la 3-17, y las dos del Manual no estan en '143 y 146' sino las dos en la 143 (la 146 es una lamina fotografica). Como el vacio no existia, el [C] tampoco se sostiene: los numeros son [N] via MTC y lo unico [A] es la eleccion de fila</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -3604,11 +3628,19 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="inlineStr"/>
-      <c r="L31" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S8)</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>9ec09d6 + 65dbebe — mismo paquete que MAT-D15. Ademas se RETIRA la afirmacion falsa del texto: el criterio decia que la Tabla 3.4.1-2 distingue 'EH activo (1.50/0.90) de EH en reposo (1.35, sin minimo declarado por la fuente)'. Verificado leyendo los dos PDF: el Manual de Puentes escribe 'En reposo. 1.35 / 0.90' y AASHTO 'At-Rest 1.35 / 0.90'. Se retira tambien la otra afirmacion en bloque, 'la tabla fuente da EV minimo 0.90, no 1.00': la tabla no tiene un EV minimo unico y la frase solo era cierta para la fila del conducto</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -5956,11 +5988,19 @@
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K75" s="6" t="inlineStr"/>
-      <c r="L75" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S8)</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>9ec09d6 + 65dbebe — gamma_EH en reposo recupera su minimo. Las tres filas de EH estan hoy en TABLA_GAMMA_P_FILAS con sus pares completos, verificados contra el PDF: Activa 1.50/0.90, En reposo 1.35/0.90, AEP Para paredes ancladas 1.35/N-A. El N-A que el criterio le atribuia al reposo pertenece a la fila siguiente, que comparte con ella el maximo 1.35: era un corrimiento de una fila. La celda N-A viaja como constantes_normativas.GAMMA_P_NO_APLICA y pedir ese extremo es DatoInvalidoError, no un None que aguas abajo seria un cero</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2748,11 +2748,19 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K15" s="6" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - CIERRA LA MITAD DECLARATIVA, NO EL CABLEADO, y no puede cerrarlo: el conflicto #8 de la seccion 6 del plan es vinculante y prohibe cablear 'clase_sitio' antes de resolver la premisa (S13). Lo que se hizo: dejar escrito en el propio criterio que ningun modulo de produccion lo invoca, que por eso no entra en criterios_usados() ni la memoria imprime la adopcion, y por que cablearlo hoy seria peor -- la memoria declararia formalmente una clasificacion que la fuente no sostiene. QUEDA ABIERTO el cableado, asignado a S14.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2802,11 +2810,19 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - CIERRA LA INCOHERENCIA, NO EL CABLEADO. La tabla ya tiene fila F (con su asterisco y su Nota 2) y 'F_pga' declara sobre que filas se lee y por que la F no esta entre ellas, de modo que las dos defensas dejan de contradecirse. Sigue siendo cierto que solo 'F_pga' llega a la memoria: eso es el cableado de SIS-B-01, prohibido por el conflicto #8 hasta S13/S14.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -3578,11 +3594,19 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K30" s="6" t="inlineStr"/>
-      <c r="L30" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - LA PREMISA QUEDA DECLARADA Y DETENIDA, que es lo que el conflicto #8 ordena, no resuelta. La justificacion de 'clase_sitio' deja de afirmar que el sitio es Clase F como cosa cerrada y registra lo verificado: el salto 'licuable -&gt; Clase F' no lo escribe ninguno de los dos documentos que el criterio invoca (AASHTO trata la licuefaccion en su Art. 10.5.4.2, por via distinta de la clase de sitio) y quien clasifica los licuables aparte es E.030 en su S5. La discrepancia entre los dos esquemas queda transcrita en `E030_S5_VS_CLASE_F`. RESOLVERLA es S13.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -4622,11 +4646,19 @@
       <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr"/>
-      <c r="L50" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La justificacion de 'F_pga' se reescribe: dice de que filas sale la envolvente, y dice por que no estan las otras tres -- A y B son roca, F no da factor sino la exigencia de estudio de la Nota 2 -- cruzando por fin las dos afirmaciones que convivian sin tocarse.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -4726,11 +4758,19 @@
       <c r="I52" s="6" t="inlineStr"/>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K52" s="6" t="inlineStr"/>
-      <c r="L52" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - `FACTOR_MURO_TABLA` retirada. El numeral no presenta ninguna tabla y fija un solo valor, permisivo: queda `REDUCCION_KH_POR_DESPLAZAMIENTO = 0.5` y el 1.0 como ausencia de reduccion. El criterio declara si se aplica, no que fila se elige. Corregido tambien el rango '25-50 mm', que redondeaba '1.0 a 2.0 in' y perdia el 'o mas'. Numeral corregido a 2.8.1.1.14.2.2.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -4776,11 +4816,19 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K53" s="6" t="inlineStr"/>
-      <c r="L53" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La afirmacion falsa ('practica corriente; no fijado por el Manual de Puentes') se retira y se sustituye por el texto literal del numeral. Misma correccion que MAT-O11.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -4822,11 +4870,19 @@
       <c r="I54" s="6" t="inlineStr"/>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K54" s="6" t="inlineStr"/>
-      <c r="L54" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La afirmacion negativa se retira. La fila F esta transcrita con su asterisco en las cinco columnas y la Nota 2 literal; elegirla es `DatoInvalidoError`, porque no hay numero que leer ahi. La etiqueta [C] que la sostenia se corrige en el criterio: no habia vacio que cubrir.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -5184,11 +5240,19 @@
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K61" s="6" t="inlineStr"/>
-      <c r="L61" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - Misma correccion que MAT-O2. Se declara por que gana AASHTO y no por preferencia de fuente: con el signo menos K_AE diverge y el caso limite deja de dar el Ka de Coulomb.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5694,11 +5758,19 @@
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K70" s="6" t="inlineStr"/>
-      <c r="L70" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La errata se declara en el punto de uso (`k_ae_mononobe_okabe`), como dato (`K_AE_ERRATA_MANUAL`, con las dos citas y sus paginas) y en la memoria (`condicion_normativa_cabezal`). El codigo NO se toca: sigue a AASHTO, que es lo correcto. Reportado ademas contra la hoja de ruta, que no advertia de la discrepancia.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6162,11 +6234,19 @@
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K78" s="6" t="inlineStr"/>
-      <c r="L78" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - El 0.0 pasa a constantes_normativas como `K_V_PRESCRITO` [N], con el texto literal del num. 2.8.1.1.14.2.1 y sus dos casos reservados. El criterio 'k_v' deja de guardar el numero y declara cual de los dos regimenes rige; si rigiera el reservado admite un numero del proyectista, porque el Manual no escribe ninguno para ese caso.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -6518,11 +6598,19 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K84" s="6" t="inlineStr"/>
-      <c r="L84" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - P_IR = k_h*(W_w + W_s) implementado (`fuerza_inercia_muro`), con W_s definido como lo define la fuente -- suelo inmediatamente encima del muro, incluido el talon -- y no como el relleno del trasdos. La combinacion 100/50 - 50/100 en `demanda_sismica_cabezal`, con el piso 'no menor que el empuje activo estatico' aplicado al segundo caso y el mas desfavorable como gobernante. El ensamble automatico sigue detenido en 'predimensionamiento_cabezal', que es vacio ya declarado y al que se le suma el ancho del talon.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -6614,11 +6702,19 @@
       <c r="I86" s="6" t="inlineStr"/>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K86" s="6" t="inlineStr"/>
-      <c r="L86" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La fila S5 deja de ser 'referencia muerta': su prohibicion condicionada se transcribe literal (`E030_S5_TEXTO`), se lee con precision -- prohibicion CON salvedad de estudio especifico, ni bloqueo duro ni referencia muerta -- y llega a la memoria por `condicion_normativa_cabezal`.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -6860,11 +6956,19 @@
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K91" s="6" t="inlineStr"/>
-      <c r="L91" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - Misma correccion que MAT-O3: se toma la via 'declarar la hipotesis' de la resolucion, con la desviacion acotada y dicha.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -6914,11 +7018,19 @@
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K92" s="6" t="inlineStr"/>
-      <c r="L92" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - Las dos mitades cerradas: k_h0 deja de ser incondicional (ver MAT-O4) y k_v pasa de [A] a [N] condicionado (ver MAT-O11).</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -7026,11 +7138,19 @@
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K94" s="6" t="inlineStr"/>
-      <c r="L94" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - Misma correccion que MAT-D6: la seccion que la hoja de ruta citaba para k_h0 exigia el termino omitido, y ahora esta. La hoja de ruta v8 se corrige en su Sec. 9.2, que es donde estaba el defecto.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -7288,11 +7408,19 @@
       <c r="I99" s="6" t="inlineStr"/>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K99" s="6" t="inlineStr"/>
-      <c r="L99" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - El rotulo de la columna se transcribe como lo imprime la tabla, 'PGA &gt; 0.50', y la lectura del borde se declara en el criterio nuevo 'F_pga_lectura_columna_extrema' con su consecuencia dicha: leyendo la columna anterior la fila D daria 1.1 y la envolvente subiria un 10 %. La Nota 1 se implementa (`factor_sitio_desde_tabla` interpola).</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -7338,11 +7466,19 @@
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K100" s="6" t="inlineStr"/>
-      <c r="L100" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La regla ni se implementaba ni se descartaba; ahora se implementa Y se descarta con motivo. Ver MAT-O4.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -7620,11 +7756,19 @@
       <c r="I105" s="6" t="inlineStr"/>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K105" s="6" t="inlineStr"/>
-      <c r="L105" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La sensibilidad (0.0, 0.5) se retira, con la razon escrita: sugeria una libertad que el numeral no concede -- el cero es prescrito -- y su comentario ('0.5*k_h') no coincidia ni con su propio extremo ni con lo que prescribe la hoja de ruta.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -7906,11 +8050,19 @@
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K110" s="6" t="inlineStr"/>
-      <c r="L110" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - Hipotesis declarada como dato (`HIPOTESIS_EMPUJE_BAJO_NF`), con la cita literal de AASHTO 3.11.3 'Presence of Water' (pag. impresa 3-118) y la desviacion cuantificada (+25 % local). Llega a la memoria. No se corrige el calculo: hacerlo exige un peso especifico sumergido que el expediente no tiene, y aplicarlo con el unico gamma declarado ALIVIARIA el empuje sin dato que lo sostenga.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -7960,11 +8112,19 @@
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K111" s="6" t="inlineStr"/>
-      <c r="L111" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La clausula ya es representable: `F_PGA_TABLA` transcrita completa incluye las filas A y B, y `coeficiente_sismico_base` tiene las dos ramas. `cimentacion_en_roca()` resuelve cual aplica con las filas que declara 'F_pga', de modo que la rama de roca queda DESCARTADA de forma trazable y se activaria sola si alguien declarase A o B. Destapado ademas que el parentesis del Manual ('1.2 kh0=FpgaPGA') es una segunda errata: gana la prosa.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -8126,11 +8286,19 @@
       <c r="I114" s="6" t="inlineStr"/>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K114" s="6" t="inlineStr"/>
-      <c r="L114" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - Procedimiento implementado entero: `excentricidad_resultante`, `presion_contacto_base` (Navier dentro del nucleo, distribucion parcial fuera, continuas en e = B/6) y `verificar_excentricidad_sismica`, codigo E6. Y el limite no es el tercio central a secas: depende de gamma_EQ (B/6 a 0.4*B, interpolado), que pasa a ser criterio propio con valor None -- antes vivia como prosa dentro de otro criterio y no podia detener nada.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -8176,11 +8344,19 @@
       <c r="I115" s="6" t="inlineStr"/>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K115" s="6" t="inlineStr"/>
-      <c r="L115" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - La razon se escribe UNA vez, en `M9.FUNCIONES_SIN_CONSUMIDOR`, y la CLI la lee de alli en vez de repetirla en su nota. Mismo patron que `criterios_sin_consumidor`.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -8284,11 +8460,19 @@
       <c r="I117" s="6" t="inlineStr"/>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K117" s="6" t="inlineStr"/>
-      <c r="L117" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - Misma correccion que SIS-B-17: las siete funciones de armado entran en `FUNCIONES_SIN_CONSUMIDOR` con su insumo bloqueado nombrado.</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -8334,11 +8518,19 @@
       <c r="I118" s="6" t="inlineStr"/>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K118" s="6" t="inlineStr"/>
-      <c r="L118" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - Misma correccion que SIS-B-17.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -10266,11 +10458,19 @@
       <c r="I156" s="6" t="inlineStr"/>
       <c r="J156" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K156" s="6" t="inlineStr"/>
-      <c r="L156" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L156" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - El concepto de `Z_E030` deja de atribuir al Art. 11.1 una cifra que ese articulo no imprime: se transcribe la probabilidad que si escribe y el Tr = 475 se declara como derivacion, con la unica pagina de E.030 donde la cifra aparece literal (Anexo III).</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -10312,11 +10512,19 @@
       <c r="I157" s="6" t="inlineStr"/>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K157" s="6" t="inlineStr"/>
-      <c r="L157" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S9)</t>
+        </is>
+      </c>
+      <c r="L157" s="6" t="inlineStr">
+        <is>
+          <t>4f45f15 + e73ab59 - El argumento de ambito del Art. 4 se incorpora, en el codigo y en la hoja de ruta, y se cita por lo que el articulo AFIRMA: acota el ambito a edificaciones. No se le hace decir que excluye expresamente a los puentes, porque no los nombra.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2524,11 +2524,19 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K11" s="6" t="inlineStr"/>
-      <c r="L11" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — la columna A/B/C de la Tabla 5.10.1-1 pasa a ser una declaracion exigida: criterio 'categoria_refuerzo_aashto' [A] con valor None, que detiene los tres recubrimientos de 9.4 con CriterioPendienteError. || 8f48bf5 — test que lo comprueba: hasta aqui la detencion solo vivia en la prosa del docstring.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2574,11 +2582,19 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr"/>
-      <c r="L12" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — el modificador del Art. 5.10.1 (0.8 / 1.0 / 1.2) entra en el calculo via 'factor_recubrimiento_por_ac', alimentado por la durabilidad del concreto. Con a/c &lt;= 0.40 el lado AASHTO cae de 76.2 a 60.96 mm y la conclusion se invierte en 'contra_suelo', tal como anticipaba la ficha. || 8f48bf5 — cerrado del todo tras la auditoria adversarial: el factor de la banda intermedia deja de ser literal del modulo y pasa a criterio [C]; el origen del factor viaja hasta la memoria; y la nota que sostenia que la banda no aplicaba lo hacia dando por sabido el dato de cloruros que este mismo cluster declaro vacio.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3764,11 +3780,19 @@
       <c r="I33" s="6" t="inlineStr"/>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="inlineStr"/>
-      <c r="L33" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — EXCEPCION_REFUERZO_MIN_MURO_TEXTO (Art. 14.8.2, literal) y M9.nota_excepcion_refuerzo_minimo, que la CLI imprime en la memoria: el minimo se aplica entero porque este expediente NO ejerce la excepcion -- no declara juntas de contraccion ni procedimientos de control --, no porque la norma no la ofrezca, que es lo que el codigo afirmaba.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -3810,11 +3834,19 @@
       <c r="I34" s="6" t="inlineStr"/>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr"/>
-      <c r="L34" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — ESPESOR_DOS_CAPAS_REFUERZO = 0.200 m (Art. 14.3.2) y M9.requiere_refuerzo_dos_capas: entre 200 y 250 mm el muro lleva dos capas aunque el acero por temperatura vaya en una cara, que es lo contrario de lo que la memoria imprimia. CIERRA EN PARTE, y se deja dicho: la nota que lo declara sigue sin llamador de produccion porque su insumo es el espesor, que sale de 'predimensionamiento_cabezal' y es un vacio declarado. La logica esta corregida; la memoria no lo imprimira hasta que ese vacio se cierre, y la CLI registra el bloqueo en cada corrida (mismo caso que SIS-B-20).</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3856,11 +3888,19 @@
       <c r="I35" s="6" t="inlineStr"/>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr"/>
-      <c r="L35" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — se retira del criterio el umbral 'Vu &gt; 0.5*phi*Vc' atribuido al Art. 11.10.10.2, que no define ninguno: verificado contra el PDF, ese articulo es una sola frase sin Vu ni phi. El 0.5*phi*Vc existe en el Art. 11.5.6.1 y para elementos en FLEXION. Los umbrales reales (Arts. 11.10.10.1 y 11.10.7/11.10.8) quedan citados. El criterio sigue siendo un vacio declarado, que es su estado correcto: M9 no calcula cortante.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -4924,11 +4964,19 @@
       <c r="I55" s="6" t="inlineStr"/>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K55" s="6" t="inlineStr"/>
-      <c r="L55" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>6768725 + b3e584c — con categoria A el valor sale de RECUBRIMIENTO_MP_MM [N] (Manual de Puentes, Tabla 2.9.1.5.5.3-1) y no de la transcripcion [C] de AASHTO; b3e584c es el que lo hace en el codigo, porque 6768725 solo lo nombraba en la etiqueta. || 8f48bf5 — la auditoria adversarial mostro que el cruce entre las dos transcripciones se saltaba SIN AVISAR en las 8 filas de la familia de pilotes (el Manual traduce 'shafts' por 'Pilares' y parte en dos la fila de ambiente corrosivo), de modo que la red de seguridad cubria 14 filas de 21. Entra RECUBRIMIENTO_MP_EQUIVALENCIA con las 21, con test que lo vigila.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -6122,11 +6170,19 @@
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K76" s="6" t="inlineStr"/>
-      <c r="L76" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — la tabla entra en pulgadas exactas (3.0 in = 76.2 mm; 2.0 in = 50.8 mm) y con el modificador por a/c que el criterio no mencionaba. Conflicto #3 respetado: NO se aplico la correccion obvia de 75 a 76.2 mm; primero se declararon categoria de acero y factor por a/c, y el valor queda determinado despues.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -6656,11 +6712,19 @@
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K85" s="6" t="inlineStr"/>
-      <c r="L85" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — beta se transcribe con sus DOS expresiones y con la condicion del Art. 5.7.3.4.2 que habilita la primera (refuerzo transversal minimo del Art. 5.7.2.5), mas el parametro sxe del que depende la segunda. || 8f48bf5 — la parafrasis decia 'rige la Ec. -2' donde AASHTO escribe 'the value of beta may be as specified in': potestativo, verificado contra el PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -7200,11 +7264,19 @@
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K95" s="6" t="inlineStr"/>
-      <c r="L95" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — las claves pasan de 'Vc_kN' y 'dv_m' a 'Vc_kip', 'dv_in' y 'f_c_prima_ksi', y el criterio declara que la Ec. 5.7.3.3-3 es del sistema kip-ksi-pulgada, con el 0.0316 = 1/raiz(1000) y la C5.1 de AASHTO citada. Se retira la etiqueta SI sobre una formula imperial, que era la contradiccion registrada.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -8174,11 +8246,19 @@
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K112" s="6" t="inlineStr"/>
-      <c r="L112" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — mismo cambio que MAT-X8, mas la condicion de aplicabilidad de beta que faltaba. 'diseno_flexion_corte' sigue deteniendose con NotImplementedError, que es lo que la propia ficha describe: la trampa de unidades era latente y se desactiva en la transcripcion.</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -10658,11 +10738,19 @@
       <c r="I160" s="6" t="inlineStr"/>
       <c r="J160" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K160" s="6" t="inlineStr"/>
-      <c r="L160" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — AMBIENTE_CORROSIVO_TEXTO con el literal integro del Art. 7.7.5.1, incluida la alternativa expresa que la cita omitia ('o debe disponerse de otro tipo de proteccion') y la forma verbal real ('debe aumentarse'). || 8f48bf5 — el aviso EVALUA su propio antecedente: decia 'si el analisis quimico del EMS confirma la exposicion', un condicional cuyo antecedente el programa ya tiene resuelto en el mismo dato del que cuelga el factor por a/c.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -10704,11 +10792,19 @@
       <c r="I161" s="6" t="inlineStr"/>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K161" s="6" t="inlineStr"/>
-      <c r="L161" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — Tabla 4.4 completa: las DOS escalas (sulfato en suelo %, sulfato en agua ppm) con la mas exigente gobernando, los SEIS cementos de exposicion moderada, y el borde que la tabla impresa deja abierto en 2,0 % y 10 000 ppm declarado fila por fila en vez de escondido en un '&gt;=' del codigo.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -10750,11 +10846,19 @@
       <c r="I162" s="6" t="inlineStr"/>
       <c r="J162" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K162" s="6" t="inlineStr"/>
-      <c r="L162" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L162" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — 'requisitos_durabilidad_concreto' cruza las Tablas 4.2 y 4.4 por la nota al pie comun (menor a/c aplicable, mayor f'c minimo), que era el eslabon que faltaba entero, y de esa a/c cuelga el factor del recubrimiento. || 8f48bf5 — cerrado del todo tras la auditoria adversarial, que encontro tres agujeros: solo 1 de las 3 filas de la Tabla 4.2 podia dispararse, de modo que 'la menor a/c APLICABLE' se evaluaba sobre un conjunto incompleto; el Art. 4.4.2 -- que es el que MANDA aplicar la Tabla 4.2 a los cloruros y remite al recubrimiento de 7.7 -- se habia perdido de la cadena de numerales, y la acusacion de cita que lo saco queda retirada por falsa; y CLORUROS_EXTERNOS quedaba muerto con un comentario que afirmaba lo contrario.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -10796,11 +10900,19 @@
       <c r="I163" s="6" t="inlineStr"/>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K163" s="6" t="inlineStr"/>
-      <c r="L163" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — CICLOPEO_FC_MATRIZ_MIN_APLICABLE toma el mayor de los dos minimos que rigen el mismo material: 14 MPa de la Clase G de la Tabla 503-07 del EG-2013 frente a los 10 MPa del Art. 22.10 de E.060. Citar solo el 10 era declarar el requisito mas bajo. || 8f48bf5 — se anade lo que faltaba de la regla de CLAUDE.md sobre la fuente primaria: la discrepancia se declara en el PUNTO DE USO y queda dicho que la Sec. 9.4 de la hoja de ruta SIGUE MAL mientras pida 10 MPa.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -12648,11 +12760,19 @@
       <c r="I199" s="6" t="inlineStr"/>
       <c r="J199" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K199" s="6" t="inlineStr"/>
-      <c r="L199" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S10)</t>
+        </is>
+      </c>
+      <c r="L199" s="6" t="inlineStr">
+        <is>
+          <t>6768725 — la fila de alcantarillas se transcribe entera, con sus tres subfilas y sus condiciones (cajon PREFABRICADO, menos de 2 pies de relleno, que no sea superficie de conduccion), ninguna de las cuales cumple el catalogo circular de Sec. 3.2. Y 2.0 in son 50.8 mm, no 50.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2322,7 +2322,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — cierra la mitad documental y la etiqueta: 'HW_D_max' pasa de [C] a [A] con la cita verificada contra el PDF (num. 2.2.5 d) 'Agency Constraints', pag. impresa 2.10; la v8 citaba la 2.14, que trata de espolones de escombros y seguridad vial), y los DOS docstrings que afirmaban que M5 verifica V4b (M4_control, modelos.ControlEntrada) dejan de afirmarlo. QUEDA ABIERTO el cableado del chequeo, que el conflicto #1 prohibe hacer antes de cerrar la etiqueta y que la tabla maestra asigna a S14.</t>
+          <t>3ed6b22 + 4f32683 — cierra la mitad documental y la etiqueta: 'HW_D_max' pasa de [C] a [A] con la cita verificada contra el PDF (num. 2.2.5 d) 'Agency Constraints', pag. impresa 2.10; la v8 citaba la 2.14, que trata de espolones de escombros y seguridad vial), y los DOS docstrings que afirmaban que M5 verifica V4b (M4_control, modelos.ControlEntrada) dejan de afirmarlo. QUEDA ABIERTO el cableado del chequeo, que el conflicto #1 prohibe hacer antes de cerrar la etiqueta y que la tabla maestra asigna a S14. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de V4b -- lo hace S14, que es la Fase 3 del plan (Plan_Fases F3 = C01 C04 C06 C08 C11, 36 hallazgos; punto 4 del guion de S14 en la hoja de ruta de correcciones v12: 'ahora si, con la etiqueta de V4b cerrada en S6, cablear (o no) HW/D &lt;= 1.5 a verificar()'). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #1 sigue siendo vinculante.</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — mismo paquete que MAT-D2. Los dos docstrings corregidos; la constancia de la fila V4b en M5.verificaciones_no_evaluadas() se actualiza (la procedencia del umbral ya no esta en revision abierta: esta cerrada) y pasa a LEER del criterio su valor, etiqueta y sensibilidad con ca.criterio_efectivo, que no registra uso -- es la unica via por la que 'HW_D_max' llega a la memoria, porque no lo consume nadie. QUEDA ABIERTO que siga sin consumidor, diferido a S14 por el conflicto #1.</t>
+          <t>3ed6b22 + 4f32683 — mismo paquete que MAT-D2. Los dos docstrings corregidos; la constancia de la fila V4b en M5.verificaciones_no_evaluadas() se actualiza (la procedencia del umbral ya no esta en revision abierta: esta cerrada) y pasa a LEER del criterio su valor, etiqueta y sensibilidad con ca.criterio_efectivo, que no registra uso -- es la unica via por la que 'HW_D_max' llega a la memoria, porque no lo consume nadie. QUEDA ABIERTO que siga sin consumidor, diferido a S14 por el conflicto #1. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de V4b -- lo hace S14, que es la Fase 3 del plan (Plan_Fases F3 = C01 C04 C06 C08 C11, 36 hallazgos; punto 4 del guion de S14 en la hoja de ruta de correcciones v12: 'ahora si, con la etiqueta de V4b cerrada en S6, cablear (o no) HW/D &lt;= 1.5 a verificar()'). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #1 sigue siendo vinculante.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 - CIERRA LA MITAD DECLARATIVA, NO EL CABLEADO, y no puede cerrarlo: el conflicto #8 de la seccion 6 del plan es vinculante y prohibe cablear 'clase_sitio' antes de resolver la premisa (S13). Lo que se hizo: dejar escrito en el propio criterio que ningun modulo de produccion lo invoca, que por eso no entra en criterios_usados() ni la memoria imprime la adopcion, y por que cablearlo hoy seria peor -- la memoria declararia formalmente una clasificacion que la fuente no sostiene. QUEDA ABIERTO el cableado, asignado a S14.</t>
+          <t>4f45f15 + e73ab59 - CIERRA LA MITAD DECLARATIVA, NO EL CABLEADO, y no puede cerrarlo: el conflicto #8 de la seccion 6 del plan es vinculante y prohibe cablear 'clase_sitio' antes de resolver la premisa (S13). Lo que se hizo: dejar escrito en el propio criterio que ningun modulo de produccion lo invoca, que por eso no entra en criterios_usados() ni la memoria imprime la adopcion, y por que cablearlo hoy seria peor -- la memoria declararia formalmente una clasificacion que la fuente no sostiene. QUEDA ABIERTO el cableado, asignado a S14. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de 'clase_sitio' -- es Fase 3: el conflicto #8 resuelve 'Resolver primero AAS-02 y VOC-04 (Fase 2), luego el cableado (Fase 3)' y la condicion de salida de F3 en Plan_Fases es, con esas palabras, 'clase_sitio entra en criterios_usados()'. Ojo con el S13 que cita la evidencia de arriba: S13 resuelve la PREMISA, que es NOR-AAS-02 y ya esta en F2; el cableado que esta fila espera lo hace S14, que es F3 (punto 1 del guion de S14 en la hoja de ruta de correcciones v12). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #8 sigue siendo vinculante.</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 - CIERRA LA INCOHERENCIA, NO EL CABLEADO. La tabla ya tiene fila F (con su asterisco y su Nota 2) y 'F_pga' declara sobre que filas se lee y por que la F no esta entre ellas, de modo que las dos defensas dejan de contradecirse. Sigue siendo cierto que solo 'F_pga' llega a la memoria: eso es el cableado de SIS-B-01, prohibido por el conflicto #8 hasta S13/S14.</t>
+          <t>4f45f15 + e73ab59 - CIERRA LA INCOHERENCIA, NO EL CABLEADO. La tabla ya tiene fila F (con su asterisco y su Nota 2) y 'F_pga' declara sobre que filas se lee y por que la F no esta entre ellas, de modo que las dos defensas dejan de contradecirse. Sigue siendo cierto que solo 'F_pga' llega a la memoria: eso es el cableado de SIS-B-01, prohibido por el conflicto #8 hasta S13/S14. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de 'clase_sitio' -- es Fase 3: el conflicto #8 resuelve 'Resolver primero AAS-02 y VOC-04 (Fase 2), luego el cableado (Fase 3)' y la condicion de salida de F3 en Plan_Fases es, con esas palabras, 'clase_sitio entra en criterios_usados()'. Ojo con el S13 que cita la evidencia de arriba: S13 resuelve la PREMISA, que es NOR-AAS-02 y ya esta en F2; el cableado que esta fila espera lo hace S14, que es F3 (punto 1 del guion de S14 en la hoja de ruta de correcciones v12). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #8 sigue siendo vinculante.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -3190,11 +3190,19 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr"/>
-      <c r="L22" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — G_LAUSHEY deja de atribuirsele a 4.1.1.3.7 c) el decimal que ese numeral NO escribe. Verificado sobre el PDF: la definicion de g en 4.1.1.3.7 c) 'Socavacion local a la salida de la alcantarilla' (pag. impresa 80 / PDF 83) es «g : Aceleracion de la gravedad (m/s2)», sin numero, y «9.81» aparece 0 veces en las 225 paginas del Manual. El 9.8 SI lo escribe el Manual, en 3.12.5 (pag. 63) y en 4.1.1.5.4 b.2.4) (pag. 111): el numero se conserva y la cita pasa a esos dos numerales, cada uno como cita del registro (MC_HHD.3.12.5#G, MC_HHD.4.1.1.5.4b24#G) y la falsa queda declarada en MC_HHD.4.1.1.3.7c#G. Corregida ademas la hoja de ruta.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -3240,11 +3248,19 @@
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — 2.1.4.3.9 es «Aparatos de Apoyo» (pag. impresa 91 / PDF 92), verificado. El texto real esta en 2.4.2.2 «Cargas de Suelo: EH, ES, y DD» (pag. impresa 102 / PDF 103), es un PISO («no menor que»), esta condicionado a trafico a distancia &lt;= H/2 y tiene exencion por losa de aproximacion. Las seis apariciones del numeral falso pasan a UNA cita del registro (MP.2.4.2.2#SOBRECARGA); la falsa queda declarada como MP.2.1.4.3.9 para que un test tenga contra que fallar si alguien la reactiva.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -3290,11 +3306,19 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr"/>
-      <c r="L24" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — resuelto como manda el conflicto #4: NO se sube h_eq a 1.12 m sin mas. h_eq = max(piso de 0.60 m del Manual, tabla AASHTO 3.11.6.4 segun altura + orientacion + borde). Verificado contra AASHTO: la -1 es de ESTRIBOS perpendiculares y la -2 de MUROS paralelos -- son binomios acoplados, no dos filas de un eje --, no hay tabla para muro perpendicular (aplicar la -1 a un cabezal es analogia declarada) y el umbral del borde es 1.0 ft = 0.3048 m EXACTO, no 0.30. La orientacion entra como dato de sitio VACIO.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -3506,11 +3530,19 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr"/>
-      <c r="L28" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — el Cuadro 4.1 (pag. impresa 28 / PDF 29) SI condiciona: 2 carriles por sentido -&gt; 4, 3 -&gt; 4, 4 -&gt; 6 calicatas x km x sentido. La cadena «4 (o 6)» no aparece en el Manual. La tabla MS.C41 del registro transcribe las tres columnas por carriles por sentido y `carriles_por_sentido` entra como dato de sitio VACIO que bloquea. Corregida ademas la hoja de ruta.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3560,11 +3592,19 @@
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr"/>
-      <c r="L29" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — mismo hallazgo que NOR-PUE-01, cerrado con la misma correccion.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3620,7 +3660,7 @@
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 - LA PREMISA QUEDA DECLARADA Y DETENIDA, que es lo que el conflicto #8 ordena, no resuelta. La justificacion de 'clase_sitio' deja de afirmar que el sitio es Clase F como cosa cerrada y registra lo verificado: el salto 'licuable -&gt; Clase F' no lo escribe ninguno de los dos documentos que el criterio invoca (AASHTO trata la licuefaccion en su Art. 10.5.4.2, por via distinta de la clase de sitio) y quien clasifica los licuables aparte es E.030 en su S5. La discrepancia entre los dos esquemas queda transcrita en `E030_S5_VS_CLASE_F`. RESOLVERLA es S13.</t>
+          <t>4f45f15 + e73ab59 - LA PREMISA QUEDA DECLARADA Y DETENIDA, que es lo que el conflicto #8 ordena, no resuelta. La justificacion de 'clase_sitio' deja de afirmar que el sitio es Clase F como cosa cerrada y registra lo verificado: el salto 'licuable -&gt; Clase F' no lo escribe ninguno de los dos documentos que el criterio invoca (AASHTO trata la licuefaccion en su Art. 10.5.4.2, por via distinta de la clase de sitio) y quien clasifica los licuables aparte es E.030 en su S5. La discrepancia entre los dos esquemas queda transcrita en `E030_S5_VS_CLASE_F`. RESOLVERLA es S13. || REVISADO EN S12: el diferimiento sigue vigente. Lo que queda abierto es resolver el esquema E.030 S5 vs Clase F de AASHTO, que el conflicto #8 asigna a S13; S12 trabajo sobre citas y tablas y no toco la cadena sismica. La premisa sigue declarada y detenida.</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3884,7 @@
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>6768725 — ESPESOR_DOS_CAPAS_REFUERZO = 0.200 m (Art. 14.3.2) y M9.requiere_refuerzo_dos_capas: entre 200 y 250 mm el muro lleva dos capas aunque el acero por temperatura vaya en una cara, que es lo contrario de lo que la memoria imprimia. CIERRA EN PARTE, y se deja dicho: la nota que lo declara sigue sin llamador de produccion porque su insumo es el espesor, que sale de 'predimensionamiento_cabezal' y es un vacio declarado. La logica esta corregida; la memoria no lo imprimira hasta que ese vacio se cierre, y la CLI registra el bloqueo en cada corrida (mismo caso que SIS-B-20).</t>
+          <t>6768725 — ESPESOR_DOS_CAPAS_REFUERZO = 0.200 m (Art. 14.3.2) y M9.requiere_refuerzo_dos_capas: entre 200 y 250 mm el muro lleva dos capas aunque el acero por temperatura vaya en una cara, que es lo contrario de lo que la memoria imprimia. CIERRA EN PARTE, y se deja dicho: la nota que lo declara sigue sin llamador de produccion porque su insumo es el espesor, que sale de 'predimensionamiento_cabezal' y es un vacio declarado. La logica esta corregida; la memoria no lo imprimira hasta que ese vacio se cierre, y la CLI registra el bloqueo en cada corrida (mismo caso que SIS-B-20). || REVISADO EN S12: el diferimiento sigue vigente. Su insumo es el espesor, que sale de 'predimensionamiento_cabezal', y ese vacio declarado sigue vacio: S12 no lo toco. La logica sigue corregida y la memoria sigue sin poder imprimirlo.</t>
         </is>
       </c>
     </row>
@@ -3946,11 +3986,19 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — 508.07 esta en la pag. impresa 984 (PDF 992), no en la 982. Verificado por encabezado impreso y por busqueda. La pagina sale ahora de la cita del registro (EG2013.508.07), no de una cadena escrita a mano, de modo que la memoria imprime lo verificado.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3992,11 +4040,19 @@
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — la cita literal del 508.07 vive donde el registro dice: cita EG2013.508.07 con texto verbatim, pagina impresa y pagina PDF, y el test T2 la vuelve a buscar en el PDF en cada corrida. El manifiesto ya no la localiza por linea sino por simbolo.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -4038,11 +4094,19 @@
       <c r="I38" s="6" t="inlineStr"/>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — los cuatro rangos de CAMA_RELLENO_LATERAL corregidos contra el PDF: 505 -&gt; 950-953, 506 -&gt; 959-961, 507 -&gt; 973-974 (el TMC estaba corrido tres paginas), 508 -&gt; 982-985. Ademas se declara, por fila, que el «95 % MDS» de tres de las cuatro fichas NO es literal de la subseccion citada sino remision al 205.12(c)(1) (campo procedencia_de_los_porcentajes en modelos.CamaApoyoRelleno).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4210,7 +4274,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — h_o deja de ser una formula 'sin numeral' y sin limite: num. 3.3.3 'Outlet Control', pag. impresa 3.24, con sus TRES condiciones transcritas verbatim y cada una atribuida a su sitio de la pagina (H_O_NUMERAL, H_O_CONDICION_TEXTO, H_O_FORMA_MAXIMO_TEXTO, H_O_CONDICION_APLICACION). DOS de las tres SE EVALUAN punto por punto: los limites HW/D &lt; 0.75 ('should not be used') y HW/D &lt; 1.2 ('caution'), como constantes [N] H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculados en control_salida(), filtrados por si el control de salida gobierna -- que es como la fuente los escribe -- e impresos EN LA MEMORIA DEL PUNTO junto a su HW. Es lo que la auditoria adversarial refuto de la primera version, que los declaraba sin evaluarlos pudiendo: el punto A-02 del CSV de ejemplo da HW/D=0.675 con el control de salida gobernando, y la memoria no lo decia. La condicion llega ademas siempre por UMBRALES_DE_VERIFICACION, tambien en la corrida bloqueada. QUEDA ABIERTO lo unico que no se puede evaluar sin un perfil de la lamina de agua: que el barril fluya lleno en la mayor parte de su longitud. Lo cerraria el procedimiento de barril parcialmente lleno del Cap. III.</t>
+          <t>3ed6b22 + 4f32683 — h_o deja de ser una formula 'sin numeral' y sin limite: num. 3.3.3 'Outlet Control', pag. impresa 3.24, con sus TRES condiciones transcritas verbatim y cada una atribuida a su sitio de la pagina (H_O_NUMERAL, H_O_CONDICION_TEXTO, H_O_FORMA_MAXIMO_TEXTO, H_O_CONDICION_APLICACION). DOS de las tres SE EVALUAN punto por punto: los limites HW/D &lt; 0.75 ('should not be used') y HW/D &lt; 1.2 ('caution'), como constantes [N] H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculados en control_salida(), filtrados por si el control de salida gobierna -- que es como la fuente los escribe -- e impresos EN LA MEMORIA DEL PUNTO junto a su HW. Es lo que la auditoria adversarial refuto de la primera version, que los declaraba sin evaluarlos pudiendo: el punto A-02 del CSV de ejemplo da HW/D=0.675 con el control de salida gobernando, y la memoria no lo decia. La condicion llega ademas siempre por UMBRALES_DE_VERIFICACION, tambien en la corrida bloqueada. QUEDA ABIERTO lo unico que no se puede evaluar sin un perfil de la lamina de agua: que el barril fluya lleno en la mayor parte de su longitud. Lo cerraria el procedimiento de barril parcialmente lleno del Cap. III. || REVISADO EN S12: el diferimiento sigue vigente. Lo abierto es la tercera condicion -- que el barril fluya lleno en la mayor parte de su longitud --, que no se puede evaluar sin el perfil de lamina de agua del Cap. III de HDS-5. S12 no implemento ese procedimiento.</t>
         </is>
       </c>
     </row>
@@ -4254,11 +4318,19 @@
       <c r="I42" s="6" t="inlineStr"/>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="inlineStr"/>
-      <c r="L42" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — LONG_MAX_CUNETA: pagina impresa 179 (no la que se citaba) y CARACTER POR VALOR, porque las dos cifras no tienen la misma fuerza normativa. Las dos cosas verificadas sobre el PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -4582,11 +4654,19 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K48" s="6" t="inlineStr"/>
-      <c r="L48" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — la cura no es repasar las 296 referencias sino quitarles la linea: src/normativa/manifiesto.py las reescribe desde el NOMBRE DE SIMBOLO (`resincronizar`) y genera el indice del registro entero desde los objetos (`indice_del_registro`). Dos tests nuevos (T8) fallan si el manifiesto o el indice quedan desfasados, y el cupo de referencias de prosa es un trinquete que solo decrece (T9, hoy 82).</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5018,11 +5098,19 @@
       <c r="I56" s="6" t="inlineStr"/>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K56" s="6" t="inlineStr"/>
-      <c r="L56" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — los 4.0 km no estan en el Cuadro sino en un parrafo del num. 4.2 (pag. impresa 29) y son doblemente condicionales. Declarado en ESPACIAMIENTO_PERFIL_KM con su cita.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -5064,11 +5152,19 @@
       <c r="I57" s="6" t="inlineStr"/>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="inlineStr"/>
-      <c r="L57" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — de los cuatro numerales citados solo el 3.2.1 sostiene los dos valores de compactacion; el 9.1(1) no contiene ningun porcentaje. Verificado y corregido en el registro.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -5180,11 +5276,19 @@
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K59" s="6" t="inlineStr"/>
-      <c r="L59" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — cerrado con NOR-PUE-02. El matiz del verificador (muro paralelo con borde &gt;= 1.0 ft da 0.61 m, no 1.12 m) es justamente lo que hace que el dato que faltaba sea la ORIENTACION y no el valor.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -5234,11 +5338,19 @@
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K60" s="6" t="inlineStr"/>
-      <c r="L60" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — la contradiccion se resuelve sin elegir bando: el 0.60 del Manual es un PISO y la tabla de AASHTO da el valor; max(piso, tabla) honra a las dos. Verificado sobre los dos PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -5412,11 +5524,19 @@
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K63" s="6" t="inlineStr"/>
-      <c r="L63" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — mismo hallazgo que NOR-SUE-01, cerrado con la misma correccion; el codigo deja de contradecir a la hoja y a la fuente.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5992,11 +6112,19 @@
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K73" s="6" t="inlineStr"/>
-      <c r="L73" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L73" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — mismo hallazgo que NOR-HID-01, cerrado con la misma correccion: numero conservado, atribucion corregida, hoja de ruta corregida y la cita falsa declarada en el registro.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6538,11 +6666,19 @@
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr"/>
-      <c r="L82" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — las cuatro paginas corridas verificadas y corregidas: V2 76-&gt;77, ke C.2-&gt;C.6, HW/D 2.14-&gt;2.10, EG-2013 982-&gt;984 y 970-&gt;973-974. Todas salen ahora de citas del registro con pagina impresa Y pagina PDF, y T2/T3 las revalidan contra el PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -10392,11 +10528,19 @@
       <c r="I153" s="6" t="inlineStr"/>
       <c r="J153" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K153" s="6" t="inlineStr"/>
-      <c r="L153" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L153" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] la luz maxima de alcantarilla esta en la pag. impresa 87, no en la 88. Verificado y corregido en LUZ_MAX_ALCANTARILLA via cita del registro.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -10438,11 +10582,19 @@
       <c r="I154" s="6" t="inlineStr"/>
       <c r="J154" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K154" s="6" t="inlineStr"/>
-      <c r="L154" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L154" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] verificado sobre el PDF de AASHTO: las paginas que el codigo vigente cita YA son las correctas (Table 3.4.1-1 en 3-17). El hallazgo se cierra por verificacion, sin correccion: lo que estaba mal era la ficha.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -10646,11 +10798,19 @@
       <c r="I158" s="6" t="inlineStr"/>
       <c r="J158" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K158" s="6" t="inlineStr"/>
-      <c r="L158" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L158" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C12/F5, de paso] E.050 no dice «sismico» en tres de las cinco filas: FS_NOMBRE_DE_LA_CONDICION transcribe la palabra de la fuente en cada una (viento incluido en el Art. 21.2, «Condicion Pseudo - dinamico» en 39.13.6) y FS_MUROS_ESTADO_LIMITE recoge la coletilla que el repositorio no traia.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -10692,11 +10852,19 @@
       <c r="I159" s="6" t="inlineStr"/>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K159" s="6" t="inlineStr"/>
-      <c r="L159" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L159" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C12/F5, de paso] el espaciamiento del SPT tiene numeral: la marca «sin numeral» se retira y el alcance queda corregido.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -11008,11 +11176,19 @@
       <c r="I165" s="6" t="inlineStr"/>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K165" s="6" t="inlineStr"/>
-      <c r="L165" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L165" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] el «Cap. IV» de la 3a ed. de HDS-5 es «CULVERT DESIGN FOR AQUATIC ORGANISM PASSAGE». La zona de transicion esta en el num. 3.1.3 y en el Apendice A.2; corregida la fuente del criterio.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -11162,11 +11338,19 @@
       <c r="I168" s="6" t="inlineStr"/>
       <c r="J168" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K168" s="6" t="inlineStr"/>
-      <c r="L168" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K168" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L168" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] el 0.25 m/s se imprime en la pag. 77; la 76 es donde arranca el parrafo. La cita del registro (MC_HHD.4.1.1.3.6#VMIN) lleva la 77 y el comentario lo dice.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -11354,11 +11538,19 @@
       <c r="I172" s="6" t="inlineStr"/>
       <c r="J172" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K172" s="6" t="inlineStr"/>
-      <c r="L172" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K172" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L172" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C12/F5, de paso] el Cuadro 4.1 SI fija la profundidad (1.50 m): es columna propia de la tabla MS.C41 y llega a CALICATAS_PROFUNDIDAD_M.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -11400,11 +11592,19 @@
       <c r="I173" s="6" t="inlineStr"/>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K173" s="6" t="inlineStr"/>
-      <c r="L173" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K173" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C12/F5, de paso] «resguardo» aparece una sola vez en las 281 paginas del Manual y en otro sentido; la fuente ofrece remedios alternativos. Declarado.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -11616,11 +11816,19 @@
       <c r="I177" s="6" t="inlineStr"/>
       <c r="J177" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K177" s="6" t="inlineStr"/>
-      <c r="L177" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S12)</t>
+        </is>
+      </c>
+      <c r="L177" s="6" t="inlineStr">
+        <is>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2769,12 +2769,12 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S9)</t>
+          <t>Claude Code (fase1, S9 + S13)</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 - CIERRA LA MITAD DECLARATIVA, NO EL CABLEADO, y no puede cerrarlo: el conflicto #8 de la seccion 6 del plan es vinculante y prohibe cablear 'clase_sitio' antes de resolver la premisa (S13). Lo que se hizo: dejar escrito en el propio criterio que ningun modulo de produccion lo invoca, que por eso no entra en criterios_usados() ni la memoria imprime la adopcion, y por que cablearlo hoy seria peor -- la memoria declararia formalmente una clasificacion que la fuente no sostiene. QUEDA ABIERTO el cableado, asignado a S14. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de 'clase_sitio' -- es Fase 3: el conflicto #8 resuelve 'Resolver primero AAS-02 y VOC-04 (Fase 2), luego el cableado (Fase 3)' y la condicion de salida de F3 en Plan_Fases es, con esas palabras, 'clase_sitio entra en criterios_usados()'. Ojo con el S13 que cita la evidencia de arriba: S13 resuelve la PREMISA, que es NOR-AAS-02 y ya esta en F2; el cableado que esta fila espera lo hace S14, que es F3 (punto 1 del guion de S14 en la hoja de ruta de correcciones v12). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #8 sigue siendo vinculante.</t>
+          <t>4f45f15 + e73ab59 + 1f54f4f — SOLUCION DEFINIDA EN S13, APLICACION EN S14. La premisa que lo bloqueaba esta resuelta (NOR-AAS-02) y la salida NO es la que el cluster C04 suponia: no se cierra cableando una invocacion a criterios_usados(), sino RETIRANDO EL VALOR. Con valor=None el criterio entra en la memoria por criterios_sin_valor(), que es la puerta de M11 que le corresponde a un vacio declarado, sin invocacion y sin detener el calculo. Invocarlo desde cadena_sismica() pararia el dimensionamiento entero del cabezal sin que ninguna norma lo exija: la cadena consume 'F_pga', no 'clase_sitio'. El defecto era el valor, no la falta de cableado. Texto exacto de memoria en docs/resolucion_clase_sitio.md seccion 4</t>
         </is>
       </c>
     </row>
@@ -2831,12 +2831,12 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S9)</t>
+          <t>Claude Code (fase1, S9 + S13)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 - CIERRA LA INCOHERENCIA, NO EL CABLEADO. La tabla ya tiene fila F (con su asterisco y su Nota 2) y 'F_pga' declara sobre que filas se lee y por que la F no esta entre ellas, de modo que las dos defensas dejan de contradecirse. Sigue siendo cierto que solo 'F_pga' llega a la memoria: eso es el cableado de SIS-B-01, prohibido por el conflicto #8 hasta S13/S14. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de 'clase_sitio' -- es Fase 3: el conflicto #8 resuelve 'Resolver primero AAS-02 y VOC-04 (Fase 2), luego el cableado (Fase 3)' y la condicion de salida de F3 en Plan_Fases es, con esas palabras, 'clase_sitio entra en criterios_usados()'. Ojo con el S13 que cita la evidencia de arriba: S13 resuelve la PREMISA, que es NOR-AAS-02 y ya esta en F2; el cableado que esta fila espera lo hace S14, que es F3 (punto 1 del guion de S14 en la hoja de ruta de correcciones v12). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #8 sigue siendo vinculante.</t>
+          <t>4f45f15 + e73ab59 + 1f54f4f — CIERRA LA INCOHERENCIA, NO EL CABLEADO. La tabla ya tiene fila F (con su asterisco y su Nota 2) y 'F_pga' declara sobre que filas se lee y por que la F no esta entre ellas. S13 le quita la causa: con la premisa retirada, 'clase_sitio' deja de reclamar una clase que 'F_pga' no lee, y la razon de excluir la fila F pasa a ser de fuente -- no da factor, y suponerla esta vedado -- y no de omision. Falta escribir en el archivo la justificacion de la seccion 4.2 de docs/resolucion_clase_sitio.md. || FASE REASIGNADA F3 (S14)</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr"/>
@@ -3655,12 +3655,12 @@
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S9)</t>
+          <t>Claude Code (fase1, S9 + S13)</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 - LA PREMISA QUEDA DECLARADA Y DETENIDA, que es lo que el conflicto #8 ordena, no resuelta. La justificacion de 'clase_sitio' deja de afirmar que el sitio es Clase F como cosa cerrada y registra lo verificado: el salto 'licuable -&gt; Clase F' no lo escribe ninguno de los dos documentos que el criterio invoca (AASHTO trata la licuefaccion en su Art. 10.5.4.2, por via distinta de la clase de sitio) y quien clasifica los licuables aparte es E.030 en su S5. La discrepancia entre los dos esquemas queda transcrita en `E030_S5_VS_CLASE_F`. RESOLVERLA es S13. || REVISADO EN S12: el diferimiento sigue vigente. Lo que queda abierto es resolver el esquema E.030 S5 vs Clase F de AASHTO, que el conflicto #8 asigna a S13; S12 trabajo sobre citas y tablas y no toco la cadena sismica. La premisa sigue declarada y detenida.</t>
+          <t>4f45f15 + e73ab59 + 1f54f4f — LA PREMISA QUEDA RESUELTA (S13, conflicto #8); SIGUE PARCIAL PORQUE EL VALOR NO SE HA RETIRADO. Verificado contra las dos fuentes primarias por tres subagentes independientes: el salto 'licuable -&gt; Clase F' no lo escribe ninguno de los dos documentos (en las 1905 pag. de AASHTO los conjuntos de paginas con 'liquef' y con 'Site Class F' son DISJUNTOS; en las 673 del Manual la licuefaccion vive en cimentaciones y el Apendice A11, nunca en el numeral de clases de sitio). Y el argumento deja de ser por silencio -- que es lo que R95-073 habia acotado con razon -- por dos vias nuevas: (a) las dos fuentes PROHIBEN suponer la clase E o F sin dato geotecnico ni determinacion de la autoridad (AASHTO Art. 3.10.3.1 al pie de la Tabla 3.10.3.1-1, pag. impresa 3-102, articulado; Manual num. 2.4.3.11.2.1.1, pag. impresa 122, que lo endurece a 'no seran supuestas'), y este expediente no tiene ninguna de las dos; (b) el Art. 10.5.4.2 espera factor de sitio TABULADO para un sitio licuable, incompatible con que la licuefaccion lo hiciera Clase F. DECISION: 'clase_sitio' pasa a [S] sin valor. Fundamento, cinco respuestas con cita de pagina y texto exacto de memoria en docs/resolucion_clase_sitio.md. 12 citas nuevas en src/normativa/citas.py (registro 78 -&gt; 90) y 4 Discrepancia en discrepancias.py. LO QUE FALTA: retirar el valor 'F_con_factores_tabulados_por_adopcion' de criterios_adoptados.py, que es cableado y el conflicto #8 lo reserva a S14. Mientras siga ahi, el repositorio contiene la premisa. || FASE REASIGNADA F2 -&gt; F3 (S14), que es donde se aplica</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2232,7 +2232,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — el vacio no era un vacio. Se transcribe la Tabla 12.6.6.3-1 de AASHTO LRFD (Art. 12.6.6.3, pag. 12-22) en el criterio 'cobertura_minima_aashto' [C] y h_rec pasa a calcularse como el mayor entre el minimo de EG-2013 (solo HDPE) y esa cobertura. Se RETIRA 'h_relleno_min_concreto_tmc'. Que fila aplica lo decide 'condicion_pavimento' [A], sin valor, que bloquea; el Bc del concreto necesita 'espesor_pared_conducto' [A], sin valor, que tambien bloquea. || dbaa501 — la transcripcion de la Tabla 12.6.6.3-1 se rehizo sobre la celda RENDERIZADA tras la auditoria adversarial: la fila del concreto dice "Bc/8 or B'c/8, whichever is greater, &gt;= 12.0 in.", no "sqrt(Bc)/8" como transcribe la propia ficha NOR-VAC-01 (la prima de B'c es un glifo de SymbolMT que la extraccion de texto rompe). B'c es la "out-to-out vertical rise of pipe", que en conducto circular es Bc, de modo que el maximo se reduce a Bc/8. Cae con la lectura falsa la rama sqrt y el factor pie-metro que se habian introducido. NOTA CONTRA LA FICHA: su transcripcion del segundo termino es erronea.</t>
+          <t>3d59da0 — el vacio no era un vacio. Se transcribe la Tabla 12.6.6.3-1 de AASHTO LRFD (Art. 12.6.6.3, pag. 12-22) en el criterio 'cobertura_minima_aashto' [C] y h_rec pasa a calcularse como el mayor entre el minimo de EG-2013 (solo HDPE) y esa cobertura. Se RETIRA 'h_relleno_min_concreto_tmc'. Que fila aplica lo decide 'condicion_pavimento' [A], sin valor, que bloquea; el Bc del concreto necesita 'espesor_pared_conducto' [A], sin valor, que tambien bloquea. || dbaa501 — la transcripcion de la Tabla 12.6.6.3-1 se rehizo sobre la celda RENDERIZADA tras la auditoria adversarial: la fila del concreto dice "Bc/8 or B'c/8, whichever is greater, &gt;= 12.0 in.", no "sqrt(Bc)/8" como transcribe la propia ficha NOR-VAC-01 (la prima de B'c es un glifo de SymbolMT que la extraccion de texto rompe). B'c es la "out-to-out vertical rise of pipe", que en conducto circular es Bc, de modo que el maximo se reduce a Bc/8. Cae con la lectura falsa la rama sqrt y el factor pie-metro que se habian introducido. NOTA CONTRA LA FICHA: su transcripcion del segundo termino es erronea. || S14 — RECONTRASTADO, sin cambio. El vacio esta cerrado: la Tabla 12.6.6.3-1 esta transcrita en 'cobertura_minima_aashto' y h_rec es el mayor entre el minimo del EG-2013 y esa cobertura, con la fila decidida por 'condicion_pavimento'. Sigue Cerrado.</t>
         </is>
       </c>
     </row>
@@ -2342,17 +2342,17 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S6)</t>
+          <t>Claude Code (fase1, S14)</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — cierra la mitad documental y la etiqueta: 'HW_D_max' pasa de [C] a [A] con la cita verificada contra el PDF (num. 2.2.5 d) 'Agency Constraints', pag. impresa 2.10; la v8 citaba la 2.14, que trata de espolones de escombros y seguridad vial), y los DOS docstrings que afirmaban que M5 verifica V4b (M4_control, modelos.ControlEntrada) dejan de afirmarlo. QUEDA ABIERTO el cableado del chequeo, que el conflicto #1 prohibe hacer antes de cerrar la etiqueta y que la tabla maestra asigna a S14. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de V4b -- lo hace S14, que es la Fase 3 del plan (Plan_Fases F3 = C01 C04 C06 C08 C11, 36 hallazgos; punto 4 del guion de S14 en la hoja de ruta de correcciones v12: 'ahora si, con la etiqueta de V4b cerrada en S6, cablear (o no) HW/D &lt;= 1.5 a verificar()'). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #1 sigue siendo vinculante.</t>
+          <t>3ed6b22 + 4f32683 — cierra la mitad documental y la etiqueta: 'HW_D_max' pasa de [C] a [A] con la cita verificada contra el PDF (num. 2.2.5 d) 'Agency Constraints', pag. impresa 2.10; la v8 citaba la 2.14, que trata de espolones de escombros y seguridad vial), y los DOS docstrings que afirmaban que M5 verifica V4b (M4_control, modelos.ControlEntrada) dejan de afirmarlo. QUEDA ABIERTO el cableado del chequeo, que el conflicto #1 prohibe hacer antes de cerrar la etiqueta y que la tabla maestra asigna a S14. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de V4b -- lo hace S14, que es la Fase 3 del plan (Plan_Fases F3 = C01 C04 C06 C08 C11, 36 hallazgos; punto 4 del guion de S14 en la hoja de ruta de correcciones v12: 'ahora si, con la etiqueta de V4b cerrada en S6, cablear (o no) HW/D &lt;= 1.5 a verificar()'). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #1 sigue siendo vinculante. || S14 — V4b CABLEADA: `M5.v4b_relacion_hw_d`, en `M5.verificar()` y en el verificador de perfil de cli.py, como obligatoria. Se hizo AHORA y no antes porque el conflicto #1 lo prohibia mientras la etiqueta siguiera abierta, y quedo cerrada en S6. El HW que se divide entre D es el del control GOBERNANTE (`ResultadoHidraulico.HW`) y no el HWi/D del control de entrada: lo que la fuente acota es «the headwater produced by a culvert», y tomar el de entrada cuando gobierna el de salida daria un numero menor que el embalse real. El numeral de la fila declara que NO es exigencia sino adopcion.</t>
         </is>
       </c>
     </row>
@@ -2644,17 +2644,17 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S6)</t>
+          <t>Claude Code (fase1, S14)</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — mismo paquete que MAT-D2. Los dos docstrings corregidos; la constancia de la fila V4b en M5.verificaciones_no_evaluadas() se actualiza (la procedencia del umbral ya no esta en revision abierta: esta cerrada) y pasa a LEER del criterio su valor, etiqueta y sensibilidad con ca.criterio_efectivo, que no registra uso -- es la unica via por la que 'HW_D_max' llega a la memoria, porque no lo consume nadie. QUEDA ABIERTO que siga sin consumidor, diferido a S14 por el conflicto #1. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de V4b -- lo hace S14, que es la Fase 3 del plan (Plan_Fases F3 = C01 C04 C06 C08 C11, 36 hallazgos; punto 4 del guion de S14 en la hoja de ruta de correcciones v12: 'ahora si, con la etiqueta de V4b cerrada en S6, cablear (o no) HW/D &lt;= 1.5 a verificar()'). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #1 sigue siendo vinculante.</t>
+          <t>3ed6b22 + 4f32683 — mismo paquete que MAT-D2. Los dos docstrings corregidos; la constancia de la fila V4b en M5.verificaciones_no_evaluadas() se actualiza (la procedencia del umbral ya no esta en revision abierta: esta cerrada) y pasa a LEER del criterio su valor, etiqueta y sensibilidad con ca.criterio_efectivo, que no registra uso -- es la unica via por la que 'HW_D_max' llega a la memoria, porque no lo consume nadie. QUEDA ABIERTO que siga sin consumidor, diferido a S14 por el conflicto #1. || FASE REASIGNADA F1 -&gt; F3 (mantenimiento del tracker): la fila quedaba huerfana. La Fase 1 se consumio en S2-S10, asi que ninguna sesion futura la levanta filtrando por fase, mientras que lo unico que sigue abierto aqui -- el cableado de V4b -- lo hace S14, que es la Fase 3 del plan (Plan_Fases F3 = C01 C04 C06 C08 C11, 36 hallazgos; punto 4 del guion de S14 en la hoja de ruta de correcciones v12: 'ahora si, con la etiqueta de V4b cerrada en S6, cablear (o no) HW/D &lt;= 1.5 a verificar()'). Solo cambia la fase de destino: el Estado sigue siendo 'Cerrado parcial', la evidencia de arriba no se toca y el conflicto #1 sigue siendo vinculante. || S14 — Mismo paquete que MAT-D2. 'HW_D_max' ya tiene consumidor de produccion y llega a la memoria por la via normal, `criterios_usados()`, con su valor, etiqueta y rango -- comprobado sobre la memoria generada. La constancia de «V4b NO evaluada» se retiro de `verificaciones_no_evaluadas()`, que ahora devuelve solo la de V2b, y los conteos se actualizaron en los cinco sitios que los repetian (docstring del modulo, M11, cli.py y los dos tests): once filas de Fase 5, DIEZ funciones.</t>
         </is>
       </c>
     </row>
@@ -2764,17 +2764,17 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S9 + S13)</t>
+          <t>Claude Code (fase1, S14)</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 + 1f54f4f — SOLUCION DEFINIDA EN S13, APLICACION EN S14. La premisa que lo bloqueaba esta resuelta (NOR-AAS-02) y la salida NO es la que el cluster C04 suponia: no se cierra cableando una invocacion a criterios_usados(), sino RETIRANDO EL VALOR. Con valor=None el criterio entra en la memoria por criterios_sin_valor(), que es la puerta de M11 que le corresponde a un vacio declarado, sin invocacion y sin detener el calculo. Invocarlo desde cadena_sismica() pararia el dimensionamiento entero del cabezal sin que ninguna norma lo exija: la cadena consume 'F_pga', no 'clase_sitio'. El defecto era el valor, no la falta de cableado. Texto exacto de memoria en docs/resolucion_clase_sitio.md seccion 4</t>
+          <t>4f45f15 + e73ab59 + 1f54f4f — SOLUCION DEFINIDA EN S13, APLICACION EN S14. La premisa que lo bloqueaba esta resuelta (NOR-AAS-02) y la salida NO es la que el cluster C04 suponia: no se cierra cableando una invocacion a criterios_usados(), sino RETIRANDO EL VALOR. Con valor=None el criterio entra en la memoria por criterios_sin_valor(), que es la puerta de M11 que le corresponde a un vacio declarado, sin invocacion y sin detener el calculo. Invocarlo desde cadena_sismica() pararia el dimensionamiento entero del cabezal sin que ninguna norma lo exija: la cadena consume 'F_pga', no 'clase_sitio'. El defecto era el valor, no la falta de cableado. Texto exacto de memoria en docs/resolucion_clase_sitio.md seccion 4 || S14 — Cerrado POR LA VIA QUE S13 definio y no por cableado: con valor=None el criterio entra en la memoria por `criterios_sin_valor()`, comprobado sobre la memoria generada. NO se anadio ninguna invocacion en produccion -- hacerlo detendria el dimensionamiento entero del cabezal sin que ninguna norma lo exija, porque la cadena sismica consume 'F_pga' y no la clase --, y esa decision esta escrita en el campo `sin_consumidor` del propio criterio, que es donde el proyecto escribe una vez las razones de este tipo. Se retiro tambien el `valor('clase_sitio')` del bloque __main__, que era la unica invocacion que quedaba y que ahora lanzaria CriterioPendienteError.</t>
         </is>
       </c>
     </row>
@@ -2826,17 +2826,17 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S9 + S13)</t>
+          <t>Claude Code (fase1, S14)</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 + 1f54f4f — CIERRA LA INCOHERENCIA, NO EL CABLEADO. La tabla ya tiene fila F (con su asterisco y su Nota 2) y 'F_pga' declara sobre que filas se lee y por que la F no esta entre ellas. S13 le quita la causa: con la premisa retirada, 'clase_sitio' deja de reclamar una clase que 'F_pga' no lee, y la razon de excluir la fila F pasa a ser de fuente -- no da factor, y suponerla esta vedado -- y no de omision. Falta escribir en el archivo la justificacion de la seccion 4.2 de docs/resolucion_clase_sitio.md. || FASE REASIGNADA F3 (S14)</t>
+          <t>4f45f15 + e73ab59 + 1f54f4f — CIERRA LA INCOHERENCIA, NO EL CABLEADO. La tabla ya tiene fila F (con su asterisco y su Nota 2) y 'F_pga' declara sobre que filas se lee y por que la F no esta entre ellas. S13 le quita la causa: con la premisa retirada, 'clase_sitio' deja de reclamar una clase que 'F_pga' no lee, y la razon de excluir la fila F pasa a ser de fuente -- no da factor, y suponerla esta vedado -- y no de omision. Falta escribir en el archivo la justificacion de la seccion 4.2 de docs/resolucion_clase_sitio.md. || FASE REASIGNADA F3 (S14) || S14 — La justificacion de 'F_pga' se reescribio con el texto de la seccion 4.2 del documento de resolucion. El VALOR ('C','D','E') y la etiqueta [A] no cambian. Lo que cambia es el argumento: la fila F queda fuera por dos razones de fuente -- no da factor (asterisco en las cinco columnas, Nota 2) y suponerla esta vedado -- y NO porque se haya descartado que el sitio sea Clase F. Se corrigio ademas su `reemplazado_por`: la profundidad pasa a «100 ft (30.48 m)» y el analisis de respuesta de sitio se reancla en el ARTICULADO (Art. 3.10.2 «shall», num. 2.4.3.11.2 «sera usado») en vez de en la Nota 2 al pie de la tabla de factores, que lo repite y no lo funda.</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>9ec09d6 + 65dbebe — el vacio se retira porque no existia. Verificado leyendo el PDF del Manual de Puentes por el encabezado impreso de cada pagina, no por aritmetica de desfase: las Tablas 2.4.5.3.1-1 'Combinaciones de Carga y Factores de Carga' y 2.4.5.3.1-2 'Factores de carga para cargas permanentes, gamma_p' estan las DOS en la pagina impresa 143, completas y con sus valores, dentro del rango de paginas que el propio repositorio citaba al declarar el vacio. Las dos estan hoy transcritas como [N] en constantes_normativas y la afirmacion negativa se retira de los cinco sitios donde vivia: el comentario de COMBINACIONES_AASHTO, la justificacion del criterio, el docstring de modelos.CombinacionCarga, el de M9.combinaciones y la fila del manifiesto (Sec. 3, Sec. 8 y Sec. 12). Corregidas ademas tres paginas mal citadas por el criterio: la Tabla 3.4.1-1 no esta en la 3-14 de AASHTO sino en la 3-17, y las dos del Manual no estan en '143 y 146' sino las dos en la 143 (la 146 es una lamina fotografica). Como el vacio no existia, el [C] tampoco se sostiene: los numeros son [N] via MTC y lo unico [A] es la eleccion de fila</t>
+          <t>9ec09d6 + 65dbebe — el vacio se retira porque no existia. Verificado leyendo el PDF del Manual de Puentes por el encabezado impreso de cada pagina, no por aritmetica de desfase: las Tablas 2.4.5.3.1-1 'Combinaciones de Carga y Factores de Carga' y 2.4.5.3.1-2 'Factores de carga para cargas permanentes, gamma_p' estan las DOS en la pagina impresa 143, completas y con sus valores, dentro del rango de paginas que el propio repositorio citaba al declarar el vacio. Las dos estan hoy transcritas como [N] en constantes_normativas y la afirmacion negativa se retira de los cinco sitios donde vivia: el comentario de COMBINACIONES_AASHTO, la justificacion del criterio, el docstring de modelos.CombinacionCarga, el de M9.combinaciones y la fila del manifiesto (Sec. 3, Sec. 8 y Sec. 12). Corregidas ademas tres paginas mal citadas por el criterio: la Tabla 3.4.1-1 no esta en la 3-14 de AASHTO sino en la 3-17, y las dos del Manual no estan en '143 y 146' sino las dos en la 143 (la 146 es una lamina fotografica). Como el vacio no existia, el [C] tampoco se sostiene: los numeros son [N] via MTC y lo unico [A] es la eleccion de fila || S14 — RECONTRASTADO, sin cambio. El guion de la sesion lo listaba como vacio a retirar; ya no existe tal vacio: 'factores_carga_aashto' declara QUE FILA de gamma_p cuelga cada estructura y las dos tablas de la pag. impresa 143 estan transcritas como [N]. No queda ninguna afirmacion negativa sobre esas paginas. Sigue Cerrado.</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe</t>
+          <t>3ea627c + 7266bfe || S14 — RECONTRASTADO, sin cambio. La afirmacion negativa esta ACOTADA a lo que se sostiene -- el Manual no incorporo un capitulo equivalente a la Seccion 12 de AASHTO y no fija altura minima de relleno --, con los cinco lugares donde SI trata estructuras enterradas enumerados y paginados. Ya no dice «vacio absoluto». Sigue Cerrado.</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe</t>
+          <t>3ea627c + 7266bfe || S14 — RECONTRASTADO, sin cambio. La evidencia de indice falsa esta retirada y NOMBRADA como falsa en el propio criterio: el 2.11 del Manual es «DISEÑO DE BARRERAS DE SONIDO», no «Muros de Contencion y Estribos». Sigue Cerrado.</t>
         </is>
       </c>
     </row>
@@ -3650,17 +3650,17 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S9 + S13)</t>
+          <t>Claude Code (fase1, S14)</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 + 1f54f4f — LA PREMISA QUEDA RESUELTA (S13, conflicto #8); SIGUE PARCIAL PORQUE EL VALOR NO SE HA RETIRADO. Verificado contra las dos fuentes primarias por tres subagentes independientes: el salto 'licuable -&gt; Clase F' no lo escribe ninguno de los dos documentos (en las 1905 pag. de AASHTO los conjuntos de paginas con 'liquef' y con 'Site Class F' son DISJUNTOS; en las 673 del Manual la licuefaccion vive en cimentaciones y el Apendice A11, nunca en el numeral de clases de sitio). Y el argumento deja de ser por silencio -- que es lo que R95-073 habia acotado con razon -- por dos vias nuevas: (a) las dos fuentes PROHIBEN suponer la clase E o F sin dato geotecnico ni determinacion de la autoridad (AASHTO Art. 3.10.3.1 al pie de la Tabla 3.10.3.1-1, pag. impresa 3-102, articulado; Manual num. 2.4.3.11.2.1.1, pag. impresa 122, que lo endurece a 'no seran supuestas'), y este expediente no tiene ninguna de las dos; (b) el Art. 10.5.4.2 espera factor de sitio TABULADO para un sitio licuable, incompatible con que la licuefaccion lo hiciera Clase F. DECISION: 'clase_sitio' pasa a [S] sin valor. Fundamento, cinco respuestas con cita de pagina y texto exacto de memoria en docs/resolucion_clase_sitio.md. 12 citas nuevas en src/normativa/citas.py (registro 78 -&gt; 90) y 4 Discrepancia en discrepancias.py. LO QUE FALTA: retirar el valor 'F_con_factores_tabulados_por_adopcion' de criterios_adoptados.py, que es cableado y el conflicto #8 lo reserva a S14. Mientras siga ahi, el repositorio contiene la premisa. || FASE REASIGNADA F2 -&gt; F3 (S14), que es donde se aplica</t>
+          <t>4f45f15 + e73ab59 + 1f54f4f — LA PREMISA QUEDA RESUELTA (S13, conflicto #8); SIGUE PARCIAL PORQUE EL VALOR NO SE HA RETIRADO. Verificado contra las dos fuentes primarias por tres subagentes independientes: el salto 'licuable -&gt; Clase F' no lo escribe ninguno de los dos documentos (en las 1905 pag. de AASHTO los conjuntos de paginas con 'liquef' y con 'Site Class F' son DISJUNTOS; en las 673 del Manual la licuefaccion vive en cimentaciones y el Apendice A11, nunca en el numeral de clases de sitio). Y el argumento deja de ser por silencio -- que es lo que R95-073 habia acotado con razon -- por dos vias nuevas: (a) las dos fuentes PROHIBEN suponer la clase E o F sin dato geotecnico ni determinacion de la autoridad (AASHTO Art. 3.10.3.1 al pie de la Tabla 3.10.3.1-1, pag. impresa 3-102, articulado; Manual num. 2.4.3.11.2.1.1, pag. impresa 122, que lo endurece a 'no seran supuestas'), y este expediente no tiene ninguna de las dos; (b) el Art. 10.5.4.2 espera factor de sitio TABULADO para un sitio licuable, incompatible con que la licuefaccion lo hiciera Clase F. DECISION: 'clase_sitio' pasa a [S] sin valor. Fundamento, cinco respuestas con cita de pagina y texto exacto de memoria en docs/resolucion_clase_sitio.md. 12 citas nuevas en src/normativa/citas.py (registro 78 -&gt; 90) y 4 Discrepancia en discrepancias.py. LO QUE FALTA: retirar el valor 'F_con_factores_tabulados_por_adopcion' de criterios_adoptados.py, que es cableado y el conflicto #8 lo reserva a S14. Mientras siga ahi, el repositorio contiene la premisa. || FASE REASIGNADA F2 -&gt; F3 (S14), que es donde se aplica || S14 — S14 aplica la decision de S13 y con eso el repositorio DEJA DE CONTENER LA PREMISA, que era lo unico que faltaba: 'clase_sitio' pasa de [A] con valor 'F_con_factores_tabulados_por_adopcion' a [S] SIN VALOR, con trazabilidad (el procedimiento de lectura de la clase, paso a paso, y su ambito de corredor), sin sensibilidad -- la guardia la rechaza en un [S] -- y con `sin_consumidor` explicando por que el vacio se DECLARA y no se interpone. La memoria imprime los cuatro bloques de la seccion 4.1 del documento de resolucion desde M9.condicion_normativa_cabezal, con las dos prohibiciones literales leidas del registro (AASHTO_LRFD_9.3.10.3.1#EXCEPCIONES y MP.2.4.3.11.2.1.1#EXCEPCIONES) y no copiadas a mano. Se anadio ademas la cita AASHTO_LRFD_9.3.10.3.1#INVESTIGACION -- el deber positivo «a site investigation shall be undertaken sufficient to determine the Site Class», que vivia solo en la `nota` de otra cita y por eso la memoria no lo podia citar sin transcribirlo dos veces --, verificada contra el PDF (pag. impresa 3-102 / PDF 156). El registro pasa de 90 a 91 citas.</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4274,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — h_o deja de ser una formula 'sin numeral' y sin limite: num. 3.3.3 'Outlet Control', pag. impresa 3.24, con sus TRES condiciones transcritas verbatim y cada una atribuida a su sitio de la pagina (H_O_NUMERAL, H_O_CONDICION_TEXTO, H_O_FORMA_MAXIMO_TEXTO, H_O_CONDICION_APLICACION). DOS de las tres SE EVALUAN punto por punto: los limites HW/D &lt; 0.75 ('should not be used') y HW/D &lt; 1.2 ('caution'), como constantes [N] H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculados en control_salida(), filtrados por si el control de salida gobierna -- que es como la fuente los escribe -- e impresos EN LA MEMORIA DEL PUNTO junto a su HW. Es lo que la auditoria adversarial refuto de la primera version, que los declaraba sin evaluarlos pudiendo: el punto A-02 del CSV de ejemplo da HW/D=0.675 con el control de salida gobernando, y la memoria no lo decia. La condicion llega ademas siempre por UMBRALES_DE_VERIFICACION, tambien en la corrida bloqueada. QUEDA ABIERTO lo unico que no se puede evaluar sin un perfil de la lamina de agua: que el barril fluya lleno en la mayor parte de su longitud. Lo cerraria el procedimiento de barril parcialmente lleno del Cap. III. || REVISADO EN S12: el diferimiento sigue vigente. Lo abierto es la tercera condicion -- que el barril fluya lleno en la mayor parte de su longitud --, que no se puede evaluar sin el perfil de lamina de agua del Cap. III de HDS-5. S12 no implemento ese procedimiento.</t>
+          <t>3ed6b22 + 4f32683 — h_o deja de ser una formula 'sin numeral' y sin limite: num. 3.3.3 'Outlet Control', pag. impresa 3.24, con sus TRES condiciones transcritas verbatim y cada una atribuida a su sitio de la pagina (H_O_NUMERAL, H_O_CONDICION_TEXTO, H_O_FORMA_MAXIMO_TEXTO, H_O_CONDICION_APLICACION). DOS de las tres SE EVALUAN punto por punto: los limites HW/D &lt; 0.75 ('should not be used') y HW/D &lt; 1.2 ('caution'), como constantes [N] H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculados en control_salida(), filtrados por si el control de salida gobierna -- que es como la fuente los escribe -- e impresos EN LA MEMORIA DEL PUNTO junto a su HW. Es lo que la auditoria adversarial refuto de la primera version, que los declaraba sin evaluarlos pudiendo: el punto A-02 del CSV de ejemplo da HW/D=0.675 con el control de salida gobernando, y la memoria no lo decia. La condicion llega ademas siempre por UMBRALES_DE_VERIFICACION, tambien en la corrida bloqueada. QUEDA ABIERTO lo unico que no se puede evaluar sin un perfil de la lamina de agua: que el barril fluya lleno en la mayor parte de su longitud. Lo cerraria el procedimiento de barril parcialmente lleno del Cap. III. || REVISADO EN S12: el diferimiento sigue vigente. Lo abierto es la tercera condicion -- que el barril fluya lleno en la mayor parte de su longitud --, que no se puede evaluar sin el perfil de lamina de agua del Cap. III de HDS-5. S12 no implemento ese procedimiento. || S14 — NO CERRADO. Lo que queda abierto es la tercera condicion de uso de h_o -- que el barril fluya lleno en la mayor parte de su longitud --, que exige el procedimiento de barril parcialmente lleno del Cap. III del HDS-5, no implementado. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>4f45f15 + e73ab59 - P_IR = k_h*(W_w + W_s) implementado (`fuerza_inercia_muro`), con W_s definido como lo define la fuente -- suelo inmediatamente encima del muro, incluido el talon -- y no como el relleno del trasdos. La combinacion 100/50 - 50/100 en `demanda_sismica_cabezal`, con el piso 'no menor que el empuje activo estatico' aplicado al segundo caso y el mas desfavorable como gobernante. El ensamble automatico sigue detenido en 'predimensionamiento_cabezal', que es vacio ya declarado y al que se le suma el ancho del talon.</t>
+          <t>4f45f15 + e73ab59 - P_IR = k_h*(W_w + W_s) implementado (`fuerza_inercia_muro`), con W_s definido como lo define la fuente -- suelo inmediatamente encima del muro, incluido el talon -- y no como el relleno del trasdos. La combinacion 100/50 - 50/100 en `demanda_sismica_cabezal`, con el piso 'no menor que el empuje activo estatico' aplicado al segundo caso y el mas desfavorable como gobernante. El ensamble automatico sigue detenido en 'predimensionamiento_cabezal', que es vacio ya declarado y al que se le suma el ancho del talon. || S14 — RECONTRASTADO, sin cambio, y es el criterio de salida de la sesion: P_IR ESTA ENSAMBLADO. `fuerza_inercia_muro` da P_IR = k_h*(W_w + W_s) y `demanda_sismica_cabezal` arma los dos casos del num. 2.8.1.1.14.1 con el piso del empuje activo estatico y sin elegir el gobernante por la suma (comprobado ejecutandolos: 100/50 da 115.0 y 50/100 da 120.0 kN/m con el piso activo, sobre un ejemplo de k_h=0.5, W_w=100, W_s=40, P_AE=80, P_A=50). Lo que sigue detenido es el ENSAMBLE AUTOMATICO, y es un BLOQUEO EXPLICITO y no una omision: depende de 'predimensionamiento_cabezal', que es un vacio declarado con valor=None que entra en `criterios_sin_valor()`, y la razon esta escrita en `M9.FUNCIONES_SIN_CONSUMIDOR` para las tres funciones implicadas. La memoria lo imprime en `condicion_normativa_cabezal` con el numeral y con el aviso de que la combinacion no es una suma.</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — la ATRIBUCION queda cerrada: 'clases_producto_por_relleno' y el docstring de M8 dejan de difierir a ASTM A-807 (que no aparece en M 170M, M 36 ni A760) y difieren a ASTM A796/A796M, con A798/A798M para instalacion; se anota que la remision del EG-2013 507.05/.06/.08 a A-807 si es correcta pero es de materiales. QUEDA ABIERTO lo que la ficha dice que se puede cerrar hoy: transcribir la relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36. Es trabajo de la tabla de clases (C01 no la transcribe) y sigue en el vacio declarado 'clases_producto_por_relleno'.</t>
+          <t>3d59da0 — la ATRIBUCION queda cerrada: 'clases_producto_por_relleno' y el docstring de M8 dejan de difierir a ASTM A-807 (que no aparece en M 170M, M 36 ni A760) y difieren a ASTM A796/A796M, con A798/A798M para instalacion; se anota que la remision del EG-2013 507.05/.06/.08 a A-807 si es correcta pero es de materiales. QUEDA ABIERTO lo que la ficha dice que se puede cerrar hoy: transcribir la relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36. Es trabajo de la tabla de clases (C01 no la transcribe) y sigue en el vacio declarado 'clases_producto_por_relleno'. || S14 — NO CERRADO, y se deja dicho que sigue abierto. La mitad que la ficha dice que se puede cerrar hoy -- transcribir la relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 -- NO se hizo en esta sesion: es transcripcion de tabla y no entra en los criterios de salida de S14. Lo que S14 si deja comprobado, para quien la tome: la Tabla 1 de A760 es LEGIBLE renderizando la pag. PDF 3 a escala 2.0 (el texto extraido de ese PDF viene con la codificacion de fuente rota y por eso parecia inaccesible). Trae 30 filas de diametro nominal (4 in / 100 mm a 144 in / 3600 mm) por siete tamaños de corrugacion mas la circunferencia exterior minima. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -7010,11 +7010,19 @@
       <c r="I88" s="6" t="inlineStr"/>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K88" s="6" t="inlineStr"/>
-      <c r="L88" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>S14 — `TW` (tirante sobre el fondo de la salida, m) y `cota_TW` (cota absoluta, msnm) quedan declarados en constantes_normativas.HOMONIMIA_TW con lo que los separa -- cota_TW = cota_fondo_salida + TW -- y con la acotacion de la propia ficha: hoy la confusion no se puede ejercitar porque las cuatro filas del CSV traen cota_TW vacia, de modo que se declara como riesgo de nomenclatura y no como error demostrado. Lo imprime M11.bloque_homonimias en las dos plantillas.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -7056,11 +7064,19 @@
       <c r="I89" s="6" t="inlineStr"/>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K89" s="6" t="inlineStr"/>
-      <c r="L89" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>S14 — Los TRES sentidos de «recubrimiento» en HOMONIMIA_RECUBRIMIENTO: (a) altura de relleno de tierra; (b) recubrimiento de concreto sobre el acero (Manual Tabla 2.9.1.5.5.3-1); (c) el que faltaba, el REVESTIMIENTO metalico o bituminoso de la plancha, verificado contra el PDF del EG-2013 -- Tabla 507-02 «Recubrimiento en peso de zinc, de acuerdo al espesor del acero base», pag. impresa 971 (PDF 979), 610 a 915 g/m2 --, que es el que gobierna la proteccion del TMC en este ambiente. Se corrige ademas la afirmacion «no tienen ninguna relacion»: la fila que se citaba para decirlo ACOPLA (a) y (b) en su propio renglon. Lo que se sostiene es lo suficiente: son magnitudes distintas, con unidades distintas, y ninguna sustituye a la otra.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -7102,11 +7118,19 @@
       <c r="I90" s="6" t="inlineStr"/>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K90" s="6" t="inlineStr"/>
-      <c r="L90" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>S14 — HOMONIMIA_LUZ declara que «luz» es un dato de ENTRADA que clasifica el cruce (6.0 m, num. 4.1.1.3.1 y 4.1.1.5.1) y el diametro un RESULTADO del catalogo. Comprobado en el codigo que NINGUN modulo convierte una en otra: la luz entra en la Fase 2 y no vuelve a aparecer en el dimensionamiento, de modo que la equivalencia que el Manual no define tampoco hace falta. Queda anotado que el num. 4.1.1.3.4 a) admite «su equivalente de otra seccion» y que esa equivalencia hay que declararla ANTES de ofrecer una seccion no circular.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -7518,7 +7542,7 @@
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — la comparacion que la ficha reclama queda DECLARADA: 'hds5_embocadura_hdpe' lleva ahora la fila alternativa ('Circular CM / Headwall') en `sensibilidad` y su verificacion_pendiente dice con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila: la adopcion se sostiene en el perfil de pared en la boca (argumento fisico que la ficha no refuta), no en un margen de seguridad, y elegir la del metal por su resultado seria sustituir una analogia por otra. Lo que cierra el punto es el detalle constructivo, y eso sigue abierto.</t>
+          <t>3d59da0 — la comparacion que la ficha reclama queda DECLARADA: 'hds5_embocadura_hdpe' lleva ahora la fila alternativa ('Circular CM / Headwall') en `sensibilidad` y su verificacion_pendiente dice con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila: la adopcion se sostiene en el perfil de pared en la boca (argumento fisico que la ficha no refuta), no en un margen de seguridad, y elegir la del metal por su resultado seria sustituir una analogia por otra. Lo que cierra el punto es el detalle constructivo, y eso sigue abierto. || S14 — NO CERRADO. Lo que la ficha pide para cerrarlo es el detalle constructivo de la embocadura, que no es trabajo de esta sesion. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -7732,11 +7756,19 @@
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K101" s="6" t="inlineStr"/>
-      <c r="L101" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>S14 — «Clase F» se desambigua con las TRES acepciones del corpus -- clase de sitio sismica, concreto EG-2013 Tabla 503-07 y acero ASTM A668 del propio Manual, pag. impresa 289 --, escritas UNA vez en constantes_normativas.HOMONIMIA_CLASE_F y renderizadas por `homonimia_como_texto` en los dos sitios que las imprimen: M9.condicion_normativa_cabezal (pegada a la cadena sismica, donde el lector se encuentra el termino) y el glosario nuevo M11.bloque_homonimias.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -7848,17 +7880,17 @@
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S6)</t>
+          <t>Claude Code (fase1, S14)</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — el docstring de ControlEntrada.HW_sobre_D deja de decir que es 'lo que compara V4b': esa comparacion no existe. Se dice lo que se sostiene (hoy solo lo leen los tests) y por que el campo se conserva. QUEDA ABIERTO que no tenga lector de produccion, hasta el cableado de V4b (S14).</t>
+          <t>3ed6b22 + 4f32683 — el docstring de ControlEntrada.HW_sobre_D deja de decir que es 'lo que compara V4b': esa comparacion no existe. Se dice lo que se sostiene (hoy solo lo leen los tests) y por que el campo se conserva. QUEDA ABIERTO que no tenga lector de produccion, hasta el cableado de V4b (S14). || S14 — `ControlEntrada.HW_sobre_D` sigue sin lector de produccion, y ahora con la razon CORRECTA escrita. Su docstring predecia que ese campo «sera el argumento del chequeo el dia que se cablee», y no lo es: V4b divide el HW del control gobernante. Es la misma clase de defecto que SIS-A-03 -- texto que describe un estado que el codigo no tiene --, solo que en futuro. Corregido tambien el docstring de M4_control, que arrastraba la misma prediccion.</t>
         </is>
       </c>
     </row>
@@ -11446,11 +11478,19 @@
       <c r="I170" s="6" t="inlineStr"/>
       <c r="J170" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K170" s="6" t="inlineStr"/>
-      <c r="L170" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K170" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L170" s="6" t="inlineStr">
+        <is>
+          <t>S14 — `_NORMA_PRODUCTO` del concreto pasa de «ASTM C76 / AASHTO M170» -- las versiones EN PULGADAS -- a «AASHTO M 170M-04 / ASTM C 76M-02 (metrica)», que es como se designa el documento que hay en normas/ y que su num. 1.2 declara «the metric counterpart of M 170» (verificado sobre el PDF). La de TMC pasa a la designacion DUAL «AASHTO M 36 / ASTM A760/A760M-10», que es la del registro, sin inventarle una metrica que la norma no separa. Corregido tambien el comentario de `modelos.Material.norma_producto`, que ponia las imperiales como ejemplo.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -11492,11 +11532,19 @@
       <c r="I171" s="6" t="inlineStr"/>
       <c r="J171" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K171" s="6" t="inlineStr"/>
-      <c r="L171" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K171" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L171" s="6" t="inlineStr">
+        <is>
+          <t>S14 — Verificado contra el PDF del Manual, pagina por pagina: el texto del num. 2.8.1.3.1.2c esta en la pag. impresa 272 (PDF 273), la Figura 2.8.1.3.1.2c-1 -- suelos COHESIVOS -- en la 273 (PDF 274) y la Figura 2.8.1.3.1.2c-2 -- suelos NO COHESIVOS -- en la 274 (PDF 275). El rango declarado, «pags. 272-273», dejaba fuera la segunda. Corregido en NUMERAL_ZAPATA_EN_TALUD y en la fuente del criterio 'N_cq_N_gammaq_meyerhof', las dos con la figura atribuida a su pagina y con cual aplica segun el tipo de suelo de fundacion.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -12768,11 +12816,19 @@
       </c>
       <c r="J195" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K195" s="6" t="inlineStr"/>
-      <c r="L195" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L195" s="6" t="inlineStr">
+        <is>
+          <t>S14 — `KU_METRICO` pasa a `KU_SI`, con el sufijo que CLAUDE.md exige a toda constante empirica dependiente de unidades, y con el equivalente imperial nombrado y la razon de no usarlo: en el sistema ingles Ku vale 1.0 -- la fuente los imprime juntos, «Ku Unit conversion 1.0 (1.811 SI)» -- y usar el 1.0 en metrico es el error silencioso SIMETRICO al del 29 de K_FRICCION_SI. Renombrado en sus cuatro consumidores y en el manifiesto; la hoja de ruta llevaba el nombre viejo en su Anexo B y se corrigio ahi tambien. La otra mitad de la ficha, el ambito de DIAMETRO_MIN, ya estaba cerrada en DIAMETRO_MIN_AMBITO con sus dos condicionantes.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
@@ -12814,11 +12870,19 @@
       <c r="I196" s="6" t="inlineStr"/>
       <c r="J196" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K196" s="6" t="inlineStr"/>
-      <c r="L196" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K196" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L196" s="6" t="inlineStr">
+        <is>
+          <t>S14 — Las cuatro referencias por NUMERO DE LINEA a la hoja de ruta que quedaban en el codigo se reanclaron por simbolo y texto, que es la regla 4 de CLAUDE.md: «linea 806» apuntaba a la longitud maxima de cuneta y ahora cita el comentario de la asignacion `D_MAX`; «linea 523» y «linea 546» caian en separadores «---» y ahora citan «tabla de Sec. 7.A, fila Concreto y TMC» y «tabla de Fase 8, fila TMC»; «linea 832» ahora cita el comentario de `H_RELLENO_MIN["tmc"]`. El defecto que la ficha denunciaba en el comentario de K_FRICCION_SI ya se habia corregido antes. De paso se reanclaron por simbolo siete referencias rotas del manifiesto (NUMERAL_C_PHI, NUMERAL_ZAPATA_TALUD_E050, Ks, NUMERAL_CRITICO, PERFIL_SUELO_PRESUNTO y los tres nombres inexistentes e3_/e4_/e5_, que son hoy `verificar_deslizamiento`, `verificar_estabilidad_global` y `verificar_talud`).</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -13392,11 +13456,19 @@
       <c r="I207" s="6" t="inlineStr"/>
       <c r="J207" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K207" s="6" t="inlineStr"/>
-      <c r="L207" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S14)</t>
+        </is>
+      </c>
+      <c r="L207" s="6" t="inlineStr">
+        <is>
+          <t>S14 — Las constantes NUMERAL_* de modulo sin lector son OCHO, no siete, y su decision queda escrita una sola vez en `modelos.NUMERALES_DE_SECCION_SIN_LECTOR` -- junto a `ReferenciaNormativa`, que es la clase que define la distincion de la que se trata: son coordenadas del apartado de la hoja de ruta, no citas. Se dice por que no se borran (son el mapa modulo -&gt; apartado), por que NO se imprimen (meter «4.1» en una memoria como si fuera un numeral es el defecto que ReferenciaNormativa existe para impedir) y la segunda razon de dos de ellas, NUMERAL_V5 y NUMERAL_V8, que son bloqueos ya declarados. La guardia que lo vigile es trabajo de S16: escribir hoy un test contra el estado actual congelaria defectos que las fases de correccion siguen cerrando (regla 6 de CLAUDE.md).</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -7020,7 +7020,7 @@
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>S14 — `TW` (tirante sobre el fondo de la salida, m) y `cota_TW` (cota absoluta, msnm) quedan declarados en constantes_normativas.HOMONIMIA_TW con lo que los separa -- cota_TW = cota_fondo_salida + TW -- y con la acotacion de la propia ficha: hoy la confusion no se puede ejercitar porque las cuatro filas del CSV traen cota_TW vacia, de modo que se declara como riesgo de nomenclatura y no como error demostrado. Lo imprime M11.bloque_homonimias en las dos plantillas.</t>
+          <t>27f0963 — `TW` (tirante sobre el fondo de la salida, m) y `cota_TW` (cota absoluta, msnm) quedan declarados en constantes_normativas.HOMONIMIA_TW con lo que los separa -- cota_TW = cota_fondo_salida + TW -- y con la acotacion de la propia ficha: hoy la confusion no se puede ejercitar porque las cuatro filas del CSV traen cota_TW vacia, de modo que se declara como riesgo de nomenclatura y no como error demostrado. Lo imprime M11.bloque_homonimias en las dos plantillas.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
-          <t>S14 — Los TRES sentidos de «recubrimiento» en HOMONIMIA_RECUBRIMIENTO: (a) altura de relleno de tierra; (b) recubrimiento de concreto sobre el acero (Manual Tabla 2.9.1.5.5.3-1); (c) el que faltaba, el REVESTIMIENTO metalico o bituminoso de la plancha, verificado contra el PDF del EG-2013 -- Tabla 507-02 «Recubrimiento en peso de zinc, de acuerdo al espesor del acero base», pag. impresa 971 (PDF 979), 610 a 915 g/m2 --, que es el que gobierna la proteccion del TMC en este ambiente. Se corrige ademas la afirmacion «no tienen ninguna relacion»: la fila que se citaba para decirlo ACOPLA (a) y (b) en su propio renglon. Lo que se sostiene es lo suficiente: son magnitudes distintas, con unidades distintas, y ninguna sustituye a la otra.</t>
+          <t>27f0963 — Los TRES sentidos de «recubrimiento» en HOMONIMIA_RECUBRIMIENTO: (a) altura de relleno de tierra; (b) recubrimiento de concreto sobre el acero (Manual Tabla 2.9.1.5.5.3-1); (c) el que faltaba, el REVESTIMIENTO metalico o bituminoso de la plancha, verificado contra el PDF del EG-2013 -- Tabla 507-02 «Recubrimiento en peso de zinc, de acuerdo al espesor del acero base», pag. impresa 971 (PDF 979), 610 a 915 g/m2 --, que es el que gobierna la proteccion del TMC en este ambiente. Se corrige ademas la afirmacion «no tienen ninguna relacion»: la fila que se citaba para decirlo ACOPLA (a) y (b) en su propio renglon. Lo que se sostiene es lo suficiente: son magnitudes distintas, con unidades distintas, y ninguna sustituye a la otra.</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="L90" s="6" t="inlineStr">
         <is>
-          <t>S14 — HOMONIMIA_LUZ declara que «luz» es un dato de ENTRADA que clasifica el cruce (6.0 m, num. 4.1.1.3.1 y 4.1.1.5.1) y el diametro un RESULTADO del catalogo. Comprobado en el codigo que NINGUN modulo convierte una en otra: la luz entra en la Fase 2 y no vuelve a aparecer en el dimensionamiento, de modo que la equivalencia que el Manual no define tampoco hace falta. Queda anotado que el num. 4.1.1.3.4 a) admite «su equivalente de otra seccion» y que esa equivalencia hay que declararla ANTES de ofrecer una seccion no circular.</t>
+          <t>27f0963 — HOMONIMIA_LUZ declara que «luz» es un dato de ENTRADA que clasifica el cruce (6.0 m, num. 4.1.1.3.1 y 4.1.1.5.1) y el diametro un RESULTADO del catalogo. Comprobado en el codigo que NINGUN modulo convierte una en otra: la luz entra en la Fase 2 y no vuelve a aparecer en el dimensionamiento, de modo que la equivalencia que el Manual no define tampoco hace falta. Queda anotado que el num. 4.1.1.3.4 a) admite «su equivalente de otra seccion» y que esa equivalencia hay que declararla ANTES de ofrecer una seccion no circular.</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="L101" s="6" t="inlineStr">
         <is>
-          <t>S14 — «Clase F» se desambigua con las TRES acepciones del corpus -- clase de sitio sismica, concreto EG-2013 Tabla 503-07 y acero ASTM A668 del propio Manual, pag. impresa 289 --, escritas UNA vez en constantes_normativas.HOMONIMIA_CLASE_F y renderizadas por `homonimia_como_texto` en los dos sitios que las imprimen: M9.condicion_normativa_cabezal (pegada a la cadena sismica, donde el lector se encuentra el termino) y el glosario nuevo M11.bloque_homonimias.</t>
+          <t>27f0963 — «Clase F» se desambigua con las TRES acepciones del corpus -- clase de sitio sismica, concreto EG-2013 Tabla 503-07 y acero ASTM A668 del propio Manual, pag. impresa 289 --, escritas UNA vez en constantes_normativas.HOMONIMIA_CLASE_F y renderizadas por `homonimia_como_texto` en los dos sitios que las imprimen: M9.condicion_normativa_cabezal (pegada a la cadena sismica, donde el lector se encuentra el termino) y el glosario nuevo M11.bloque_homonimias.</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11488,7 @@
       </c>
       <c r="L170" s="6" t="inlineStr">
         <is>
-          <t>S14 — `_NORMA_PRODUCTO` del concreto pasa de «ASTM C76 / AASHTO M170» -- las versiones EN PULGADAS -- a «AASHTO M 170M-04 / ASTM C 76M-02 (metrica)», que es como se designa el documento que hay en normas/ y que su num. 1.2 declara «the metric counterpart of M 170» (verificado sobre el PDF). La de TMC pasa a la designacion DUAL «AASHTO M 36 / ASTM A760/A760M-10», que es la del registro, sin inventarle una metrica que la norma no separa. Corregido tambien el comentario de `modelos.Material.norma_producto`, que ponia las imperiales como ejemplo.</t>
+          <t>27f0963 — `_NORMA_PRODUCTO` del concreto pasa de «ASTM C76 / AASHTO M170» -- las versiones EN PULGADAS -- a «AASHTO M 170M-04 / ASTM C 76M-02 (metrica)», que es como se designa el documento que hay en normas/ y que su num. 1.2 declara «the metric counterpart of M 170» (verificado sobre el PDF). La de TMC pasa a la designacion DUAL «AASHTO M 36 / ASTM A760/A760M-10», que es la del registro, sin inventarle una metrica que la norma no separa. Corregido tambien el comentario de `modelos.Material.norma_producto`, que ponia las imperiales como ejemplo.</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="L171" s="6" t="inlineStr">
         <is>
-          <t>S14 — Verificado contra el PDF del Manual, pagina por pagina: el texto del num. 2.8.1.3.1.2c esta en la pag. impresa 272 (PDF 273), la Figura 2.8.1.3.1.2c-1 -- suelos COHESIVOS -- en la 273 (PDF 274) y la Figura 2.8.1.3.1.2c-2 -- suelos NO COHESIVOS -- en la 274 (PDF 275). El rango declarado, «pags. 272-273», dejaba fuera la segunda. Corregido en NUMERAL_ZAPATA_EN_TALUD y en la fuente del criterio 'N_cq_N_gammaq_meyerhof', las dos con la figura atribuida a su pagina y con cual aplica segun el tipo de suelo de fundacion.</t>
+          <t>27f0963 — Verificado contra el PDF del Manual, pagina por pagina: el texto del num. 2.8.1.3.1.2c esta en la pag. impresa 272 (PDF 273), la Figura 2.8.1.3.1.2c-1 -- suelos COHESIVOS -- en la 273 (PDF 274) y la Figura 2.8.1.3.1.2c-2 -- suelos NO COHESIVOS -- en la 274 (PDF 275). El rango declarado, «pags. 272-273», dejaba fuera la segunda. Corregido en NUMERAL_ZAPATA_EN_TALUD y en la fuente del criterio 'N_cq_N_gammaq_meyerhof', las dos con la figura atribuida a su pagina y con cual aplica segun el tipo de suelo de fundacion.</t>
         </is>
       </c>
     </row>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="L195" s="6" t="inlineStr">
         <is>
-          <t>S14 — `KU_METRICO` pasa a `KU_SI`, con el sufijo que CLAUDE.md exige a toda constante empirica dependiente de unidades, y con el equivalente imperial nombrado y la razon de no usarlo: en el sistema ingles Ku vale 1.0 -- la fuente los imprime juntos, «Ku Unit conversion 1.0 (1.811 SI)» -- y usar el 1.0 en metrico es el error silencioso SIMETRICO al del 29 de K_FRICCION_SI. Renombrado en sus cuatro consumidores y en el manifiesto; la hoja de ruta llevaba el nombre viejo en su Anexo B y se corrigio ahi tambien. La otra mitad de la ficha, el ambito de DIAMETRO_MIN, ya estaba cerrada en DIAMETRO_MIN_AMBITO con sus dos condicionantes.</t>
+          <t>27f0963 — `KU_METRICO` pasa a `KU_SI`, con el sufijo que CLAUDE.md exige a toda constante empirica dependiente de unidades, y con el equivalente imperial nombrado y la razon de no usarlo: en el sistema ingles Ku vale 1.0 -- la fuente los imprime juntos, «Ku Unit conversion 1.0 (1.811 SI)» -- y usar el 1.0 en metrico es el error silencioso SIMETRICO al del 29 de K_FRICCION_SI. Renombrado en sus cuatro consumidores y en el manifiesto; la hoja de ruta llevaba el nombre viejo en su Anexo B y se corrigio ahi tambien. La otra mitad de la ficha, el ambito de DIAMETRO_MIN, ya estaba cerrada en DIAMETRO_MIN_AMBITO con sus dos condicionantes.</t>
         </is>
       </c>
     </row>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="L196" s="6" t="inlineStr">
         <is>
-          <t>S14 — Las cuatro referencias por NUMERO DE LINEA a la hoja de ruta que quedaban en el codigo se reanclaron por simbolo y texto, que es la regla 4 de CLAUDE.md: «linea 806» apuntaba a la longitud maxima de cuneta y ahora cita el comentario de la asignacion `D_MAX`; «linea 523» y «linea 546» caian en separadores «---» y ahora citan «tabla de Sec. 7.A, fila Concreto y TMC» y «tabla de Fase 8, fila TMC»; «linea 832» ahora cita el comentario de `H_RELLENO_MIN["tmc"]`. El defecto que la ficha denunciaba en el comentario de K_FRICCION_SI ya se habia corregido antes. De paso se reanclaron por simbolo siete referencias rotas del manifiesto (NUMERAL_C_PHI, NUMERAL_ZAPATA_TALUD_E050, Ks, NUMERAL_CRITICO, PERFIL_SUELO_PRESUNTO y los tres nombres inexistentes e3_/e4_/e5_, que son hoy `verificar_deslizamiento`, `verificar_estabilidad_global` y `verificar_talud`).</t>
+          <t>27f0963 — Las cuatro referencias por NUMERO DE LINEA a la hoja de ruta que quedaban en el codigo se reanclaron por simbolo y texto, que es la regla 4 de CLAUDE.md: «linea 806» apuntaba a la longitud maxima de cuneta y ahora cita el comentario de la asignacion `D_MAX`; «linea 523» y «linea 546» caian en separadores «---» y ahora citan «tabla de Sec. 7.A, fila Concreto y TMC» y «tabla de Fase 8, fila TMC»; «linea 832» ahora cita el comentario de `H_RELLENO_MIN["tmc"]`. El defecto que la ficha denunciaba en el comentario de K_FRICCION_SI ya se habia corregido antes. De paso se reanclaron por simbolo siete referencias rotas del manifiesto (NUMERAL_C_PHI, NUMERAL_ZAPATA_TALUD_E050, Ks, NUMERAL_CRITICO, PERFIL_SUELO_PRESUNTO y los tres nombres inexistentes e3_/e4_/e5_, que son hoy `verificar_deslizamiento`, `verificar_estabilidad_global` y `verificar_talud`).</t>
         </is>
       </c>
     </row>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="L207" s="6" t="inlineStr">
         <is>
-          <t>S14 — Las constantes NUMERAL_* de modulo sin lector son OCHO, no siete, y su decision queda escrita una sola vez en `modelos.NUMERALES_DE_SECCION_SIN_LECTOR` -- junto a `ReferenciaNormativa`, que es la clase que define la distincion de la que se trata: son coordenadas del apartado de la hoja de ruta, no citas. Se dice por que no se borran (son el mapa modulo -&gt; apartado), por que NO se imprimen (meter «4.1» en una memoria como si fuera un numeral es el defecto que ReferenciaNormativa existe para impedir) y la segunda razon de dos de ellas, NUMERAL_V5 y NUMERAL_V8, que son bloqueos ya declarados. La guardia que lo vigile es trabajo de S16: escribir hoy un test contra el estado actual congelaria defectos que las fases de correccion siguen cerrando (regla 6 de CLAUDE.md).</t>
+          <t>27f0963 — Las constantes NUMERAL_* de modulo sin lector son OCHO, no siete, y su decision queda escrita una sola vez en `modelos.NUMERALES_DE_SECCION_SIN_LECTOR` -- junto a `ReferenciaNormativa`, que es la clase que define la distincion de la que se trata: son coordenadas del apartado de la hoja de ruta, no citas. Se dice por que no se borran (son el mapa modulo -&gt; apartado), por que NO se imprimen (meter «4.1» en una memoria como si fuera un numeral es el defecto que ReferenciaNormativa existe para impedir) y la segunda razon de dos de ellas, NUMERAL_V5 y NUMERAL_V8, que son bloqueos ya declarados. La guardia que lo vigile es trabajo de S16: escribir hoy un test contra el estado actual congelaria defectos que las fases de correccion siguen cerrando (regla 6 de CLAUDE.md).</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -12504,11 +12504,19 @@
       <c r="I189" s="6" t="inlineStr"/>
       <c r="J189" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K189" s="6" t="inlineStr"/>
-      <c r="L189" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S15)</t>
+        </is>
+      </c>
+      <c r="L189" s="6" t="inlineStr">
+        <is>
+          <t>d158496 — la guardia que faltaba: DatoSitio.__post_init__ + _coherencia_de_datos_sitio() al importar, homologas de _verificar_criterio/_coherencia_de_etiquetas. Rechaza el caso exacto del hallazgo (trazabilidad="" con etiqueta="A") y los campos con que un [S] se reproduce. Va en __post_init__ y no solo en el barrido porque datos_sitio.py no tiene API de escritura: el unico camino es construir el objeto. tests/test_datos_sitio.py, 11 tests nuevos.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -8886,11 +8886,19 @@
       <c r="I120" s="6" t="inlineStr"/>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K120" s="6" t="inlineStr"/>
-      <c r="L120" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — El manejador de EJECUTAR pasa de (OSError, ValueError) a (OSError, UnicodeDecodeError, json.JSONDecodeError), el mismo brazo estrecho que usa cli.py::main: un ValueError nacido en el pipeline ya no se muestra como 'No se pudo leer la entrada' ni se come el brazo que imprime la traza. UnicodeDecodeError se nombra explicitamente porque es subclase de ValueError y estrechar sin el habria sido una regresion. tests/test_gui_contrato.py.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -8936,11 +8944,19 @@
       <c r="I121" s="6" t="inlineStr"/>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K121" s="6" t="inlineStr"/>
-      <c r="L121" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -8986,11 +9002,19 @@
       <c r="I122" s="6" t="inlineStr"/>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K122" s="6" t="inlineStr"/>
-      <c r="L122" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — La rama que SI escribe el archivo fuente de los criterios se ejecuta ahora sobre una copia del archivo en tmp_path, con lectura posterior del contenido escrito. tests/test_criterios_adoptados.py.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -9036,11 +9060,19 @@
       <c r="I123" s="6" t="inlineStr"/>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K123" s="6" t="inlineStr"/>
-      <c r="L123" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Caso patron CP-9 nuevo (CP9_MONONOBE_OKABE, tres juegos con phi, i, beta, delta, k_h y k_v todos distintos y distintos de cero, mas CP9_RANKINE_LIMITE), autoverificado en el bloque __main__ del fixture con recomputacion independiente. El caso limite de Rankine era ciego a los signos porque con i=beta=delta=0 los cuatro cosenos son simetricos. Barrido de mutacion: los diez mutantes de signo de k_ae_mononobe_okabe y angulo_inercia_sismica MUEREN, incluido el [1+R]-&gt;[1-R] de la errata del Manual.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -9086,11 +9118,19 @@
       <c r="I124" s="6" t="inlineStr"/>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K124" s="6" t="inlineStr"/>
-      <c r="L124" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L124" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Caso patron CP-9 bloque de empujes (CP9_EMPUJE_TRASDOS), con k_v = 0.15 de PRUEBA para que el factor (1-k_v) sea visible -- el test viejo invocaba con k_v = 0.0 y el mutante era indetectable por construccion. El unico assert era tautologico porque incremento_sismico llama a las mismas dos funciones que el test usaba para armar el lado derecho. Barrido de mutacion: los cuatro mutantes de empuje_activo_sismico_total mueren, mas los de empuje_activo_estatico y brazo_incremento_sismico.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -9136,11 +9176,19 @@
       <c r="I125" s="6" t="inlineStr"/>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K125" s="6" t="inlineStr"/>
-      <c r="L125" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Asserts de VALOR sobre el FS de E3: verificar_deslizamiento se contrasta contra un FS calculado a mano (65/50 = 1.30), de modo que el mutante FS = R*A (4500) y la guarda invertida (fs = inf siempre) mueren los dos. Se abrio ademas, sin ID de auditoria propio, la contraparte que la ficha daba por cubierta. tests/test_M9_cabezal.py.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -9186,11 +9234,19 @@
       <c r="I126" s="6" t="inlineStr"/>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K126" s="6" t="inlineStr"/>
-      <c r="L126" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L126" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — tests/test_modelos.py pasa de comparar ORDEN a comparar VALOR en EmpujesTrasdos.empuje_horizontal_total y .momento_volcante, con los terminos desglosados. Mueren * -&gt; /, + -&gt; -, borrar LS o WA de la suma, meter U_subpresion (que es vertical) en la horizontal y usar altura_empuje en vez de z_activo. Ademas modelos.EmpujesTrasdos.__post_init__ hace imposible el estado EQ a medias -- incremento_sismico con z_incremento=None contaba EQ en la fuerza y lo perdia en el momento volcante, que es NO conservador.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -9236,11 +9292,19 @@
       <c r="I127" s="6" t="inlineStr"/>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K127" s="6" t="inlineStr"/>
-      <c r="L127" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Caso patron CP9_GEOMETRIA_7B, consumido por tests/test_M7_geometria.py, con assert de valor sobre la rama viva de longitud y proyeccion. Mueren los tres mutantes de la ficha y los cuatro mas que el barrido encontro en las mismas tres lineas, mas los dos de g2_cota_salida que ninguna auditoria habia reportado. Las referencias archivo:linea de la ficha (442/454/532/534) estaban corridas ~180 lineas; el cierre se ancla por simbolo.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -9286,11 +9350,19 @@
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K128" s="6" t="inlineStr"/>
-      <c r="L128" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L128" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Cerrado con SIS-C-06: el barrido recorre cli.py y gui/app.py, con la regla estrechada de la capa de presentacion declarada en el encabezado de tests/test_sin_literales.py.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -9336,11 +9408,19 @@
       <c r="I129" s="6" t="inlineStr"/>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K129" s="6" t="inlineStr"/>
-      <c r="L129" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L129" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — La guardia de subcadena de factor_muro pasa a comprobacion AST (tests/apoyo/estructura.py::constructor_de_clave): no mira comillas, de modo que la entrada con comillas simples que evadia la version anterior ya no evade. Al portarla se descubrio que el test hermano estaba VERDE SOBRE UN COMENTARIO: FACTOR_MURO_TABLA se habia retirado de constantes_normativas.py (NOR-PUE-07) y la cadena sobrevivia dentro del comentario que explica la retirada. Reescrito contra los simbolos que si existen (REDUCCION_KH_POR_DESPLAZAMIENTO, FACTOR_MURO_DECLARACIONES).</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -9386,11 +9466,19 @@
       <c r="I130" s="6" t="inlineStr"/>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K130" s="6" t="inlineStr"/>
-      <c r="L130" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L130" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Los 22 asserts de subcadena sobre el texto fuente pasan al AST (tests/apoyo/estructura.py: nombres_asignados, valor_asignado, nombres_usados, claves_de_dict, constructor_de_clave, llamadas_a, argumentos_de_texto). Un comentario o un docstring ya no los satisface. Afectados: test_sin_literales.py, test_criterios_adoptados.py, test_datos_sitio.py, test_M8_estructural.py.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -9436,11 +9524,19 @@
       <c r="I131" s="6" t="inlineStr"/>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K131" s="6" t="inlineStr"/>
-      <c r="L131" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L131" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — La marca deja de buscarse como subcadena de la linea y se detecta con tokenize, como COMMENT token: una marca dentro de un string o de un docstring ya no exime nada. Se exige ademas la razon ('# literal-ok: &lt;razon&gt;' con texto detras), como escribe CLAUDE.md; dos marcas del arbol que no la traian la llevan ahora. tests/test_sin_literales.py::test_sis_c_03_* y ::test_toda_marca_declara_su_razon.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -9486,11 +9582,19 @@
       <c r="I132" s="6" t="inlineStr"/>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K132" s="6" t="inlineStr"/>
-      <c r="L132" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L132" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — _nodos_de_indice deja de eximir la CLAVE de una tabla declarada: un entero dentro de un subscript sobre un nombre en MAYUSCULAS es una magnitud, no una posicion, y cae. _base_del_subscript resuelve la raiz, de modo que TABLA[900][2500] cae en los dos niveles y no solo en el primero. El indice sobre una secuencia sigue exento, que es lo unico que CLAUDE.md permite.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -9536,11 +9640,19 @@
       <c r="I133" s="6" t="inlineStr"/>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K133" s="6" t="inlineStr"/>
-      <c r="L133" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — La lista de exentos se compara por RUTA RELATIVA a la raiz del barrido y no por nombre de archivo: un src/modulos/dominios.py ya no queda exento por homonimia. tests/test_sin_literales.py::test_sis_c_05_el_exento_se_reconoce_por_ruta_y_no_por_nombre.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -9590,11 +9702,19 @@
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K134" s="6" t="inlineStr"/>
-      <c r="L134" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — cli.py, gui/app.py y verificar_sesion.py entran al barrido con una regla ESTRECHADA y declarada, homologa a la que ya tenia src/normativa/: un entero dentro de una llamada de presentacion pasa; un float o un complejo cae SIEMPRE, tambien marcado; una clave de tabla cae aunque este dentro de la llamada; lo demas cae salvo marca. Se anadieron 34 marcas de geometria y se nombraron ANCHO, SANGRIA_DETALLE, DECIMALES_PENDIENTE, HALLAZGOS_EN_LA_MATRIZ y ANCHO_CONSOLA. Ademas test_ningun_py_fuera_de_src_se_queda_sin_declarar cierra la FAMILIA: todo .py fuera de src/ tiene que estar vigilado o exento con su razon escrita (conftest.py es el unico exento, y su razon esta escrita).</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -9640,11 +9760,19 @@
       <c r="I135" s="6" t="inlineStr"/>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K135" s="6" t="inlineStr"/>
-      <c r="L135" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — La marca vale SOLO en la linea fisica del literal: una marca en linea propia ya no blanquea la linea siguiente. Las expresiones partidas de src/ que dependian de la linea anterior llevan ahora la marca en su propia linea. tests/test_sin_literales.py::test_sis_c_07_la_marca_en_linea_propia_no_exime_la_siguiente y ::test_sis_c_07_la_marca_al_final_de_la_linea_si_exime.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -9690,11 +9818,19 @@
       <c r="I136" s="6" t="inlineStr"/>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K136" s="6" t="inlineStr"/>
-      <c r="L136" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L136" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — La rama if informe.dimensionado de M11.exportar_csv se ejercita ahora con un punto REALMENTE dimensionado, comprobando las filas y no solo la cabecera. tests/test_cli.py.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -9740,11 +9876,19 @@
       <c r="I137" s="6" t="inlineStr"/>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K137" s="6" t="inlineStr"/>
-      <c r="L137" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Las guardas de ErrorProyecto sin cobertura quedan ejercitadas en M1, M2, M4, M5, M7, M9, criterios_adoptados, datos_sitio, modelos y cli. MEDIDO con coverage sobre el arbol de cierre: de los 115 `raise` de la taxonomia que hay en src/ + cli.py, 112 quedan cubiertos y solo 3 no, y esos tres son guardas defensivas provablemente inalcanzables del mismo tipo que documenta SIS-B-23 -- M1_clasificacion._categoria (segundo `raise`, tras un CategoriaTR() que ya tuvo exito), M9_cabezal:541 (fin del barrido de tramos que cubren todo el rango, con la razon escrita en el propio codigo) y M9_cabezal:1249 (idem para la tabla de h_eq). CORRECCION A LA FICHA: dice trece `raise` sin cobertura; la auditoria corrio sobre un arbol menor y el conteo no es portable al de hoy.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -9790,11 +9934,19 @@
       <c r="I138" s="6" t="inlineStr"/>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K138" s="6" t="inlineStr"/>
-      <c r="L138" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Las seis banderas del CLI sin cobertura (--pdf, --csv-resumen, --criterios y las tres restantes) se ejercitan de punta a punta, cableado bandera-&gt;funcion incluido. tests/test_cli.py.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -9840,11 +9992,19 @@
       <c r="I139" s="6" t="inlineStr"/>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K139" s="6" t="inlineStr"/>
-      <c r="L139" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Las dos ramas de _texto -- columna ausente del encabezado y celda de texto vacia (id, progresiva_km, familia, sucs_fundacion) -- se ejecutan y distinguen DatoFaltanteError de DatoInvalidoError. tests/test_M0_carga.py.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -9890,11 +10050,19 @@
       <c r="I140" s="6" t="inlineStr"/>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K140" s="6" t="inlineStr"/>
-      <c r="L140" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L140" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — PARCIAL. El fixture gana CP-9 y con el pasan a consumir caso patron M7 (CP9_GEOMETRIA_7B) y M9 (CP9_MONONOBE_OKABE, CP9_RANKINE_LIMITE, CP9_EMPUJE_TRASDOS). SIGUEN SIN CASO PATRON M2, M8 y M10: para esos el fixture no da dorados y fabricarlos aqui seria inventar el valor de referencia, que es justo lo que el conflicto n.7 (CP-1 dorados / SIS-F-14) prohibe. Queda declarado como deuda abierta.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -10002,11 +10170,19 @@
       <c r="I142" s="6" t="inlineStr"/>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K142" s="6" t="inlineStr"/>
-      <c r="L142" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L142" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Las cinco afirmaciones falsas de los dos .md de fixtures se corrigen EN SU SITIO y con la razon, en vez de borrarse: v_max_hdpe y v_max_tmc ya no son vacios (4.572 m/s [C], WSDOT M 23-03.12 Tabla 8-4) y el fixture avisa de que aplicar 6.0/4.5 pisaria un valor con cita; remanso_derecho_via ya no aborta la corrida; los cinco sitios de AssertionError se anclan por SIMBOLO y no por archivo:linea (uno de los cinco ya no existe); Material.v_max_rango es un simbolo retirado; y el baseline de 653 tests se sustituye por la instruccion de leerlo de origin/main. Guardianes en tests/test_guardias_de_la_suite.py para que las afirmaciones no vuelvan a caducar en silencio.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -10052,11 +10228,19 @@
       <c r="I143" s="6" t="inlineStr"/>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K143" s="6" t="inlineStr"/>
-      <c r="L143" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L143" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Los asserts se convierten a pytest.approx con tolerancia NOMBRADA (tests/apoyo/aproximacion.py: REL_TRANSPORTE para un valor que el pipeline solo transporta, ABS_CERO para la comparacion contra cero, donde la tolerancia relativa no existe). Guardian nuevo tests/test_guardias_de_la_suite.py::test_ningun_assert_compara_floats_con_igualdad_exacta, detector AST propio (==, !=, in, not in; contenedores; negativos; marca '# float-exacto: &lt;razon&gt;'), con su banco de casos y sus limites declarados. CORRECCION A LA FICHA: los 15 son el conteo del grep, que solo ve 'assert &lt;algo&gt; == &lt;literal float&gt;'; el detector AST encuentra ~57 con la definicion ancha, y todos los reales quedaron convertidos.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -10102,11 +10286,19 @@
       <c r="I144" s="6" t="inlineStr"/>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K144" s="6" t="inlineStr"/>
-      <c r="L144" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L144" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — El test que no invocaba codigo de produccion (reescribia la formula y se comparaba consigo mismo) pasa a llamar la funcion real; la autoverificacion de la formula queda donde corresponde, en el bloque __main__ de casos_patron.py. tests/test_M3_hidraulica.py.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -10214,11 +10406,19 @@
       <c r="I146" s="6" t="inlineStr"/>
       <c r="J146" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K146" s="6" t="inlineStr"/>
-      <c r="L146" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L146" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — La pertenencia a NUMEROS_PERMITIDOS se comprueba por TIPO ademas de por valor: un complejo cae siempre, tambien 0j y 2+0j, que se colaban porque son iguales a 0 y a 2. tests/test_sin_literales.py::test_sis_c_08_un_complejo_nunca_esta_permitido.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -10264,11 +10464,19 @@
       <c r="I147" s="6" t="inlineStr"/>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K147" s="6" t="inlineStr"/>
-      <c r="L147" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L147" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Se detectan las conversiones desde texto (int, float, complex, Decimal, Fraction) con argumento literal que parsea como numero: int('500') y float('4.6') dejan de ser invisibles. tests/test_sin_literales.py::test_sis_c_09_*.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -10314,11 +10522,19 @@
       <c r="I148" s="6" t="inlineStr"/>
       <c r="J148" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K148" s="6" t="inlineStr"/>
-      <c r="L148" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L148" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Las plantillas src/plantillas/*.html entran con su propia regla, declarada: fuera de los bloques &lt;style&gt; los unicos numeros admitidos son la numeracion de secciones de la memoria, porque toda magnitud entra por un marcador %%...%% que rellena M11. tests/test_sin_literales.py::test_las_plantillas_no_traen_valores_de_calculo.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -10364,11 +10580,19 @@
       <c r="I149" s="6" t="inlineStr"/>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K149" s="6" t="inlineStr"/>
-      <c r="L149" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L149" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — M11.tableros_pendientes fallaba de forma ruidosa solo ante la perdida TOTAL del bloque; medido, retirar la tabla de un solo Tablero daba 2 tableros / 10 filas en vez de 3 / 15, en silencio. Ahora falla tambien ante la degradacion PARCIAL: una cabecera 'Tablero N' que no produce tabla, o un tablero con cero filas. tests/test_M11_reporte.py.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -10414,11 +10638,19 @@
       <c r="I150" s="6" t="inlineStr"/>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K150" s="6" t="inlineStr"/>
-      <c r="L150" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L150" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — El patron de escribir_valor_en_archivo se ejercita sobre los criterios de VALOR MULTILINEA y su ValueError queda cubierto. CORRECCION A LA FICHA: dice dos criterios de valor multilinea; medidos sobre el arbol de hoy son seis. tests/test_criterios_adoptados.py.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -10464,11 +10696,19 @@
       <c r="I151" s="6" t="inlineStr"/>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K151" s="6" t="inlineStr"/>
-      <c r="L151" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L151" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Las dos ramas de ImportError de MD quedan cubiertas sin borrar el modulo: la primera con un None en el registro, la segunda con un modulo presente que no expone verificar. Cubierta ademas la segunda deuda de la ficha, la resolucion del lote en disenar_lote. El skip permanente sigue siendo uno y sigue documentado. tests/test_MD.py.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -10514,11 +10754,19 @@
       <c r="I152" s="6" t="inlineStr"/>
       <c r="J152" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K152" s="6" t="inlineStr"/>
-      <c r="L152" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L152" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — El borde de TOL_UMBRAL_NORMATIVO en _verificacion_por_fs se cubre con los tres casos que lo fijan (justo dentro, justo fuera, y el signo de la resta), de modo que invertir el signo de la tolerancia ya no deja la suite verde. tests/test_M9_cabezal.py.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -11698,11 +11946,19 @@
       <c r="I174" s="6" t="inlineStr"/>
       <c r="J174" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K174" s="6" t="inlineStr"/>
-      <c r="L174" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K174" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L174" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — cli._bloqueo dejaba de resolver toda clave con ca.criterio(): un [S] de corredor pendiente salia como KeyError, fallo de programa. Se anade criterios_adoptados.declaracion_de(clave), que resuelve indistintamente un criterio o un dato de sitio y devuelve la declaracion, y _bloqueo la consume. tests/test_cli.py.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -11922,11 +12178,19 @@
       <c r="I178" s="6" t="inlineStr"/>
       <c r="J178" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K178" s="6" t="inlineStr"/>
-      <c r="L178" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L178" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — El diagnostico de Familia C que MD escribio es inalcanzable desde el CSV porque gana antes DatoFaltanteError('Q_m3s'): el hecho se fija con la fila C-01 del CSV de ejemplo y la rama se alcanza llamando _motivo_sin_candidatos directamente, con la razon de por que se hace asi escrita en el test. tests/test_MD.py.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -12620,11 +12884,19 @@
       <c r="I191" s="6" t="inlineStr"/>
       <c r="J191" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K191" s="6" t="inlineStr"/>
-      <c r="L191" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L191" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Los DatoInvalidoError que validan strings producidos por el propio codigo quedan declarados en M9_cabezal.py con la razon de por que la taxonomia del expediente es aqui la eleccion correcta y no un fallo de programa disfrazado. El quinto sitio que la ficha listaba, _recubrimiento_aashto_detallado, ya no existe.</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -12670,11 +12942,19 @@
       <c r="I192" s="6" t="inlineStr"/>
       <c r="J192" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K192" s="6" t="inlineStr"/>
-      <c r="L192" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L192" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — tr_desde_riesgo comprueba el DENOMINADOR antes de dividir y lanza DatoInvalidoError('R'): con R suficientemente pequeno (1-R)^(1/n) redondea a 1.0 y el ZeroDivisionError quedaba fuera de la taxonomia ErrorProyecto. Se comprueba el denominador, y en forma POSITIVA (if not denominador &gt; 0) para que nan tambien caiga, en vez de un umbral sobre R: el limite depende de n (R ~ n*eps/4, medido 1.39e-15 para n=25) y un umbral seria un literal de precision disfrazado de valor normativo. El mensaje nombra CRITERIO_RIESGO_PROPIETARIO, que es donde el revisor corrige. tests/test_M1_clasificacion.py.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -12720,11 +13000,19 @@
       <c r="I193" s="6" t="inlineStr"/>
       <c r="J193" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K193" s="6" t="inlineStr"/>
-      <c r="L193" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L193" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — _a_float exige math.isfinite y lanza DatoInvalidoError: 'inf' pasa toda cota inferior y 'nan' es falso frente a &lt;= y a &gt;= a la vez, de modo que ninguna validacion de rango los atrapaba y el dato salia a la memoria como un numero que no lo es. Medido: inf SI se colaba por ocho columnas; nan no, y solo por suerte de redaccion. Se cierra ademas la simetria en criterios_adoptados y datos_sitio (_verificar_finitud, primero en el orden y absorbiendo OverflowError del entero enorme) y la via cli.py --declarar CLAVE=nan, que era el agujero mas grave: 'nan' e 'inf' son NOMBRES y no literales, ast.literal_eval los rechazaba y el respaldo de cadena guardaba el STRING por debajo de la guarda; M9_cabezal.cuantia_de_diseno hacia float() sobre el y la memoria salia con cuantia_adoptada = nan. tests/test_M0_carga.py, tests/test_cli.py, tests/test_criterios_adoptados.py, tests/test_datos_sitio.py.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -12770,11 +13058,19 @@
       <c r="I194" s="6" t="inlineStr"/>
       <c r="J194" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K194" s="6" t="inlineStr"/>
-      <c r="L194" s="6" t="inlineStr"/>
+          <t>Cerrado parcial</t>
+        </is>
+      </c>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L194" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — PARCIAL. Se corrige el contrato de None de M3.tirante_normal, que mentia: None es CONSERVADOR, no literal; para D=0.90, S=0.005, n=0.013 se mide Q_pico=1.377 y Q_lleno=1.280, y en esa banda SI existe theta. Se declara ademas la asintota no acotada de M7.factor_esviaje. CORRECCION A LA FICHA: clasifica esos bordes como no alcanzables desde un CSV validado y DOS DE ELLOS SI LO SON -- esviaje ~89.999999 grados (factor 5.73e10) y la banda de None de M3. Queda fuera de este cierre la parte de R^(4/3) que la ficha lista aparte.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
@@ -13098,11 +13394,19 @@
       <c r="I200" s="6" t="inlineStr"/>
       <c r="J200" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K200" s="6" t="inlineStr"/>
-      <c r="L200" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L200" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Las dos validaciones cruzadas que no son fila de la tabla de Sec. 1.5 -- diametro implicito y entrega por gravedad -- quedan declaradas en su punto de uso, en un bloque de M0_carga.py que dice que no vienen de la tabla y por que se aplican igual.</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
@@ -14012,11 +14316,19 @@
       <c r="I217" s="6" t="inlineStr"/>
       <c r="J217" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K217" s="6" t="inlineStr"/>
-      <c r="L217" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K217" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L217" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Las dos guardas provablemente inalcanzables (tabla de resguardo exhaustiva en M5.resguardo_por_cbr; esviaje negativo que M0 ya rechaza en M7.factor_esviaje) se cierran como corresponde a una guarda defensiva: no por inyeccion, sino con la DEMOSTRACION de que el dominio que M0 admite cae entero dentro del que la funcion admite, escrita en el test. Igual para la segunda guarda de M1._categoria. tests/test_M1_clasificacion.py, tests/test_M5_verificaciones.py, tests/test_M7_geometria.py.</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -14228,11 +14540,19 @@
       <c r="I221" s="6" t="inlineStr"/>
       <c r="J221" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K221" s="6" t="inlineStr"/>
-      <c r="L221" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K221" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L221" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Los exportadores separan (OSError, ErrorProyecto) -- que el proyectista corrige y salen sin traza -- del fallo de programa, que imprime traceback.print_exc() como ya hacia el patron hermano de ejecutar_pipeline. CORRECCION A LA FICHA: dice tres exportadores; son CUATRO -- exportar_json estaba sin tocar y tambien se corrigio. tests/test_gui_contrato.py, con guardianes AST que impiden except BaseException, que revisan TODOS los brazos y no solo el primero, y que exigen print_exc como sentencia directa del cuerpo.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -14278,11 +14598,19 @@
       <c r="I222" s="6" t="inlineStr"/>
       <c r="J222" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K222" s="6" t="inlineStr"/>
-      <c r="L222" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K222" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L222" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — El unico raise de la GUI valida un campo TECLEADO por el usuario y se atrapa tres lineas mas abajo: es deliberado y no sale de la clase. Queda declarado en el docstring de _interpretar_valor_declarado y fijado por test, para que estrechar el brazo de captura no lo convierta en una traza. tests/test_gui_contrato.py.</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -14328,11 +14656,19 @@
       <c r="I223" s="6" t="inlineStr"/>
       <c r="J223" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K223" s="6" t="inlineStr"/>
-      <c r="L223" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K223" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L223" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — establecer_valor_dinamico rechaza con ValueError, fuera de ErrorProyecto, y el docstring argumenta por que: CLAUDE.md define DatoInvalidoError para el dato del EXPEDIENTE, y una declaracion tecleada en la GUI no es un dato del expediente sino una entrada de interfaz que su propio manejador atrapa. tests/test_criterios_adoptados.py fija el contrato en los dos sentidos.</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
@@ -14378,11 +14714,19 @@
       <c r="I224" s="6" t="inlineStr"/>
       <c r="J224" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K224" s="6" t="inlineStr"/>
-      <c r="L224" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K224" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16)</t>
+        </is>
+      </c>
+      <c r="L224" s="6" t="inlineStr">
+        <is>
+          <t>52c11d2 — Lo que faltaba era la actualizacion de la CONSTITUCION, como decia la propia ficha: CLAUDE.md ensancha la clausula de DatoFaltanteError para cubrir el dato que no viene del CSV (tablero externo), que es lo que modelos.py ya declaraba y el codigo ya explotaba. tests/test_criterios_adoptados.py.</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -669,6 +669,34 @@
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Claude.md: cuando el código y la hoja de ruta discrepan, el defecto se reporta contra la hoja de ruta primero y la fuente primaria decide quién tiene razón. Por eso la Fase 2 (documentos y citas) va antes que casi todo el código: si corrige el código primero, deja la hoja de ruta contradiciéndolo y el siguiente revisor deshace su trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Cómo se leen los conteos de este archivo (nota de S16.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Los números de la columna «Hallazgos» de la hoja Plan_Fases —y los de la §10 del documento hoja_de_ruta_correcciones_v12.md— son ESTIMACIONES PREVIAS A EJECUTAR. Se calcularon antes de la primera sesión y no se actualizan solos. EL CONTEO QUE MANDA ES EL «Estado» VIVO DE LA HOJA «Hallazgos»: cualquier otra cifra de este archivo es orientativa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>La columna «Clusters» de Plan_Fases se lee distinto según la fase. En una fase YA EJECUTADA es histórica: dice qué se atacó entonces. En una fase PENDIENTE es una lista de quién-reclama-qué-residuo, no un alcance completo: un cluster puede figurar ahí con el 90 % de sus filas ya cerradas, sólo porque le queda un «Cerrado parcial» que ninguna otra fase reclamaría. Que un cluster aparezca en dos o tres fases NO es un defecto: es el diseño de la hoja (8 de los 14 lo hacen), porque un cluster se corrige por capas y cada capa entra donde le toca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Por qué se añadió esta nota: F4 decía 33 y su alcance real (C09+C10) era 48, porque el 33 contaba filas por la columna «Fase» y no por los clusters que la propia fila F4 lista. Y 6 de las 7 filas en «Cerrado parcial» tenían como únicas fases F1/F3/F4 —todas ya ejecutadas—, de modo que ninguna fase futura las reclamaba: se añadieron C01, C06 y C09 a la fila F5 para que ese residuo sea visible para quien lea la hoja por cluster y no por prosa.</t>
         </is>
       </c>
     </row>
@@ -1493,8 +1521,10 @@
           <t>C09 C10</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
-        <v>33</v>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>48 (alcance C09+C10 en S16; el 33 anterior solo contaba las filas con Fase=F4, que subestimaba C09). Historico: F4 ya corrio</t>
+        </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -1520,11 +1550,13 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>C04 C05 C07 C10 C11 C12 C14</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>73</v>
+          <t>C04 C05 C07 C10 C11 C12 C14 + residuos de C01 C06 C09</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ver Hallazgos: Estado='Pendiente' (hoy 15, todos C14 salvo SIS-G-03) + 6 residuos de C01/C06/C09 reclamados aqui. El 73 original y cualquier suma por cluster completo sobreestiman: la mayoria de C04/C05/C07/C10/C11/C12 ya esta cerrada</t>
+        </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -1867,7 +1899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L235"/>
+  <dimension ref="A1:L238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10060,7 +10092,11 @@
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 — PARCIAL. El fixture gana CP-9 y con el pasan a consumir caso patron M7 (CP9_GEOMETRIA_7B) y M9 (CP9_MONONOBE_OKABE, CP9_RANKINE_LIMITE, CP9_EMPUJE_TRASDOS). SIGUEN SIN CASO PATRON M2, M8 y M10: para esos el fixture no da dorados y fabricarlos aqui seria inventar el valor de referencia, que es justo lo que el conflicto n.7 (CP-1 dorados / SIS-F-14) prohibe. Queda declarado como deuda abierta.</t>
+          <t>52c11d2 — PARCIAL. El fixture gana CP-9 y con el pasan a consumir caso patron M7 (CP9_GEOMETRIA_7B) y M9 (CP9_MONONOBE_OKABE, CP9_RANKINE_LIMITE, CP9_EMPUJE_TRASDOS). SIGUEN SIN CASO PATRON M2, M8 y M10: para esos el fixture no da dorados y fabricarlos aqui seria inventar el valor de referencia, que es justo lo que el conflicto n.7 (CP-1 dorados / SIS-F-14) prohibe. Queda declarado como deuda abierta.
+PRECISADO EN S16.5 (fase1) — pendiente de SHA (sin correccion de codigo; la frontera se describia de menos). Hoy son CINCO los tests que no importan casos_patron, no tres, y por TRES razones distintas que no se pueden contar juntas -- docs/linea_base.md ya avisaba en S1 que 'el grep real da 7 modulos, verificar alcance exacto en la fase de correccion':
+  * M2, M8, M10 — no hay dorado que traer sin violar el conflicto n.7. Es la unica deuda de las tres. QUE HARIA FALTA TRAER a cada uno queda escrito en la §15 del plan (hoja_de_ruta_correcciones_v12.md), con la fuente concreta: series de diametros nominales de las normas de producto para M2; AASHTO M 170M Tablas 1-5 y ASTM A796/A796M para M8; y para M10 no una norma sino el expediente vial (seccion de cuneta, su n, la intensidad de TR=35 y el metodo de area tributaria), porque su brazo normativo ya es [N] y un caso patron sobre el seria tautologico.
+  * M5 — NO es deuda de dorado: el fixture SI define su caso (CP3_VELOCIDAD_MINIMA, Sec. 5.2), pero lo consumen test_M3 y test_constantes_normativas en vez de test_M5.
+  * M11 — modulo de reporte, no de calculo: no le corresponde dorado numerico.</t>
         </is>
       </c>
     </row>
@@ -13055,20 +13091,29 @@
           <t>Bordes de funciones públicas: el contrato None de M3 miente en la banda (Q_lleno, Q_pico) — conservador; R^(4/3) underflow (R≤~1e-243) y q\*² overflow (Q≥~1.3e154) como fallos de programa solo alcanzables inyectando; M7 acepta S=0/negativa explícita y esviaje→90° produce factores astronómicos sin cota de cordura; las guardas de M-O nunca capturan ψ=90 exacto (cos=6.1e-17) y un φ absurdo &gt; ψ devuelve K_AE≈1.9e17 en silencio (φ sin validación de rango). Ninguno alcanzable desde el CSV validado</t>
         </is>
       </c>
-      <c r="I194" s="6" t="inlineStr"/>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>SIS-G-01, SIS-G-02</t>
+        </is>
+      </c>
       <c r="J194" s="6" t="inlineStr">
         <is>
-          <t>Cerrado parcial</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K194" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S16)</t>
+          <t>Claude Code (fase1, S16 + S16.5)</t>
         </is>
       </c>
       <c r="L194" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 — PARCIAL. Se corrige el contrato de None de M3.tirante_normal, que mentia: None es CONSERVADOR, no literal; para D=0.90, S=0.005, n=0.013 se mide Q_pico=1.377 y Q_lleno=1.280, y en esa banda SI existe theta. Se declara ademas la asintota no acotada de M7.factor_esviaje. CORRECCION A LA FICHA: clasifica esos bordes como no alcanzables desde un CSV validado y DOS DE ELLOS SI LO SON -- esviaje ~89.999999 grados (factor 5.73e10) y la banda de None de M3. Queda fuera de este cierre la parte de R^(4/3) que la ficha lista aparte.</t>
+          <t>52c11d2 (S16, parcial) + S16.5 (fase1) — pendiente de SHA (cierre). S16 corrigio el contrato de None de M3.tirante_normal y declaro la asintota de M7.factor_esviaje, y ya habia refutado la afirmacion de la ficha de que 'ninguno es alcanzable desde el CSV validado' en DOS de sus clausulas. S16.5 remide las CUATRO restantes, ninguna heredada:
+(1) R^(4/3) underflow (R&lt;=~1e-243): NO ALCANZABLE, con dos barreras independientes medidas. (a) Ningun Q en 325 decadas atraviesa tirante_critico con D=1e-243. (b) Aun inyectando `critico` a mano para saltarse esa guardia, control_salida revienta ANTES en _geometria_de_referencia (Q/A), porque A=pi*D^2/4 subdesborda 81 ordenes de magnitud antes que R^(4/3). Solo se alcanza llamando perdida_carga directamente con un R que no viene de ningun D. Se declara sin guardia.
+(2) q*^2 overflow (Q&gt;=~1.3e154): SI ALCANZABLE, Y LA FICHA LO ANCLA MAL. No esta en q*: esta en `Q ** 2` de _residuo_critico. Q_m3s no tiene techo en dominios.py, de modo que Q=1e155 llega entero desde un CSV valido y float.__pow__ lanza OverflowError CRUDO (Q=1e154 todavia cae como DatoInvalidoError por la guardia de bracket). CERRADO con guardia + test, con LimiteNumericoError. TERCERA correccion a la ficha.
+(3) 'las guardas de M-O nunca capturan psi=90 exacto': REFUTADA. k_v=1.0 da psi=90.0 y hoy dispara DisenoNoFactibleError.
+(4) 'un phi absurdo &gt; psi devuelve K_AE~1.9e17 en silencio': REFUTADA. Medido phi=34 -&gt; 0.745, phi=89 -&gt; 0.0672, phi=89.999 -&gt; 0.0625. No hay explosion.
+(5) 'M7 acepta S=0/negativa explicita': CONFIRMADA como DELIBERADA, no defecto. cota_salida recibe S por argumento y su docstring declara (MAT-D9) que es una identidad geometrica sobre la pendiente que reciba; el unico camino de produccion es S_cauce, que M0 valida 0 &lt; S &lt; 1.</t>
         </is>
       </c>
     </row>
@@ -14266,11 +14311,22 @@
       <c r="I216" s="6" t="inlineStr"/>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K216" s="6" t="inlineStr"/>
-      <c r="L216" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K216" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16.5)</t>
+        </is>
+      </c>
+      <c r="L216" s="6" t="inlineStr">
+        <is>
+          <t>S16.5 (fase1) — pendiente de SHA. LAS DOS AFIRMACIONES DE LA FICHA VERIFICADAS CONTRA EL CODIGO DE HOY, y la segunda se sostiene con MAS fuerza que cuando se escribio:
+(a) aplica_sobrecarga_trasdos SI declara su motivo en su docstring, y ademas ya figura en M9.FUNCIONES_SIN_CONSUMIDOR con su razon escrita. Nada que hacer.
+(b) la acusacion sobre v_max_definida es falsa, y hoy mas: el simbolo en que se apoyaba, Material.v_max_rango, YA NO EXISTE en el repositorio (retirado al cerrar SIS-A-06). No hay nada que reimplementar porque no hay que reimplementar.
+Quedaban las DOS utilidades sin llamador de produccion, y se cierran escribiendo su decision en el docstring de cada una -- mismo tratamiento que la ficha ya acepto para aplica_sobrecarga_trasdos, y donde el revisor la busca: criterios_adoptados.limpiar_valores_dinamicos (una corrida de la CLI es un proceso de un solo uso y no necesita borrar todo; la GUI retira UNA clave; el consumidor real es conftest.py, que la nombra al explicar su fixture autouse) y M11_reporte.marcadores_de_la_memoria (puerta publica del contrato de la plantilla, para no atar a un consumidor externo al nombre de la constante MARCADORES). NO se crean dos registros FUNCIONES_SIN_CONSUMIDOR nuevos de una entrada cada uno.</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -15285,6 +15341,190 @@
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="inlineStr">
+        <is>
+          <t>SIS-G-01</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="G236" s="6" t="inlineStr">
+        <is>
+          <t>src/modulos/M7_geometria.py::proyeccion_taludes, longitud_conducto, altura_terraplen, cota_salida</t>
+        </is>
+      </c>
+      <c r="H236" s="6" t="inlineStr">
+        <is>
+          <t>Overflow aritmetico a la salida de 7.B: entradas finitas y validas producen inf, que el informe imprime como "valor": "inf". Una cota_rasante = 1e308 pasa _a_float, _valida_rangos y _valida_cruzadas porque NINGUNA cota tiene techo en dominios.py (ponerselo seria inventar un valor de proyecto). La guardia de ENTRADA (criterios_adoptados._verificar_finitud, MAT-D14) no puede cerrarlo: no es un dato no finito que entra, es una multiplicacion finita que desborda  [defecto real]</t>
+        </is>
+      </c>
+      <c r="I236" s="6" t="inlineStr">
+        <is>
+          <t>SIS-G-02, MAT-O18, MAT-D14</t>
+        </is>
+      </c>
+      <c r="J236" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K236" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16.5)</t>
+        </is>
+      </c>
+      <c r="L236" s="6" t="inlineStr">
+        <is>
+          <t>S16.5 (fase1) — pendiente de SHA. Declarado por S16 en el docstring de _verificar_finitud sin ID y sin cerrar; S16.5 lo da de alta y lo cierra. Guardia a la SALIDA de M7 (_exigir_finito), no a la entrada de dominios.py. Excepcion: modelos.LimiteNumericoError, quinta de la taxonomia (NO DatoInvalidoError: el dato cumple su rango, es la aritmetica la que no cabe). MEDIDO: cota_rasante=1e308 -&gt; altura_terraplen finita 1e308, proyeccion_taludes=inf. Barrido previo de los inf legitimos: son DOS (M9.verificar_volteo y M9.verificar_deslizamiento), la guardia vive solo en M7 y un test fija el censo. CLAUDE.md enmendada de cuatro excepciones a cinco</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>SIS-G-02</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>G-02</t>
+        </is>
+      </c>
+      <c r="D237" s="7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E237" s="6" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="F237" s="6" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="G237" s="6" t="inlineStr">
+        <is>
+          <t>src/modulos/M4_control.py::tirante_critico (la division V_c = Q / geom.A posterior a brentq)</t>
+        </is>
+      </c>
+      <c r="H237" s="6" t="inlineStr">
+        <is>
+          <t>La guardia de tirante_critico protege el BRACKET de Brent, no la division de despues. Con un Q diminuto el residuo cruza el cero, brentq converge, y el theta al que converge cae bajo el umbral en que el area se cancela: V_c = Q/geom.A lanzaba ZeroDivisionError CRUDO, fuera de ErrorProyecto, de modo que la GUI no podia distinguir problema del expediente de fallo del programa  [defecto real]</t>
+        </is>
+      </c>
+      <c r="I237" s="6" t="inlineStr">
+        <is>
+          <t>SIS-G-01, MAT-O18, MAT-D13</t>
+        </is>
+      </c>
+      <c r="J237" s="6" t="inlineStr">
+        <is>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K237" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S16.5)</t>
+        </is>
+      </c>
+      <c r="L237" s="6" t="inlineStr">
+        <is>
+          <t>S16.5 (fase1) — pendiente de SHA. Hallado al remedir MAT-O18. MEDIDO con D=0.90 m y CERO criterios declarados de mas: Q=1e-32 resuelve (theta=2.979e-08, area positiva), Q=1e-33 revienta. Umbral real: A=(D^2/8)(theta - sen theta) vale exactamente 0.0 desde theta&lt;=2.149e-08, porque theta-sen(theta)~theta^3/6 cae bajo el ultimo bit de theta. IRONIA UTIL: _residuo_critico YA esquiva esta misma cancelacion a proposito (por eso escribe A^3/T y no divide entre A^3) -- la defensa estaba en el residuo y faltaba tras el solver. Guardia con la FORMA de MAT-D13 (umbral medido, `not geom.A &gt; 0` en positivo para atrapar NaN, mensaje que nombra el par (Q,D)) y clase LimiteNumericoError</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>SIS-G-03</t>
+        </is>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>Sistema</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="n"/>
+      <c r="F238" s="6" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="G238" s="6" t="inlineStr">
+        <is>
+          <t>docs/manifiesto_citas.md (filas de NF_profundidad_m y de SECCION_EG2013); tests/test_manifiesto_citas.py::test_ninguna_referencia_aterriza_en_una_linea_vacia</t>
+        </is>
+      </c>
+      <c r="H238" s="6" t="inlineStr">
+        <is>
+          <t>Referencias DE PROSA del manifiesto apuntando a lineas equivocadas desde ANTES de S16.5, sin que ninguna guardia lo vea. NO ES UN CASO AISLADO: se encontraron DOS de forma independiente, y ninguna de las dos se buscaba.
+  * La fila de NF_profundidad_m citaba [modelos.py:359]; en el origin/main de esa fecha la linea 359 decia HIDRAULICO = "hidraulico" (capacidad admisible de la cuneta), sin relacion con el campo. La prosa que si lo describe vivia en :410. Desviada 51 lineas.
+  * La fila de SECCION_EG2013 citaba [M11:721]; en ese mismo origin/main la linea 721 era un comentario sobre el prefijo 'num.' de NUMERAL_TR. El unico sitio de M11 que toca seccion_eg2013 era la :783. Desviada 62 lineas.
+EL HUECO ES DEL TEST, no solo de las citas: para las referencias que no se pueden anclar a un simbolo (69 de 326, dentro del cupo que test_T9 ya raciona) las unicas comprobaciones de destino son que el archivo exista, que la linea este en rango y que NO ESTE EN BLANCO. Una linea con contenido EQUIVOCADO pasa en verde. Las dos encontradas salieron por casualidad -- porque una insercion de S16.5 las movio a una linea vacia y el test las delato por el otro motivo --, de modo que la tasa real entre las 67 restantes es DESCONOCIDA y no hay razon para suponerla cero  [defecto real]</t>
+        </is>
+      </c>
+      <c r="I238" s="6" t="inlineStr">
+        <is>
+          <t>NOR-MAN-04, SIS-G-01</t>
+        </is>
+      </c>
+      <c r="J238" s="6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K238" s="6" t="n"/>
+      <c r="L238" s="6" t="inlineStr">
+        <is>
+          <t>DECLARADO, NO CERRADO, a proposito. S16.5 corrigio las DOS citas concretas -- modelos.py :359 -&gt; :481 y M11 :721 -&gt; :799, ambas verificadas LEYENDO la linea de destino y no restando el desplazamiento -- porque sus propias inserciones las movian de todos modos. Pero NO arregla el hueco del test en el mismo commit: eso es un cambio de diseño de la guardia y merece su propia sesion, con un barrido de las 67 restantes.
+LO QUE HARIA FALTA, en orden de preferencia: (1) anclar la fila a un simbolo y sacarla del cupo de test_T9, que es la cura que NOR-MAN-04 ya prescribe y que el resincronizador (python3 -m src.normativa.manifiesto --escribir) mantiene solo; o (2) donde no haya simbolo que anclar, que la fila declare un FRAGMENTO LITERAL del texto que espera encontrar en su destino, para que el test compare contenido y no solo 'no esta en blanco'.
+Sin cluster asignado: no encaja en C09 (tests de calculo) ni en C11 (citas normativas contra PDF); es la guardia del manifiesto, que es un tercer objeto.
+Severidad MEDIA y no MENOR: el manifiesto es el mapa por el que un revisor llega al codigo, y una cita que aterriza en otra cosa lo manda a leer el simbolo equivocado creyendo que leyo el correcto.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L235"/>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -10093,7 +10093,7 @@
       <c r="L140" s="6" t="inlineStr">
         <is>
           <t>52c11d2 — PARCIAL. El fixture gana CP-9 y con el pasan a consumir caso patron M7 (CP9_GEOMETRIA_7B) y M9 (CP9_MONONOBE_OKABE, CP9_RANKINE_LIMITE, CP9_EMPUJE_TRASDOS). SIGUEN SIN CASO PATRON M2, M8 y M10: para esos el fixture no da dorados y fabricarlos aqui seria inventar el valor de referencia, que es justo lo que el conflicto n.7 (CP-1 dorados / SIS-F-14) prohibe. Queda declarado como deuda abierta.
-PRECISADO EN S16.5 (fase1) — pendiente de SHA (sin correccion de codigo; la frontera se describia de menos). Hoy son CINCO los tests que no importan casos_patron, no tres, y por TRES razones distintas que no se pueden contar juntas -- docs/linea_base.md ya avisaba en S1 que 'el grep real da 7 modulos, verificar alcance exacto en la fase de correccion':
+PRECISADO EN 96084e8 (fase1, S16.5) (sin correccion de codigo; la frontera se describia de menos). Hoy son CINCO los tests que no importan casos_patron, no tres, y por TRES razones distintas que no se pueden contar juntas -- docs/linea_base.md ya avisaba en S1 que 'el grep real da 7 modulos, verificar alcance exacto en la fase de correccion':
   * M2, M8, M10 — no hay dorado que traer sin violar el conflicto n.7. Es la unica deuda de las tres. QUE HARIA FALTA TRAER a cada uno queda escrito en la §15 del plan (hoja_de_ruta_correcciones_v12.md), con la fuente concreta: series de diametros nominales de las normas de producto para M2; AASHTO M 170M Tablas 1-5 y ASTM A796/A796M para M8; y para M10 no una norma sino el expediente vial (seccion de cuneta, su n, la intensidad de TR=35 y el metodo de area tributaria), porque su brazo normativo ya es [N] y un caso patron sobre el seria tautologico.
   * M5 — NO es deuda de dorado: el fixture SI define su caso (CP3_VELOCIDAD_MINIMA, Sec. 5.2), pero lo consumen test_M3 y test_constantes_normativas en vez de test_M5.
   * M11 — modulo de reporte, no de calculo: no le corresponde dorado numerico.</t>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="L194" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 (S16, parcial) + S16.5 (fase1) — pendiente de SHA (cierre). S16 corrigio el contrato de None de M3.tirante_normal y declaro la asintota de M7.factor_esviaje, y ya habia refutado la afirmacion de la ficha de que 'ninguno es alcanzable desde el CSV validado' en DOS de sus clausulas. S16.5 remide las CUATRO restantes, ninguna heredada:
+          <t>52c11d2 (S16, parcial) + 96084e8 (fase1, S16.5) (cierre). S16 corrigio el contrato de None de M3.tirante_normal y declaro la asintota de M7.factor_esviaje, y ya habia refutado la afirmacion de la ficha de que 'ninguno es alcanzable desde el CSV validado' en DOS de sus clausulas. S16.5 remide las CUATRO restantes, ninguna heredada:
 (1) R^(4/3) underflow (R&lt;=~1e-243): NO ALCANZABLE, con dos barreras independientes medidas. (a) Ningun Q en 325 decadas atraviesa tirante_critico con D=1e-243. (b) Aun inyectando `critico` a mano para saltarse esa guardia, control_salida revienta ANTES en _geometria_de_referencia (Q/A), porque A=pi*D^2/4 subdesborda 81 ordenes de magnitud antes que R^(4/3). Solo se alcanza llamando perdida_carga directamente con un R que no viene de ningun D. Se declara sin guardia.
 (2) q*^2 overflow (Q&gt;=~1.3e154): SI ALCANZABLE, Y LA FICHA LO ANCLA MAL. No esta en q*: esta en `Q ** 2` de _residuo_critico. Q_m3s no tiene techo en dominios.py, de modo que Q=1e155 llega entero desde un CSV valido y float.__pow__ lanza OverflowError CRUDO (Q=1e154 todavia cae como DatoInvalidoError por la guardia de bracket). CERRADO con guardia + test, con LimiteNumericoError. TERCERA correccion a la ficha.
 (3) 'las guardas de M-O nunca capturan psi=90 exacto': REFUTADA. k_v=1.0 da psi=90.0 y hoy dispara DisenoNoFactibleError.
@@ -14321,7 +14321,7 @@
       </c>
       <c r="L216" s="6" t="inlineStr">
         <is>
-          <t>S16.5 (fase1) — pendiente de SHA. LAS DOS AFIRMACIONES DE LA FICHA VERIFICADAS CONTRA EL CODIGO DE HOY, y la segunda se sostiene con MAS fuerza que cuando se escribio:
+          <t>96084e8 (fase1, S16.5). LAS DOS AFIRMACIONES DE LA FICHA VERIFICADAS CONTRA EL CODIGO DE HOY, y la segunda se sostiene con MAS fuerza que cuando se escribio:
 (a) aplica_sobrecarga_trasdos SI declara su motivo en su docstring, y ademas ya figura en M9.FUNCIONES_SIN_CONSUMIDOR con su razon escrita. Nada que hacer.
 (b) la acusacion sobre v_max_definida es falsa, y hoy mas: el simbolo en que se apoyaba, Material.v_max_rango, YA NO EXISTE en el repositorio (retirado al cerrar SIS-A-06). No hay nada que reimplementar porque no hay que reimplementar.
 Quedaban las DOS utilidades sin llamador de produccion, y se cierran escribiendo su decision en el docstring de cada una -- mismo tratamiento que la ficha ya acepto para aplica_sobrecarga_trasdos, y donde el revisor la busca: criterios_adoptados.limpiar_valores_dinamicos (una corrida de la CLI es un proceso de un solo uso y no necesita borrar todo; la GUI retira UNA clave; el consumidor real es conftest.py, que la nombra al explicar su fixture autouse) y M11_reporte.marcadores_de_la_memoria (puerta publica del contrato de la plantilla, para no atar a un consumidor externo al nombre de la constante MARCADORES). NO se crean dos registros FUNCIONES_SIN_CONSUMIDOR nuevos de una entrada cada uno.</t>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="L236" s="6" t="inlineStr">
         <is>
-          <t>S16.5 (fase1) — pendiente de SHA. Declarado por S16 en el docstring de _verificar_finitud sin ID y sin cerrar; S16.5 lo da de alta y lo cierra. Guardia a la SALIDA de M7 (_exigir_finito), no a la entrada de dominios.py. Excepcion: modelos.LimiteNumericoError, quinta de la taxonomia (NO DatoInvalidoError: el dato cumple su rango, es la aritmetica la que no cabe). MEDIDO: cota_rasante=1e308 -&gt; altura_terraplen finita 1e308, proyeccion_taludes=inf. Barrido previo de los inf legitimos: son DOS (M9.verificar_volteo y M9.verificar_deslizamiento), la guardia vive solo en M7 y un test fija el censo. CLAUDE.md enmendada de cuatro excepciones a cinco</t>
+          <t>96084e8 (fase1, S16.5). Declarado por S16 en el docstring de _verificar_finitud sin ID y sin cerrar; S16.5 lo da de alta y lo cierra. Guardia a la SALIDA de M7 (_exigir_finito), no a la entrada de dominios.py. Excepcion: modelos.LimiteNumericoError, quinta de la taxonomia (NO DatoInvalidoError: el dato cumple su rango, es la aritmetica la que no cabe). MEDIDO: cota_rasante=1e308 -&gt; altura_terraplen finita 1e308, proyeccion_taludes=inf. Barrido previo de los inf legitimos: son DOS (M9.verificar_volteo y M9.verificar_deslizamiento), la guardia vive solo en M7 y un test fija el censo. CLAUDE.md enmendada de cuatro excepciones a cinco</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="L237" s="6" t="inlineStr">
         <is>
-          <t>S16.5 (fase1) — pendiente de SHA. Hallado al remedir MAT-O18. MEDIDO con D=0.90 m y CERO criterios declarados de mas: Q=1e-32 resuelve (theta=2.979e-08, area positiva), Q=1e-33 revienta. Umbral real: A=(D^2/8)(theta - sen theta) vale exactamente 0.0 desde theta&lt;=2.149e-08, porque theta-sen(theta)~theta^3/6 cae bajo el ultimo bit de theta. IRONIA UTIL: _residuo_critico YA esquiva esta misma cancelacion a proposito (por eso escribe A^3/T y no divide entre A^3) -- la defensa estaba en el residuo y faltaba tras el solver. Guardia con la FORMA de MAT-D13 (umbral medido, `not geom.A &gt; 0` en positivo para atrapar NaN, mensaje que nombra el par (Q,D)) y clase LimiteNumericoError</t>
+          <t>96084e8 (fase1, S16.5). Hallado al remedir MAT-O18. MEDIDO con D=0.90 m y CERO criterios declarados de mas: Q=1e-32 resuelve (theta=2.979e-08, area positiva), Q=1e-33 revienta. Umbral real: A=(D^2/8)(theta - sen theta) vale exactamente 0.0 desde theta&lt;=2.149e-08, porque theta-sen(theta)~theta^3/6 cae bajo el ultimo bit de theta. IRONIA UTIL: _residuo_critico YA esquiva esta misma cancelacion a proposito (por eso escribe A^3/T y no divide entre A^3) -- la defensa estaba en el residuo y faltaba tras el solver. Guardia con la FORMA de MAT-D13 (umbral medido, `not geom.A &gt; 0` en positivo para atrapar NaN, mensaje que nombra el par (Q,D)) y clase LimiteNumericoError</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -8981,12 +8981,12 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S16)</t>
+          <t>Claude Code (fase1, S16 + S17)</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets.</t>
+          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets. || S17 (5ec63ae) — sigue PARCIAL y avanza mucho: la funcionalidad nueva de la GUI nace con 86 tests ejecutables (47 de contenido de la ventana, 33 del camino de declaracion, 6 de contrato) y con la comprobacion DE PUNTA A PUNTA que faltaba: declarar desde la ventana -&gt; pipeline -&gt; la memoria imprime el valor como declarado y con su procedencia. La estrategia que lo hace posible es partir el componente: el CONTENIDO vive en src/ventana_normativa.py y se compara campo a campo sin escritorio; gui/ventana_normativa.py solo cablea widgets. Sigue sin cubrirse el cableado de widgets de gui/app.py anterior a esta sesion.</t>
         </is>
       </c>
     </row>
@@ -12272,11 +12272,19 @@
       <c r="I179" s="6" t="inlineStr"/>
       <c r="J179" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K179" s="6" t="inlineStr"/>
-      <c r="L179" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S17)</t>
+        </is>
+      </c>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>5ec63ae — cerrado de paso al reescribir ese encabezado para SIS-A-17 y SIS-A-18, y en las DOS mitades que la ficha nombra: la lista dice ahora las cuatro pestanas --- incluida la de Criterios, que es la que reescribe criterios_adoptados.py y la que faltaba --- y la de exportaciones nombra el CSV junto a JSON, HTML y PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -13497,11 +13505,19 @@
       <c r="I201" s="6" t="inlineStr"/>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K201" s="6" t="inlineStr"/>
-      <c r="L201" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S17)</t>
+        </is>
+      </c>
+      <c r="L201" s="6" t="inlineStr">
+        <is>
+          <t>5ec63ae — la pestana 1 expone el alcance de la corrida con las constantes ALCANCE_PERFIL/ALCANCE_EXPEDIENTE de cli.py (no dos cadenas escritas otra vez), el valor llega a cli.correr, y las dos exportaciones de memoria eligen plantilla con cli.plantilla_por_alcance --- la MISMA funcion que usa cli.main, para que la misma corrida no de dos memorias segun la puerta. memoria_perfil.html deja de ser inalcanzable desde la interfaz. El resumen anade dos filas: el alcance y el numero de etapas diferidas por el. Comprobado con Tk real bajo Xvfb: la corrida de perfil desde la ventana produce la memoria de perfil. Cuatro tests de contrato en tests/test_gui_contrato.py.</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -13547,11 +13563,19 @@
       <c r="I202" s="6" t="inlineStr"/>
       <c r="J202" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K202" s="6" t="inlineStr"/>
-      <c r="L202" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S17)</t>
+        </is>
+      </c>
+      <c r="L202" s="6" t="inlineStr">
+        <is>
+          <t>5ec63ae — la sesion (formato v2) guarda "alcance" y "criterios", y este ultimo lleva los valores dinamicos Y la procedencia de cada uno. Se restaura por declaracion.restaurar_sesion, que repone con establecer_valor_dinamico --- la misma guardia que el archivo ---, de modo que un JSON editado a mano no es una puerta de atras. Lo que la guardia rechaza NO se descarta en silencio: sale con su motivo en un aviso. Una sesion v1 se sigue leyendo y avisa de lo que no traia (patron de legacy/Tc.py). Tests: round-trip por json en tests/test_declaracion.py y contrato en tests/test_gui_contrato.py.</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets. || S17 (5ec63ae) — sigue PARCIAL y avanza mucho: la funcionalidad nueva de la GUI nace con 86 tests ejecutables (47 de contenido de la ventana, 33 del camino de declaracion, 6 de contrato) y con la comprobacion DE PUNTA A PUNTA que faltaba: declarar desde la ventana -&gt; pipeline -&gt; la memoria imprime el valor como declarado y con su procedencia. La estrategia que lo hace posible es partir el componente: el CONTENIDO vive en src/ventana_normativa.py y se compara campo a campo sin escritorio; gui/ventana_normativa.py solo cablea widgets. Sigue sin cubrirse el cableado de widgets de gui/app.py anterior a esta sesion.</t>
+          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets. || S17 (rama claude/ventanas-emergentes-4-2-4-3-s50kk0, PR ABIERTO Y NO FUSIONADO --- nada de esto esta en main todavia): la funcionalidad nueva de la GUI nace con 86 tests ejecutables (47 de contenido de la ventana, 33 del camino de declaracion, 6 de contrato) y con la comprobacion DE PUNTA A PUNTA que faltaba: declarar desde la ventana -&gt; pipeline -&gt; la memoria imprime el valor como declarado y con su procedencia. La estrategia que lo hace posible es partir el componente: el CONTENIDO vive en src/ventana_normativa.py y se compara campo a campo sin escritorio; gui/ventana_normativa.py solo cablea widgets. Sigue sin cubrirse el cableado de widgets de gui/app.py anterior a esta sesion.</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       <c r="I179" s="6" t="inlineStr"/>
       <c r="J179" s="6" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>PR abierto contra main, NO fusionado</t>
         </is>
       </c>
       <c r="K179" s="6" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L179" s="6" t="inlineStr">
         <is>
-          <t>5ec63ae — cerrado de paso al reescribir ese encabezado para SIS-A-17 y SIS-A-18, y en las DOS mitades que la ficha nombra: la lista dice ahora las cuatro pestanas --- incluida la de Criterios, que es la que reescribe criterios_adoptados.py y la que faltaba --- y la de exportaciones nombra el CSV junto a JSON, HTML y PDF.</t>
+          <t>NO FUSIONADO. El trabajo vive en la rama claude/ventanas-emergentes-4-2-4-3-s50kk0 (HEAD 4bfda57, con el cambio de codigo en su commit padre) y NO esta en main: hay un PR abierto, pendiente de revision. Esta fila NO dice «Cerrado» a proposito, y no cita ningun SHA de main porque no lo hay. Se pasa a «Cerrado», con el SHA de la fusion, cuando el PR se fusione. Cerrado de paso al reescribir el encabezado de gui/app.py para SIS-A-17 y SIS-A-18, y en las DOS mitades que la ficha nombra: la lista dice ahora las cuatro pestanas --- incluida la de Criterios, que es la que reescribe criterios_adoptados.py y la que faltaba --- y la de exportaciones nombra el CSV junto a JSON, HTML y PDF.</t>
         </is>
       </c>
     </row>
@@ -13505,7 +13505,7 @@
       <c r="I201" s="6" t="inlineStr"/>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>PR abierto contra main, NO fusionado</t>
         </is>
       </c>
       <c r="K201" s="6" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="L201" s="6" t="inlineStr">
         <is>
-          <t>5ec63ae — la pestana 1 expone el alcance de la corrida con las constantes ALCANCE_PERFIL/ALCANCE_EXPEDIENTE de cli.py (no dos cadenas escritas otra vez), el valor llega a cli.correr, y las dos exportaciones de memoria eligen plantilla con cli.plantilla_por_alcance --- la MISMA funcion que usa cli.main, para que la misma corrida no de dos memorias segun la puerta. memoria_perfil.html deja de ser inalcanzable desde la interfaz. El resumen anade dos filas: el alcance y el numero de etapas diferidas por el. Comprobado con Tk real bajo Xvfb: la corrida de perfil desde la ventana produce la memoria de perfil. Cuatro tests de contrato en tests/test_gui_contrato.py.</t>
+          <t>NO FUSIONADO. El trabajo vive en la rama claude/ventanas-emergentes-4-2-4-3-s50kk0 (HEAD 4bfda57, con el cambio de codigo en su commit padre) y NO esta en main: hay un PR abierto, pendiente de revision. Esta fila NO dice «Cerrado» a proposito, y no cita ningun SHA de main porque no lo hay. Se pasa a «Cerrado», con el SHA de la fusion, cuando el PR se fusione. La pestana 1 expone el alcance de la corrida con las constantes ALCANCE_PERFIL/ALCANCE_EXPEDIENTE de cli.py (no dos cadenas escritas otra vez), el valor llega a cli.correr, y las dos exportaciones de memoria eligen plantilla con cli.plantilla_por_alcance --- la MISMA funcion que usa cli.main, para que la misma corrida no de dos memorias segun la puerta. memoria_perfil.html deja de ser inalcanzable desde la interfaz. El resumen anade dos filas: el alcance y el numero de etapas diferidas por el. Comprobado con Tk real bajo Xvfb: la corrida de perfil desde la ventana produce la memoria de perfil. Cuatro tests de contrato en tests/test_gui_contrato.py.</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       <c r="I202" s="6" t="inlineStr"/>
       <c r="J202" s="6" t="inlineStr">
         <is>
-          <t>Cerrado</t>
+          <t>PR abierto contra main, NO fusionado</t>
         </is>
       </c>
       <c r="K202" s="6" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="L202" s="6" t="inlineStr">
         <is>
-          <t>5ec63ae — la sesion (formato v2) guarda "alcance" y "criterios", y este ultimo lleva los valores dinamicos Y la procedencia de cada uno. Se restaura por declaracion.restaurar_sesion, que repone con establecer_valor_dinamico --- la misma guardia que el archivo ---, de modo que un JSON editado a mano no es una puerta de atras. Lo que la guardia rechaza NO se descarta en silencio: sale con su motivo en un aviso. Una sesion v1 se sigue leyendo y avisa de lo que no traia (patron de legacy/Tc.py). Tests: round-trip por json en tests/test_declaracion.py y contrato en tests/test_gui_contrato.py.</t>
+          <t>NO FUSIONADO. El trabajo vive en la rama claude/ventanas-emergentes-4-2-4-3-s50kk0 (HEAD 4bfda57, con el cambio de codigo en su commit padre) y NO esta en main: hay un PR abierto, pendiente de revision. Esta fila NO dice «Cerrado» a proposito, y no cita ningun SHA de main porque no lo hay. Se pasa a «Cerrado», con el SHA de la fusion, cuando el PR se fusione. La sesion (formato v2) guarda "alcance" y "criterios", y este ultimo lleva los valores dinamicos Y la procedencia de cada uno. Se restaura por declaracion.restaurar_sesion, que repone con establecer_valor_dinamico --- la misma guardia que el archivo ---, de modo que un JSON editado a mano no es una puerta de atras. Lo que la guardia rechaza NO se descarta en silencio: sale con su motivo en un aviso. Una sesion v1 se sigue leyendo y avisa de lo que no traia (patron de legacy/Tc.py). Tests: round-trip por json en tests/test_declaracion.py y contrato en tests/test_gui_contrato.py.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets. || S17 (rama claude/ventanas-emergentes-4-2-4-3-s50kk0, PR ABIERTO Y NO FUSIONADO --- nada de esto esta en main todavia): la funcionalidad nueva de la GUI nace con 86 tests ejecutables (47 de contenido de la ventana, 33 del camino de declaracion, 6 de contrato) y con la comprobacion DE PUNTA A PUNTA que faltaba: declarar desde la ventana -&gt; pipeline -&gt; la memoria imprime el valor como declarado y con su procedencia. La estrategia que lo hace posible es partir el componente: el CONTENIDO vive en src/ventana_normativa.py y se compara campo a campo sin escritorio; gui/ventana_normativa.py solo cablea widgets. Sigue sin cubrirse el cableado de widgets de gui/app.py anterior a esta sesion.</t>
+          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets. || S17 (rama claude/ventanas-emergentes-4-2-4-3-s50kk0, PR ABIERTO Y NO FUSIONADO --- nada de esto esta en main todavia): la funcionalidad nueva de la GUI nace con 86 tests ejecutables (47 de contenido de la ventana, 33 del camino de declaracion, 6 de contrato) y con la comprobacion DE PUNTA A PUNTA que faltaba: declarar desde la ventana -&gt; pipeline -&gt; la memoria imprime el valor como declarado y con su procedencia. La estrategia que lo hace posible es partir el componente: el CONTENIDO vive en src/ventana_normativa.py y se compara campo a campo sin escritorio; gui/ventana_normativa.py solo cablea widgets. Sigue sin cubrirse el cableado de widgets de gui/app.py anterior a esta sesion. Y EL CODIGO NUEVO TAMPOCO, dicho aqui para que no se lea de menos: gui/ventana_normativa.py --- el modulo de S17 que pinta widgets --- NO tiene cobertura automatica con Tk real. Se verifico UNA VEZ a mano, bajo Xvfb (las cuatro caras construidas sobre doce variables, la declaracion desde una fila, los tres colores del campo de rango al escribir y la corrida de perfil produciendo memoria_perfil.html), y esa comprobacion no quedo en la suite: no protege contra regresion. Lo que la suite si vigila de ese archivo es su ARBOL (brazos de excepcion, que recorra el orden visual declarado, que declare por declaracion.py y no por su cuenta) y, aparte, TODO su contenido a traves de src/ventana_normativa.py. Es el MISMO HUECO que la ficha declara para gui/app.py, no uno nuevo ni uno menor: el codigo que construye widgets sigue sin ejecutarse en la suite, y probarlo con un doble de tkinter seria un espejismo --- lo que se veria correr no es lo que corre en pantalla.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets. || S17 (rama claude/ventanas-emergentes-4-2-4-3-s50kk0, PR ABIERTO Y NO FUSIONADO --- nada de esto esta en main todavia): la funcionalidad nueva de la GUI nace con 86 tests ejecutables (47 de contenido de la ventana, 33 del camino de declaracion, 6 de contrato) y con la comprobacion DE PUNTA A PUNTA que faltaba: declarar desde la ventana -&gt; pipeline -&gt; la memoria imprime el valor como declarado y con su procedencia. La estrategia que lo hace posible es partir el componente: el CONTENIDO vive en src/ventana_normativa.py y se compara campo a campo sin escritorio; gui/ventana_normativa.py solo cablea widgets. Sigue sin cubrirse el cableado de widgets de gui/app.py anterior a esta sesion. Y EL CODIGO NUEVO TAMPOCO, dicho aqui para que no se lea de menos: gui/ventana_normativa.py --- el modulo de S17 que pinta widgets --- NO tiene cobertura automatica con Tk real. Se verifico UNA VEZ a mano, bajo Xvfb (las cuatro caras construidas sobre doce variables, la declaracion desde una fila, los tres colores del campo de rango al escribir y la corrida de perfil produciendo memoria_perfil.html), y esa comprobacion no quedo en la suite: no protege contra regresion. Lo que la suite si vigila de ese archivo es su ARBOL (brazos de excepcion, que recorra el orden visual declarado, que declare por declaracion.py y no por su cuenta) y, aparte, TODO su contenido a traves de src/ventana_normativa.py. Es el MISMO HUECO que la ficha declara para gui/app.py, no uno nuevo ni uno menor: el codigo que construye widgets sigue sin ejecutarse en la suite, y probarlo con un doble de tkinter seria un espejismo --- lo que se veria correr no es lo que corre en pantalla.</t>
+          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets. || S17 (5ec63ae, fusionado en main por 6ff80fc): la funcionalidad nueva de la GUI nace con 86 tests ejecutables (47 de contenido de la ventana, 33 del camino de declaracion, 6 de contrato) y con la comprobacion DE PUNTA A PUNTA que faltaba: declarar desde la ventana -&gt; pipeline -&gt; la memoria imprime el valor como declarado y con su procedencia. La estrategia que lo hace posible es partir el componente: el CONTENIDO vive en src/ventana_normativa.py y se compara campo a campo sin escritorio; gui/ventana_normativa.py solo cablea widgets. Sigue sin cubrirse el cableado de widgets de gui/app.py anterior a esta sesion. Y EL CODIGO NUEVO TAMPOCO, dicho aqui para que no se lea de menos: gui/ventana_normativa.py --- el modulo de S17 que pinta widgets --- NO tiene cobertura automatica con Tk real. Se verifico UNA VEZ a mano, bajo Xvfb (las cuatro caras construidas sobre doce variables, la declaracion desde una fila, los tres colores del campo de rango al escribir y la corrida de perfil produciendo memoria_perfil.html), y esa comprobacion no quedo en la suite: no protege contra regresion. Lo que la suite si vigila de ese archivo es su ARBOL (brazos de excepcion, que recorra el orden visual declarado, que declare por declaracion.py y no por su cuenta) y, aparte, TODO su contenido a traves de src/ventana_normativa.py. Es el MISMO HUECO que la ficha declara para gui/app.py, no uno nuevo ni uno menor: el codigo que construye widgets sigue sin ejecutarse en la suite, y probarlo con un doble de tkinter seria un espejismo --- lo que se veria correr no es lo que corre en pantalla.</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       <c r="I179" s="6" t="inlineStr"/>
       <c r="J179" s="6" t="inlineStr">
         <is>
-          <t>PR abierto contra main, NO fusionado</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K179" s="6" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="L179" s="6" t="inlineStr">
         <is>
-          <t>NO FUSIONADO. El trabajo vive en la rama claude/ventanas-emergentes-4-2-4-3-s50kk0 (HEAD 4bfda57, con el cambio de codigo en su commit padre) y NO esta en main: hay un PR abierto, pendiente de revision. Esta fila NO dice «Cerrado» a proposito, y no cita ningun SHA de main porque no lo hay. Se pasa a «Cerrado», con el SHA de la fusion, cuando el PR se fusione. Cerrado de paso al reescribir el encabezado de gui/app.py para SIS-A-17 y SIS-A-18, y en las DOS mitades que la ficha nombra: la lista dice ahora las cuatro pestanas --- incluida la de Criterios, que es la que reescribe criterios_adoptados.py y la que faltaba --- y la de exportaciones nombra el CSV junto a JSON, HTML y PDF.</t>
+          <t>5ec63ae (fusionado en main por 6ff80fc, PR #1, revisado y aprobado). Cerrado de paso al reescribir el encabezado de gui/app.py para SIS-A-17 y SIS-A-18, y en las DOS mitades que la ficha nombra: la lista dice ahora las cuatro pestanas --- incluida la de Criterios, que es la que reescribe criterios_adoptados.py y la que faltaba --- y la de exportaciones nombra el CSV junto a JSON, HTML y PDF.</t>
         </is>
       </c>
     </row>
@@ -13505,7 +13505,7 @@
       <c r="I201" s="6" t="inlineStr"/>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>PR abierto contra main, NO fusionado</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K201" s="6" t="inlineStr">
@@ -13515,7 +13515,7 @@
       </c>
       <c r="L201" s="6" t="inlineStr">
         <is>
-          <t>NO FUSIONADO. El trabajo vive en la rama claude/ventanas-emergentes-4-2-4-3-s50kk0 (HEAD 4bfda57, con el cambio de codigo en su commit padre) y NO esta en main: hay un PR abierto, pendiente de revision. Esta fila NO dice «Cerrado» a proposito, y no cita ningun SHA de main porque no lo hay. Se pasa a «Cerrado», con el SHA de la fusion, cuando el PR se fusione. La pestana 1 expone el alcance de la corrida con las constantes ALCANCE_PERFIL/ALCANCE_EXPEDIENTE de cli.py (no dos cadenas escritas otra vez), el valor llega a cli.correr, y las dos exportaciones de memoria eligen plantilla con cli.plantilla_por_alcance --- la MISMA funcion que usa cli.main, para que la misma corrida no de dos memorias segun la puerta. memoria_perfil.html deja de ser inalcanzable desde la interfaz. El resumen anade dos filas: el alcance y el numero de etapas diferidas por el. Comprobado con Tk real bajo Xvfb: la corrida de perfil desde la ventana produce la memoria de perfil. Cuatro tests de contrato en tests/test_gui_contrato.py.</t>
+          <t>5ec63ae (fusionado en main por 6ff80fc, PR #1, revisado y aprobado). La pestana 1 expone el alcance de la corrida con las constantes ALCANCE_PERFIL/ALCANCE_EXPEDIENTE de cli.py (no dos cadenas escritas otra vez), el valor llega a cli.correr, y las dos exportaciones de memoria eligen plantilla con cli.plantilla_por_alcance --- la MISMA funcion que usa cli.main, para que la misma corrida no de dos memorias segun la puerta. memoria_perfil.html deja de ser inalcanzable desde la interfaz. El resumen anade dos filas: el alcance y el numero de etapas diferidas por el. Comprobado con Tk real bajo Xvfb: la corrida de perfil desde la ventana produce la memoria de perfil. Cuatro tests de contrato en tests/test_gui_contrato.py.</t>
         </is>
       </c>
     </row>
@@ -13563,7 +13563,7 @@
       <c r="I202" s="6" t="inlineStr"/>
       <c r="J202" s="6" t="inlineStr">
         <is>
-          <t>PR abierto contra main, NO fusionado</t>
+          <t>Cerrado</t>
         </is>
       </c>
       <c r="K202" s="6" t="inlineStr">
@@ -13573,7 +13573,7 @@
       </c>
       <c r="L202" s="6" t="inlineStr">
         <is>
-          <t>NO FUSIONADO. El trabajo vive en la rama claude/ventanas-emergentes-4-2-4-3-s50kk0 (HEAD 4bfda57, con el cambio de codigo en su commit padre) y NO esta en main: hay un PR abierto, pendiente de revision. Esta fila NO dice «Cerrado» a proposito, y no cita ningun SHA de main porque no lo hay. Se pasa a «Cerrado», con el SHA de la fusion, cuando el PR se fusione. La sesion (formato v2) guarda "alcance" y "criterios", y este ultimo lleva los valores dinamicos Y la procedencia de cada uno. Se restaura por declaracion.restaurar_sesion, que repone con establecer_valor_dinamico --- la misma guardia que el archivo ---, de modo que un JSON editado a mano no es una puerta de atras. Lo que la guardia rechaza NO se descarta en silencio: sale con su motivo en un aviso. Una sesion v1 se sigue leyendo y avisa de lo que no traia (patron de legacy/Tc.py). Tests: round-trip por json en tests/test_declaracion.py y contrato en tests/test_gui_contrato.py.</t>
+          <t>5ec63ae (fusionado en main por 6ff80fc, PR #1, revisado y aprobado). La sesion (formato v2) guarda "alcance" y "criterios", y este ultimo lleva los valores dinamicos Y la procedencia de cada uno. Se restaura por declaracion.restaurar_sesion, que repone con establecer_valor_dinamico --- la misma guardia que el archivo ---, de modo que un JSON editado a mano no es una puerta de atras. Lo que la guardia rechaza NO se descarta en silencio: sale con su motivo en un aviso. Una sesion v1 se sigue leyendo y avisa de lo que no traia (patron de legacy/Tc.py). Tests: round-trip por json en tests/test_declaracion.py y contrato en tests/test_gui_contrato.py.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -4467,12 +4467,12 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S5)</t>
+          <t>Claude Code (fase1, S5) + Claude Code (fase1, S18)</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>00da460 — La frase 'el rango recorre la calidad del revestimiento' sale de la cita y pasa a declararse como INTERPRETACION DEL PROYECTISTA en `constantes_normativas.TABLA_10_INTERPRETACION_PROYECTO`, que M11 imprime separada, en su propio aviso. La `fuente` de 'v_max_concreto_eleccion', `M5.NUMERAL_V3` y la nota de la §1 del manifiesto separan ahora lo que la fuente sostiene (los dos numeros son maximos: lo dice el titulo y el rotulo 'VELOCIDAD (M/S)') de lo que pone el proyecto, y citan los dos hechos que juegan en contra de la lectura de acabados: la frase que introduce la tabla ('un rango, cuyos limites se describen a continuacion') y la fila de mamposteria con un solo valor.</t>
+          <t>00da460 — La frase 'el rango recorre la calidad del revestimiento' sale de la cita y pasa a declararse como INTERPRETACION DEL PROYECTISTA en `constantes_normativas.TABLA_10_INTERPRETACION_PROYECTO`, que M11 imprime separada, en su propio aviso. La `fuente` de 'v_max_concreto_eleccion', `M5.NUMERAL_V3` y la nota de la §1 del manifiesto separan ahora lo que la fuente sostiene (los dos numeros son maximos: lo dice el titulo y el rotulo 'VELOCIDAD (M/S)') de lo que pone el proyecto, y citan los dos hechos que juegan en contra de la lectura de acabados: la frase que introduce la tabla ('un rango, cuyos limites se describen a continuacion') y la fila de mamposteria con un solo valor. || f865969 (S18) — Reforzado en S18 con la separacion TIPOGRAFICA, que es lo que la ficha pedia y que en S5 quedo como separacion de campos. El texto sale ahora del registro (`TablaNormativa.interpretacion`, del tipo `Interpretacion`, que OBLIGA a declarar lo que juega en contra) y no de una segunda redaccion en `constantes_normativas`; se imprime en su propio bloque `class='aviso interpretacion'`, con los hechos EN CONTRA delante; y un test recorre todo lo que la memoria entrecomilla como literal y falla si la interpretacion aparece dentro de alguno.</t>
         </is>
       </c>
     </row>
@@ -4749,12 +4749,12 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S5)</t>
+          <t>Claude Code (fase1, S5) + Claude Code (fase1, S18)</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>00da460 — Cerrado sobre el PRODUCTO, que era donde fallaba. El matiz viajaba solo dentro de `M5.NUMERAL_V2`, o sea dentro de la tabla de verificaciones del punto, que no se imprime si el punto no llego a evaluarse -- y no llega, porque 'homogeneidad_serie_fen' bloquea el Q de la Familia A. Se agrega `constantes_normativas.UMBRALES_DE_VERIFICACION` (V1, V2, V3, TR y D_min con numeral, caracter, texto literal y lo que el proyecto hace con cada uno), `M11.bloque_umbrales()` y el marcador %%bloque_umbrales en las dos plantillas, en la seccion nueva '0-ter. Umbrales normativos y su caracter', que se imprime siempre. Medido sobre la memoria generada con tests/ejemplo_puntos.csv en los dos alcances: 'recomend' pasa de 0 a 7 apariciones y 'sedimentaci' de 0 a 3. || 76791d0 -- ademas, la memoria imprimia 'num. MC-HHD (...), num. 3.6' porque M11 anteponia 'num.' a un NUMERAL_TR que ya lo trae; y NUMERAL_V3 remitia a un simbolo de codigo que un revisor con el PDF no puede resolver.</t>
+          <t>00da460 — Cerrado sobre el PRODUCTO, que era donde fallaba. El matiz viajaba solo dentro de `M5.NUMERAL_V2`, o sea dentro de la tabla de verificaciones del punto, que no se imprime si el punto no llego a evaluarse -- y no llega, porque 'homogeneidad_serie_fen' bloquea el Q de la Familia A. Se agrega `constantes_normativas.UMBRALES_DE_VERIFICACION` (V1, V2, V3, TR y D_min con numeral, caracter, texto literal y lo que el proyecto hace con cada uno), `M11.bloque_umbrales()` y el marcador %%bloque_umbrales en las dos plantillas, en la seccion nueva '0-ter. Umbrales normativos y su caracter', que se imprime siempre. Medido sobre la memoria generada con tests/ejemplo_puntos.csv en los dos alcances: 'recomend' pasa de 0 a 7 apariciones y 'sedimentaci' de 0 a 3. || 76791d0 -- ademas, la memoria imprimia 'num. MC-HHD (...), num. 3.6' porque M11 anteponia 'num.' a un NUMERAL_TR que ya lo trae; y NUMERAL_V3 remitia a un simbolo de codigo que un revisor con el PDF no puede resolver. || f865969 (S18) — Reforzado en S18 y medido de nuevo sobre el producto. El matiz ya no viaja solo dentro del bloque fijo de umbrales: cada `PasoDeMemoria` de V2 lo lleva en su `Umbral` (caracter leido de la cita, no redactado a mano) y en `nota_del_proyecto`. Ademas se separaron las DOS MITADES del parrafo, que tienen fuerza distinta y se leian como una: 'se debera verificar' es EXIGENCIA (cita nueva `MC_HHD.4.1.1.3.6#VMIN_INICIO`, que vivia dentro de una `nota` y por eso no se podia imprimir aparte) y 'recomendandose que la velocidad minima sea igual a 0.25 m/s' es RECOMENDACION sobre el valor. Leida solo la segunda, 'V2 es una recomendacion' se entiende como que verificar el piso es opcional.</t>
         </is>
       </c>
     </row>
@@ -6579,12 +6579,12 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S5)</t>
+          <t>Claude Code (fase1, S5) + Claude Code (fase1, S18)</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>00da460 — `M5.NUMERAL_V1` deja de ser el numeral pelado: lleva RD, pag. impresa 79, el texto literal del 4.1.1.3.7 b) y el matiz de RECOMENDACION, igual que NUMERAL_V2, mas la declaracion de que el proyecto lo aplica como umbral duro. El comportamiento no cambia. Verificado contra el PDF: 'Se recomienda que el diseño hidraulico considere como minimo el 25 % de la altura, diametro o flecha de la estructura' (pag. impresa 79).</t>
+          <t>00da460 — `M5.NUMERAL_V1` deja de ser el numeral pelado: lleva RD, pag. impresa 79, el texto literal del 4.1.1.3.7 b) y el matiz de RECOMENDACION, igual que NUMERAL_V2, mas la declaracion de que el proyecto lo aplica como umbral duro. El comportamiento no cambia. Verificado contra el PDF: 'Se recomienda que el diseño hidraulico considere como minimo el 25 % de la altura, diametro o flecha de la estructura' (pag. impresa 79). || f865969 (S18) — Reforzado en S18: V1 emite `PasoDeMemoria` con el mismo aparato que V2 -- caracter RECOMENDACION leido de `MC_HHD.4.1.1.3.7b`, y la declaracion de que el proyecto lo aplica como umbral duro por decision conservadora propia -- y su fundamento `F5.V1` dice ademas que el 0.75 es la DERIVACION aritmetica del 25 % que el numeral escribe, no una cifra impresa.</t>
         </is>
       </c>
     </row>
@@ -8091,12 +8091,12 @@
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S2)</t>
+          <t>Claude Code (fase1, S2) + Claude Code (fase1, S18)</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe</t>
+          <t>3ea627c + 7266bfe || f865969 (S18) — Confirmado vigente en S18: `angulo_aletas` lleva `reemplazado_por`, `fuente` PENDIENTE y `sin_consumidor`, y la columna 'Que lo resuelve' de M11 ya no imprime el enunciado del vacio como si fuera lo que lo resuelve.</t>
         </is>
       </c>
     </row>
@@ -12103,12 +12103,12 @@
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S2)</t>
+          <t>Claude Code (fase1, S2) + Claude Code (fase1, S18)</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe</t>
+          <t>3ea627c + 7266bfe (S2) — `y/D` se retiro de M11 y vive en `ResultadoPunto.y_sobre_D`, escrito una vez. || f865969 — Cerrado DE RAIZ en S18, no solo retirando la division. M11 dejo de RECONSTRUIR la memoria: las funciones de calculo emiten `PasoDeMemoria` (§4.4) y M11 formatea. La frase del docstring 'sin calcular nada nuevo' pasa de intencion a propiedad comprobada -- `test_memoria_sustentada.test_M11_no_calcula_y_sobre_D` barre el AST del modulo y falla ante cualquier BinOp de division sobre magnitudes.</t>
         </is>
       </c>
     </row>
@@ -12596,11 +12596,19 @@
       <c r="I185" s="6" t="inlineStr"/>
       <c r="J185" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K185" s="6" t="inlineStr"/>
-      <c r="L185" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K185" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S18)</t>
+        </is>
+      </c>
+      <c r="L185" s="6" t="inlineStr">
+        <is>
+          <t>f865969 — El analisis de sensibilidad llega al documento. `_sensibilidad_declarada` imprime el rango como ANALISIS -- valor adoptado dentro de que margen, y si un barrido lo puede recorrer o no, consultando `parametros_sensibilizables(solo_numericos=True)`, que asi deja de tener por unico consumidor a los tests --. Va acompanado de la procedencia R1 de cada eleccion (`_de_donde_sale_el_valor`, que lee `Criterio.resolucion`), que era la mitad que faltaba: `_de_donde_salio` solo disparaba para lo declarado por la ventana emergente, o sea para casi nada de lo que gobierna una corrida.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -12646,11 +12654,19 @@
       <c r="I186" s="6" t="inlineStr"/>
       <c r="J186" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K186" s="6" t="inlineStr"/>
-      <c r="L186" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S18)</t>
+        </is>
+      </c>
+      <c r="L186" s="6" t="inlineStr">
+        <is>
+          <t>f865969 — Cerrado en las dos direcciones. (1) Las dos plantillas llevan ya los MISMOS marcadores -- el contrato que el docstring de la CLI promete -- y quien decide que va dentro de `bloque_pendientes` es el ALCANCE de la corrida, que es de donde tenia que salir la decision: a nivel de perfil no se vuelca Tableros 1-2-3 y se DICE, en vez de desaparecer con el marcador. (2) `memoria_html` se detiene con ValueError si la plantilla que se le pasa no imprime un bloque que ESA corrida si produjo, medido sobre el contenido real y no sobre la lista de marcadores. El test `test_la_de_perfil_usa_un_subconjunto_estricto` EXIGIA la omision, o sea vigilaba el defecto: se reescribio como `test_las_dos_plantillas_comparten_EL_MISMO_contrato_de_marcadores` diciendo por que.</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -1555,12 +1555,12 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>ver Hallazgos: Estado='Pendiente' (hoy 15, todos C14 salvo SIS-G-03) + 6 residuos de C01/C06/C09 reclamados aqui. El 73 original y cualquier suma por cluster completo sobreestiman: la mayoria de C04/C05/C07/C10/C11/C12 ya esta cerrada</t>
+          <t>CERRADA EN S19 (4141fd5). Al entrar eran DIECISEIS, no 73: diez con Estado='Pendiente' (todos C14 salvo SIS-G-03) mas seis 'Cerrado parcial' reclamados desde C01/C06/C09. El 73 salia de sumar los clusters ENTEROS asignados a F5, y la mayoria de sus hallazgos ya se habia cerrado en fases anteriores: un cluster entra a una fase, pero sus hallazgos se cierran donde toque. SALDO: los diez Pendiente pasan a Cerrado --- el tracker no deja ninguno ---, y los seis parciales siguen parciales con la razon PRECISADA y verificada: los cuatro NOR esperan algo que no es trabajo documental (un vacio declarado, un procedimiento hidraulico del Cap. III del HDS-5, una tabla por transcribir de una fuente que en un caso no esta en normas/, un detalle constructivo); SIS-F-01 gana la parte que faltaba dentro de su frontera declarada, que no se mueve (el cableado de widgets pide Tk real en CI); y SIS-F-13 estrecha su razon de tres a dos.</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Los 22 hallazgos clasificados como "deliberado sin documentar" tienen su decisión escrita; la GUI tiene tests de contrato; ningún dato no finito entra al pipeline como diagnóstico falso.</t>
+          <t>CUMPLIDA. (1) Los 22 'deliberado sin documentar' tienen su decision escrita EN UN SOLO LUGAR, docs/decisiones_diferidas.md, con cuatro campos fijos y una guardia (tests/test_decisiones_diferidas.py) que DERIVA la lista de los 22 del propio informe de auditoria y comprueba que el simbolo de cada ficha siga existiendo. (2) La GUI tiene tests de contrato: 43 en test_gui_contrato.py, con las tres decisiones de gui/app.py que nadie ejercitaba y dos guardias de encabezado; los tres mutantes probados mueren. (3) 'Ningun dato no finito entra al pipeline como diagnostico falso' ya se cumplia desde S16.5 (LimiteNumericoError, SIS-G-01/G-02). AÑADIDO NO PEDIDO: MAT-D1 estaba corregido y no lo defendia ningun test --- la mutacion dejaba la suite entera en verde ---, y SIS-A-08 estaba cerrado solo en su letra: su premisa falsa se habia sustituido por otra premisa falsa. Suite 1507 passed / 1 skipped (1508 collected).</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>00da460 — V2 deja de leer la rama n_min. `modelos.TiranteNormal` y `modelos.ResultadoHidraulico` retiran el campo `V` y llevan dos: `V_erosion` (n_min, estimacion ALTA) y `V_sedimentacion` (n_max, estimacion BAJA), las dos sobre la MISMA geometria de Brent. `M5.v2_velocidad_minima` consume `V_sedimentacion`; `v3_velocidad_maxima` y Laushey (cli._fase_6 -&gt; M6) consumen `V_erosion`. No hay campo neutro que permita elegir mal en silencio. Recomputado a mano: D=0.90, y/D=0.75 (theta=4pi/3), S=5e-5, concreto -&gt; A=0.511800 m2, R=0.271518 m, V(n_max)=0.228073 m/s y V(n_min)=0.296495 m/s con Q=0.116728 m3/s: V2 pasa de 'cumple' a 'NO cumple', que es lo correcto. `Material.n_para_velocidad` se renombra `n_para_velocidad_maxima` (los terminos de la Sec. 4.1 de la hoja de ruta) y se agrega `n_para_velocidad_minima`.</t>
+          <t>00da460 — V2 deja de leer la rama n_min. `modelos.TiranteNormal` y `modelos.ResultadoHidraulico` retiran el campo `V` y llevan dos: `V_erosion` (n_min, estimacion ALTA) y `V_sedimentacion` (n_max, estimacion BAJA), las dos sobre la MISMA geometria de Brent. `M5.v2_velocidad_minima` consume `V_sedimentacion`; `v3_velocidad_maxima` y Laushey (cli._fase_6 -&gt; M6) consumen `V_erosion`. No hay campo neutro que permita elegir mal en silencio. Recomputado a mano: D=0.90, y/D=0.75 (theta=4pi/3), S=5e-5, concreto -&gt; A=0.511800 m2, R=0.271518 m, V(n_max)=0.228073 m/s y V(n_min)=0.296495 m/s con Q=0.116728 m3/s: V2 pasa de 'cumple' a 'NO cumple', que es lo correcto. `Material.n_para_velocidad` se renombra `n_para_velocidad_maxima` (los terminos de la Sec. 4.1 de la hoja de ruta) y se agrega `n_para_velocidad_minima`. || S19 — LA CORRECCION ESTABA VIVA Y NO LA DEFENDIA NADIE. Al escribir el caso patron de M5 se muto `v2_velocidad_minima` de vuelta a `resultado.V_erosion` y la suite entera quedo EN VERDE (1497 tests). La razon: todos los tests de V2 usaban `_resultado(V=...)`, que fija LAS DOS ramas al mismo numero, y con las dos iguales la rama que se lea da igual. Anadido test_v2_decide_con_la_rama_de_n_MAXIMO_y_no_con_la_de_erosion, que las separa a los dos lados del piso --- la ventana que el propio docstring de la funcion describe, S entre 3.55e-5 y 6.01e-5 --- y mata la mutacion. El hallazgo sigue Cerrado; lo que cambia es que ahora esta defendido.</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S10)</t>
+          <t>Claude Code (fase1, S19)</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>6768725 — ESPESOR_DOS_CAPAS_REFUERZO = 0.200 m (Art. 14.3.2) y M9.requiere_refuerzo_dos_capas: entre 200 y 250 mm el muro lleva dos capas aunque el acero por temperatura vaya en una cara, que es lo contrario de lo que la memoria imprimia. CIERRA EN PARTE, y se deja dicho: la nota que lo declara sigue sin llamador de produccion porque su insumo es el espesor, que sale de 'predimensionamiento_cabezal' y es un vacio declarado. La logica esta corregida; la memoria no lo imprimira hasta que ese vacio se cierre, y la CLI registra el bloqueo en cada corrida (mismo caso que SIS-B-20). || REVISADO EN S12: el diferimiento sigue vigente. Su insumo es el espesor, que sale de 'predimensionamiento_cabezal', y ese vacio declarado sigue vacio: S12 no lo toco. La logica sigue corregida y la memoria sigue sin poder imprimirlo.</t>
+          <t>S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: `predimensionamiento_cabezal` sigue siendo vacio declarado (valor=None, [A]), de modo que el diferimiento sigue vigente por la misma causa que en S10 y S12. La logica sigue corregida (ESPESOR_DOS_CAPAS_REFUERZO + M9.requiere_refuerzo_dos_capas) y la funcion esta censada en M9_cabezal.FUNCIONES_SIN_CONSUMIDOR con su razon. QUE FALTA, escrito ya en docs/decisiones_diferidas.md: que el proyectista declare el predimensionamiento Y que `diseno_flexion_corte` deje de detenerse en NotImplementedError. Ninguna de las dos es trabajo documental: NO se cierra en F5.</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S6)</t>
+          <t>Claude Code (fase1, S19)</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>3ed6b22 + 4f32683 — h_o deja de ser una formula 'sin numeral' y sin limite: num. 3.3.3 'Outlet Control', pag. impresa 3.24, con sus TRES condiciones transcritas verbatim y cada una atribuida a su sitio de la pagina (H_O_NUMERAL, H_O_CONDICION_TEXTO, H_O_FORMA_MAXIMO_TEXTO, H_O_CONDICION_APLICACION). DOS de las tres SE EVALUAN punto por punto: los limites HW/D &lt; 0.75 ('should not be used') y HW/D &lt; 1.2 ('caution'), como constantes [N] H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculados en control_salida(), filtrados por si el control de salida gobierna -- que es como la fuente los escribe -- e impresos EN LA MEMORIA DEL PUNTO junto a su HW. Es lo que la auditoria adversarial refuto de la primera version, que los declaraba sin evaluarlos pudiendo: el punto A-02 del CSV de ejemplo da HW/D=0.675 con el control de salida gobernando, y la memoria no lo decia. La condicion llega ademas siempre por UMBRALES_DE_VERIFICACION, tambien en la corrida bloqueada. QUEDA ABIERTO lo unico que no se puede evaluar sin un perfil de la lamina de agua: que el barril fluya lleno en la mayor parte de su longitud. Lo cerraria el procedimiento de barril parcialmente lleno del Cap. III. || REVISADO EN S12: el diferimiento sigue vigente. Lo abierto es la tercera condicion -- que el barril fluya lleno en la mayor parte de su longitud --, que no se puede evaluar sin el perfil de lamina de agua del Cap. III de HDS-5. S12 no implemento ese procedimiento. || S14 — NO CERRADO. Lo que queda abierto es la tercera condicion de uso de h_o -- que el barril fluya lleno en la mayor parte de su longitud --, que exige el procedimiento de barril parcialmente lleno del Cap. III del HDS-5, no implementado. Sigue Cerrado parcial.</t>
+          <t>S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md.</t>
         </is>
       </c>
     </row>
@@ -6993,12 +6993,12 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S4)</t>
+          <t>Claude Code (fase1, S19)</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — la ATRIBUCION queda cerrada: 'clases_producto_por_relleno' y el docstring de M8 dejan de difierir a ASTM A-807 (que no aparece en M 170M, M 36 ni A760) y difieren a ASTM A796/A796M, con A798/A798M para instalacion; se anota que la remision del EG-2013 507.05/.06/.08 a A-807 si es correcta pero es de materiales. QUEDA ABIERTO lo que la ficha dice que se puede cerrar hoy: transcribir la relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36. Es trabajo de la tabla de clases (C01 no la transcribe) y sigue en el vacio declarado 'clases_producto_por_relleno'. || S14 — NO CERRADO, y se deja dicho que sigue abierto. La mitad que la ficha dice que se puede cerrar hoy -- transcribir la relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 -- NO se hizo en esta sesion: es transcripcion de tabla y no entra en los criterios de salida de S14. Lo que S14 si deja comprobado, para quien la tome: la Tabla 1 de A760 es LEGIBLE renderizando la pag. PDF 3 a escala 2.0 (el texto extraido de ese PDF viene con la codificacion de fuente rota y por eso parecia inaccesible). Trae 30 filas de diametro nominal (4 in / 100 mm a 144 in / 3600 mm) por siete tamaños de corrugacion mas la circunferencia exterior minima. Sigue Cerrado parcial.</t>
+          <t>S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada.</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S4)</t>
+          <t>Claude Code (fase1, S19)</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>3d59da0 — la comparacion que la ficha reclama queda DECLARADA: 'hds5_embocadura_hdpe' lleva ahora la fila alternativa ('Circular CM / Headwall') en `sensibilidad` y su verificacion_pendiente dice con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila: la adopcion se sostiene en el perfil de pared en la boca (argumento fisico que la ficha no refuta), no en un margen de seguridad, y elegir la del metal por su resultado seria sustituir una analogia por otra. Lo que cierra el punto es el detalle constructivo, y eso sigue abierto. || S14 — NO CERRADO. Lo que la ficha pide para cerrarlo es el detalle constructivo de la embocadura, que no es trabajo de esta sesion. Sigue Cerrado parcial.</t>
+          <t>S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: la comparacion que la ficha reclama sigue DECLARADA en 'hds5_embocadura_hdpe' --- la fila alternativa ('Circular CM / Headwall') en `sensibilidad`, y `verificacion_pendiente` diciendo con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila, y es decision, no omision: la adopcion se sostiene en el perfil de pared en la boca --- argumento fisico que la ficha no refuta ---, no en un margen de seguridad. QUE FALTA: el detalle constructivo de la embocadura, que es contenido de planos. NO se cierra en F5.</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S16 + S17)</t>
+          <t>Claude Code (fase1, S19)</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 — PARCIAL Y DECLARADO COMO TAL en el encabezado de tests/test_gui_contrato.py (19 tests): se cubre el CONTRATO, no las 584 sentencias. Parte AST: forma de los brazos de excepcion, todos los manejadores y no solo el primero, BaseException prohibida, print_exc como sentencia directa del cuerpo. Parte EJECUTABLE con un doble de tkinter inyectado en sys.modules: _interpretar_valor_declarado y _leer_banderas, las dos reimplementaciones que la ficha nombra, mas la divergencia deliberada GUI-vs-CLI sobre '1,5', fijada como tal. Queda fuera el resto del cableado de widgets. || S17 (5ec63ae, fusionado en main por 6ff80fc): la funcionalidad nueva de la GUI nace con 86 tests ejecutables (47 de contenido de la ventana, 33 del camino de declaracion, 6 de contrato) y con la comprobacion DE PUNTA A PUNTA que faltaba: declarar desde la ventana -&gt; pipeline -&gt; la memoria imprime el valor como declarado y con su procedencia. La estrategia que lo hace posible es partir el componente: el CONTENIDO vive en src/ventana_normativa.py y se compara campo a campo sin escritorio; gui/ventana_normativa.py solo cablea widgets. Sigue sin cubrirse el cableado de widgets de gui/app.py anterior a esta sesion. Y EL CODIGO NUEVO TAMPOCO, dicho aqui para que no se lea de menos: gui/ventana_normativa.py --- el modulo de S17 que pinta widgets --- NO tiene cobertura automatica con Tk real. Se verifico UNA VEZ a mano, bajo Xvfb (las cuatro caras construidas sobre doce variables, la declaracion desde una fila, los tres colores del campo de rango al escribir y la corrida de perfil produciendo memoria_perfil.html), y esa comprobacion no quedo en la suite: no protege contra regresion. Lo que la suite si vigila de ese archivo es su ARBOL (brazos de excepcion, que recorra el orden visual declarado, que declare por declaracion.py y no por su cuenta) y, aparte, TODO su contenido a traves de src/ventana_normativa.py. Es el MISMO HUECO que la ficha declara para gui/app.py, no uno nuevo ni uno menor: el codigo que construye widgets sigue sin ejecutarse en la suite, y probarlo con un doble de tkinter seria un espejismo --- lo que se veria correr no es lo que corre en pantalla.</t>
+          <t>4141fd5 — S19 cubre la parte que faltaba DENTRO de la frontera declarada, y la frontera no se mueve. NUEVO: `_estado_criterio` ejercitado en sus tres casos (incluido «declarado (corrida)», el que SIS-A-01 dejo invisible); la leyenda de etiquetas contrastada contra `ca.CRITERIOS` en vez de contra una lista copiada; que `_llenar_tabla_criterios` lea el valor por `ca.criterio_efectivo` y no por una regla propia (SIS-A-01 en forma de guardia); y dos guardias de encabezado contra el arbol --- las cuatro pestanas y las cuatro exportaciones (SIS-A-10, que se habia cerrado a mano y no vigilaba nadie), y que el encabezado no vuelva a afirmar que usa el campo validable. MEDIDO: gui/app.py tiene hoy 1182 lineas y ~595 sentencias ejecutables; la suite ejecuta una fraccion pequeña y el resto se lee del AST. SIGUE ABIERTO, y es lo mismo que S17 declaro: el codigo que CONSTRUYE WIDGETS no se ejecuta en la suite, ni el viejo de gui/app.py ni el nuevo de gui/ventana_normativa.py. No es descuido: con un doble de tkinter seria un espejismo. QUE HARIA FALTA: una suite con Tk real bajo servidor X virtual en CI. Es infraestructura, no un test mas.</t>
         </is>
       </c>
     </row>
@@ -10087,16 +10087,12 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S16)</t>
+          <t>Claude Code (fase1, S19)</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>52c11d2 — PARCIAL. El fixture gana CP-9 y con el pasan a consumir caso patron M7 (CP9_GEOMETRIA_7B) y M9 (CP9_MONONOBE_OKABE, CP9_RANKINE_LIMITE, CP9_EMPUJE_TRASDOS). SIGUEN SIN CASO PATRON M2, M8 y M10: para esos el fixture no da dorados y fabricarlos aqui seria inventar el valor de referencia, que es justo lo que el conflicto n.7 (CP-1 dorados / SIS-F-14) prohibe. Queda declarado como deuda abierta.
-PRECISADO EN 96084e8 (fase1, S16.5) (sin correccion de codigo; la frontera se describia de menos). Hoy son CINCO los tests que no importan casos_patron, no tres, y por TRES razones distintas que no se pueden contar juntas -- docs/linea_base.md ya avisaba en S1 que 'el grep real da 7 modulos, verificar alcance exacto en la fase de correccion':
-  * M2, M8, M10 — no hay dorado que traer sin violar el conflicto n.7. Es la unica deuda de las tres. QUE HARIA FALTA TRAER a cada uno queda escrito en la §15 del plan (hoja_de_ruta_correcciones_v12.md), con la fuente concreta: series de diametros nominales de las normas de producto para M2; AASHTO M 170M Tablas 1-5 y ASTM A796/A796M para M8; y para M10 no una norma sino el expediente vial (seccion de cuneta, su n, la intensidad de TR=35 y el metodo de area tributaria), porque su brazo normativo ya es [N] y un caso patron sobre el seria tautologico.
-  * M5 — NO es deuda de dorado: el fixture SI define su caso (CP3_VELOCIDAD_MINIMA, Sec. 5.2), pero lo consumen test_M3 y test_constantes_normativas en vez de test_M5.
-  * M11 — modulo de reporte, no de calculo: no le corresponde dorado numerico.</t>
+          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial.</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12162,7 @@
       </c>
       <c r="L177" s="6" t="inlineStr">
         <is>
-          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa.</t>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa. || S19 — REABIERTO Y VUELTO A CERRAR, porque estaba cerrado solo en su letra. La premisa falsa «M5 todavia no existe en el repositorio» se habia retirado de MD.py y sustituido por otra razon --- «la importacion perezosa evita ademas un ciclo de importacion en el arranque» --- que TAMBIEN ES FALSA: M5 importa criterios_adoptados, constantes_normativas, modelos, M2, M8 y tolerancias, y ninguno vuelve a MD. Sustituir una premisa falsa por otra no cierra el hallazgo: le cambia el hecho. Ademas la premisa original sobrevivia VERBATIM en el docstring de tests/test_MD.py, remitiendo a un parrafo de MD que ya no dice eso. Corregidas las dos, con la razon que si se sostiene, y con guardia: test_la_premisa_de_que_M5_no_existe_no_vuelve_como_afirmacion mira los docstrings POR AST y admite la mencion solo cuando el parrafo la declara caducada --- la leccion de FACTOR_MURO_TABLA.</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12278,7 @@
       </c>
       <c r="L179" s="6" t="inlineStr">
         <is>
-          <t>5ec63ae (fusionado en main por 6ff80fc, PR #1, revisado y aprobado). Cerrado de paso al reescribir el encabezado de gui/app.py para SIS-A-17 y SIS-A-18, y en las DOS mitades que la ficha nombra: la lista dice ahora las cuatro pestanas --- incluida la de Criterios, que es la que reescribe criterios_adoptados.py y la que faltaba --- y la de exportaciones nombra el CSV junto a JSON, HTML y PDF.</t>
+          <t>5ec63ae (fusionado en main por 6ff80fc, PR #1, revisado y aprobado). Cerrado de paso al reescribir el encabezado de gui/app.py para SIS-A-17 y SIS-A-18, y en las DOS mitades que la ficha nombra: la lista dice ahora las cuatro pestanas --- incluida la de Criterios, que es la que reescribe criterios_adoptados.py y la que faltaba --- y la de exportaciones nombra el CSV junto a JSON, HTML y PDF. || S19 — sigue cerrado, verificado de forma independiente (el encabezado numera cuatro pestanas y cuatro exportaciones, y el codigo crea cuatro `nb.add` y expone cuatro `exportar_*`). Se le pone GUARDIA, que era lo que faltaba: test_el_encabezado_enumera_las_pestanas_y_exportaciones_que_la_ventana_crea cuenta las dos cosas en el AST y las contrasta con lo que el docstring numera. Se cerro a mano en S17 y nada impedia que se reabriera con la quinta pestana.</t>
         </is>
       </c>
     </row>
@@ -12330,11 +12326,19 @@
       <c r="I180" s="6" t="inlineStr"/>
       <c r="J180" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K180" s="6" t="inlineStr"/>
-      <c r="L180" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L180" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — La leyenda de la pestana de Criterios enumera ahora las CUATRO etiquetas que criterios_adoptados.py puede contener ([N-&gt;] 2, [S] 3, [C] 13, [A] 41, medidas hoy), dice que lo normativo vive en constantes_normativas.py y ya no anuncia [N]. Y el conjunto NO se transcribe en el test: `test_la_leyenda_nombra_exactamente_las_etiquetas_que_el_archivo_puede_tener` lo DERIVA de `ca.CRITERIOS`, de modo que la leyenda no puede volver a envejecer en silencio. PRECISION SOBRE LA FICHA: decia que [N] es 'imposible' en ese archivo y a nivel de codigo no lo es --- ETIQUETAS_VALIDAS admite 'N' y _verificar_criterio la aceptaria ---; lo que lo impide es el guardian test_ningun_criterio_adoptado_lleva_ya_la_etiqueta_N. La leyenda nueva dice lo que es cierto: que ninguna fila de esa tabla es normativa.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -12380,11 +12384,19 @@
       <c r="I181" s="6" t="inlineStr"/>
       <c r="J181" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K181" s="6" t="inlineStr"/>
-      <c r="L181" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L181" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — El encabezado de gui/app.py deja de afirmar que reutiliza el 'campo validable' y dice donde vive de verdad: `gui/componentes.CampoValidable`, que lo cablea la ventana emergente porque la Sec. 4.3 pide validar AL ESCRIBIR, mientras la principal valida al pulsar EJECUTAR. `color_borde_ok` retirado: se calculaba en `_crear_interfaz` y no lo leia nadie (barrido AST, incluido acceso dinamico). LA FICHA ESTA HOY A MEDIAS OBSOLETA y se deja dicho: decia que el campo validable 'no existe', y desde S17 SI existe --- lo que no existe es su uso en gui/app.py. Fijado por test_la_ventana_principal_no_afirma_reutilizar_el_campo_validable.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -12430,11 +12442,19 @@
       <c r="I182" s="6" t="inlineStr"/>
       <c r="J182" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K182" s="6" t="inlineStr"/>
-      <c r="L182" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K182" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L182" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — El docstring de `escribir_valor_en_archivo` decia 'reescribe el valor=None' y el patron es `valor=)([^,\n]*)(,)`, que casa con lo que haya: un criterio YA declarado se reescribe por la misma via y el boton de la GUI esta disponible para toda fila. Es DELIBERADO --- corregir un valor adoptado es tan legitimo como declararlo, y obligar a editar el archivo a mano empujaria a saltarse la guardia --- y lo que faltaba era decirlo. Queda escrito ademas lo que la funcion NO toca (etiqueta, justificacion, fuente, sensibilidad, resolucion) y que la GUI lo advierte en su confirmacion.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -13753,11 +13773,19 @@
       <c r="I205" s="6" t="inlineStr"/>
       <c r="J205" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K205" s="6" t="inlineStr"/>
-      <c r="L205" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L205" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Dentro de `cli.correr` lo unico que corre fuera de `_etapa` es `M0_carga.cargar_puntos`, que no importa criterios ni datos de sitio y solo levanta DatoFaltante/DatoInvalido, de modo que ningun CriterioPendienteError alcanza el `except ErrorProyecto` de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -13803,11 +13831,19 @@
       <c r="I206" s="6" t="inlineStr"/>
       <c r="J206" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K206" s="6" t="inlineStr"/>
-      <c r="L206" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K206" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L206" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — CONSERVADO con su razon escrita. El docstring prometia un consumidor ('unico acceso permitido cuando el modulo que llama NECESITA el numero') cuya condicion no se cumple en ningun sitio, que es la forma que este mismo archivo ya desterro al cerrar SIS-B-02. Ahora dice la verdad: los cinco accesos de produccion tratan el None; se conserva porque es la unica sentencia ejecutable del invariante y sin ella el consumidor que llegue escribira `tr.anios or 35`. SE DECLARA ADEMAS UN LIMITE QUE LA FICHA NO VIO: la guardia distingue mal sus dos ramas (Familia C = falta el dato; puente = fuera de alcance, donde corresponderia DisenoNoFactibleError), y `PeriodoRetorno` no lleva con que separarlas sin oler el texto de `fundamento`. Cerrarlo pide un discriminante en el objeto: queda anotado en el registro.</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -13911,11 +13947,19 @@
       <c r="I208" s="6" t="inlineStr"/>
       <c r="J208" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K208" s="6" t="inlineStr"/>
-      <c r="L208" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K208" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L208" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — DECISION: SE CONSERVA, y no por nostalgia. legacy/Tc.py NO es codigo muerto: es OTRO PROGRAMA, el de aguas arriba, y la Sec. 1.2 de la hoja de ruta lo nombra en la fila del caudal ('Caudal de diseño Q | m3/s | Tc.py + IDF con TR de Fase 2'), de modo que Q entra al calculador como columna del CSV y este archivo es la herramienta que la produce. Su estatus queda escrito EN SU PROPIO ENCABEZADO, con las dos cosas que hay que decir enteras: tal como esta commiteado NO CORRE aqui (matplotlib es import de nivel superior y no esta en requirements.txt; plantilla_memoria.html no existe en el repositorio), y sus ocho componentes ya estan extraidos a gui/componentes.py y M11.PlantillaMemoria. MEDIDO HOY: 1320 lineas, 0 importadores, 0 tests, exento por directorio en test_sin_literales.DIRECTORIOS_FUERA_DEL_BARRIDO con su razon verificada por un test que barre el AST. DEFECTO CONTRA CLAUDE.md CORREGIDO: la §GUI ordenaba 'leer esos archivos antes de escribir GUI', mandando a un programa que ya no se puede importar.</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -14077,11 +14121,19 @@
       <c r="I211" s="6" t="inlineStr"/>
       <c r="J211" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K211" s="6" t="inlineStr"/>
-      <c r="L211" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L211" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — CONSERVADO, con la mitad que faltaba escrita: no basta decir que None significa 'no declarado'; hay que decir POR QUE nadie debe despachar sobre el campo. Despacharlo convertiria la frase de la Sec. 2.3 en un FILTRO y dejaria a la Familia A sin V3, V6, V7, V8 y V9 --- que la tabla de la Fase 5 no exime por familia --- y a B y C sin conjunto ninguno. DEFECTO REPORTADO CONTRA LA HOJA DE RUTA (regla 7): la Sec. 2.3 escribe 'Aceptacion: V1 + V2 + V4 + V5' solo para la Familia A y en forma que se lee exhaustiva, mientras la Fase 5 tabula sin calificar por familia y para B y C no declara nada. La fuente primaria no puede dirimirlo (la taxonomia A/B/C y las etiquetas V1..V9 son de la hoja). MIENTRAS NO SE CORRIJA, LA HOJA SIGUE MAL: quien la lea sin leer el codigo creera que a la Familia A no se le exige V7 ni V9.</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
@@ -14301,11 +14353,19 @@
       <c r="I215" s="6" t="inlineStr"/>
       <c r="J215" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K215" s="6" t="inlineStr"/>
-      <c r="L215" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K215" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L215" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — La ficha esta OBSOLETA en su unica acusacion viva y se deja dicho: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva.</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -14528,11 +14588,19 @@
       <c r="I219" s="6" t="inlineStr"/>
       <c r="J219" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K219" s="6" t="inlineStr"/>
-      <c r="L219" s="6" t="inlineStr"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K219" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
+      <c r="L219" s="6" t="inlineStr">
+        <is>
+          <t>4141fd5 — Y EL HALLAZGO SE QUEDABA CORTO, dicho para que no se lea de menos: no era solo que el ejemplo diera las luces sin la salvedad que si lleva el test y con ids del fixture presentados como cruces reales --- es que NO EJECUTABA. Llamaba a `clasificar_puntos` con dos de sus tres argumentos y abortaba en el primer punto con CriterioPendienteError sobre 'umbral_area_quebrada_importante_ha' (reproducido). El bloque Uso nuevo corre y da 71/35/35/None, dice que los ids son del fixture y que la luz no es columna de la Sec. 1.2, y corrige '# detiene los puentes', que describia un efecto que con esas cuatro luces no se produce. Lo fija un test que EXTRAE el bloque del archivo y lo ejecuta, de modo que ejemplo y test no puedan volver a divergir.</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -15553,16 +15621,17 @@
       </c>
       <c r="J238" s="6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="K238" s="6" t="n"/>
+          <t>Cerrado</t>
+        </is>
+      </c>
+      <c r="K238" s="6" t="inlineStr">
+        <is>
+          <t>Claude Code (fase1, S19)</t>
+        </is>
+      </c>
       <c r="L238" s="6" t="inlineStr">
         <is>
-          <t>DECLARADO, NO CERRADO, a proposito. S16.5 corrigio las DOS citas concretas -- modelos.py :359 -&gt; :481 y M11 :721 -&gt; :799, ambas verificadas LEYENDO la linea de destino y no restando el desplazamiento -- porque sus propias inserciones las movian de todos modos. Pero NO arregla el hueco del test en el mismo commit: eso es un cambio de diseño de la guardia y merece su propia sesion, con un barrido de las 67 restantes.
-LO QUE HARIA FALTA, en orden de preferencia: (1) anclar la fila a un simbolo y sacarla del cupo de test_T9, que es la cura que NOR-MAN-04 ya prescribe y que el resincronizador (python3 -m src.normativa.manifiesto --escribir) mantiene solo; o (2) donde no haya simbolo que anclar, que la fila declare un FRAGMENTO LITERAL del texto que espera encontrar en su destino, para que el test compare contenido y no solo 'no esta en blanco'.
-Sin cluster asignado: no encaja en C09 (tests de calculo) ni en C11 (citas normativas contra PDF); es la guardia del manifiesto, que es un tercer objeto.
-Severidad MEDIA y no MENOR: el manifiesto es el mapa por el que un revisor llega al codigo, y una cita que aterriza en otra cosa lo manda a leer el simbolo equivocado creyendo que leyo el correcto.</t>
+          <t>4141fd5 — EL BARRIDO QUE LA FICHA PEDIA, HECHO, y el hueco del test cerrado por cambio de diseño. La ficha decia que la tasa entre las no ancladas era DESCONOCIDA: medida, era mala. De 68 referencias no ancladas, 16 llevaban a un sitio que no habla de lo que la fila dice --- entre ellas `e2_volteo()` y `empuje_flotacion()`, nombres que el codigo ya no tiene, y ESPACIAMIENTO_MAX_VECES_ESPESOR apuntando al bloque de `n_s_zapata_en_talud` --- y de las 32 restantes sin identificador, 27 tambien. Todas verificadas LEYENDO la linea de destino y reparadas. EL CAMBIO DE DISEÑO: «de prosa» mezclaba dos poblaciones, la fila que no nombra nada (hueco real) y la que nombra un simbolo que el archivo USA sin definir (verificable). Separadas: `test_toda_fila_que_cita_un_identificador_lo_nombra_en_su_destino`, SIN CUPO. Ademas: `_simbolos_citados` devuelve la cola punteada (`M9.cuantia_de_diseno`) y filtra ids de ficha --- eso solo destapo 4 desviadas ---; el resincronizador aprende a mantener las referencias por mencion; y se retiran 40 etiquetas con rango IMPOSIBLE (`[CN:170-49]`), defecto nunca reportado que nacia de reescribir el inicio conservando el final viejo. RESULTADO: 326 referencias = 299 por simbolo + 25 por mencion + 2 sin identificador (las dos legitimas, a docstring de modulo), 0 rotas. Cupos bajados 82-&gt;27 y 33-&gt;2, cobertura verificable del 99 %.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L205" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Dentro de `cli.correr` lo unico que corre fuera de `_etapa` es `M0_carga.cargar_puntos`, que no importa criterios ni datos de sitio y solo levanta DatoFaltante/DatoInvalido, de modo que ningun CriterioPendienteError alcanza el `except ErrorProyecto` de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md.</t>
+          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Comprobado vaciando el valor de los 46 criterios y de todos los datos de sitio: cli.correr devuelve informe sin levantar nada, con 12 bloqueos archivados. Los tres unicos sitios que levantan CriterioPendienteError cuelgan de etapas envueltas por _etapa, de modo que ninguno alcanza el except ErrorProyecto de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md.</t>
         </is>
       </c>
     </row>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="L208" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — DECISION: SE CONSERVA, y no por nostalgia. legacy/Tc.py NO es codigo muerto: es OTRO PROGRAMA, el de aguas arriba, y la Sec. 1.2 de la hoja de ruta lo nombra en la fila del caudal ('Caudal de diseño Q | m3/s | Tc.py + IDF con TR de Fase 2'), de modo que Q entra al calculador como columna del CSV y este archivo es la herramienta que la produce. Su estatus queda escrito EN SU PROPIO ENCABEZADO, con las dos cosas que hay que decir enteras: tal como esta commiteado NO CORRE aqui (matplotlib es import de nivel superior y no esta en requirements.txt; plantilla_memoria.html no existe en el repositorio), y sus ocho componentes ya estan extraidos a gui/componentes.py y M11.PlantillaMemoria. MEDIDO HOY: 1320 lineas, 0 importadores, 0 tests, exento por directorio en test_sin_literales.DIRECTORIOS_FUERA_DEL_BARRIDO con su razon verificada por un test que barre el AST. DEFECTO CONTRA CLAUDE.md CORREGIDO: la §GUI ordenaba 'leer esos archivos antes de escribir GUI', mandando a un programa que ya no se puede importar.</t>
+          <t>4141fd5 — DECISION: SE CONSERVA, y no por nostalgia. legacy/Tc.py NO es codigo muerto: es OTRO PROGRAMA, el de aguas arriba, y la Sec. 1.2 de la hoja de ruta lo nombra en la fila del caudal ('Caudal de diseño Q | m3/s | Tc.py + IDF con TR de Fase 2'), de modo que Q entra al calculador como columna del CSV y este archivo es la herramienta que la produce. Su estatus queda escrito EN SU PROPIO ENCABEZADO, con las dos cosas que hay que decir enteras: tal como esta commiteado NO CORRE aqui (matplotlib es import de nivel superior y no esta en requirements.txt; plantilla_memoria.html no existe en el repositorio), y sus ocho componentes ya estan extraidos a gui/componentes.py y M11.PlantillaMemoria. MEDIDO HOY: 0 importadores, 0 tests, exento por directorio en test_sin_literales.DIRECTORIOS_FUERA_DEL_BARRIDO con su razon verificada por un test que barre el AST. DEFECTO CONTRA CLAUDE.md CORREGIDO: la §GUI ordenaba 'leer esos archivos antes de escribir GUI', mandando a un programa que ya no se puede importar.</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="L215" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — La ficha esta OBSOLETA en su unica acusacion viva y se deja dicho: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva.</t>
+          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -12162,7 +12162,7 @@
       </c>
       <c r="L177" s="6" t="inlineStr">
         <is>
-          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa. || S19 — REABIERTO Y VUELTO A CERRAR, porque estaba cerrado solo en su letra. La premisa falsa «M5 todavia no existe en el repositorio» se habia retirado de MD.py y sustituido por otra razon --- «la importacion perezosa evita ademas un ciclo de importacion en el arranque» --- que TAMBIEN ES FALSA: M5 importa criterios_adoptados, constantes_normativas, modelos, M2, M8 y tolerancias, y ninguno vuelve a MD. Sustituir una premisa falsa por otra no cierra el hallazgo: le cambia el hecho. Ademas la premisa original sobrevivia VERBATIM en el docstring de tests/test_MD.py, remitiendo a un parrafo de MD que ya no dice eso. Corregidas las dos, con la razon que si se sostiene, y con guardia: test_la_premisa_de_que_M5_no_existe_no_vuelve_como_afirmacion mira los docstrings POR AST y admite la mencion solo cuando el parrafo la declara caducada --- la leccion de FACTOR_MURO_TABLA.</t>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa. || S19 — REABIERTO Y VUELTO A CERRAR, porque estaba cerrado solo en su letra. La premisa falsa «M5 todavia no existe en el repositorio» se habia retirado de MD.py y sustituido por otra razon --- «la importacion perezosa evita ademas un ciclo de importacion en el arranque» --- que TAMBIEN ES FALSA: M5 importa criterios_adoptados, constantes_normativas, modelos, M2, M8 y tolerancias, y ninguno vuelve a MD. Sustituir una premisa falsa por otra no cierra el hallazgo: le cambia el hecho. Ademas la premisa original sobrevivia VERBATIM en el docstring de tests/test_MD.py, remitiendo a un parrafo de MD que ya no dice eso. Corregidas las dos, con la razon que si se sostiene, y con guardia: test_la_premisa_de_que_M5_no_existe_no_vuelve_como_afirmacion mira los docstrings POR AST y admite la mencion solo cuando el parrafo la declara caducada --- la leccion de FACTOR_MURO_TABLA. || REFUTADO EN f175fab: el guardian que S19 escribio era VACUO en su mitad de ciclo (partia nodo.module por el punto y se quedaba con 'modulos', su segunda clausula era una tautologia, y solo miraba ImportFrom). Un test verde sobre el comentario, que es el precedente FACTOR_MURO_TABLA cometido en el docstring que lo invoca para presumir de no cometerlo. Reescrito como cierre transitivo sobre Import e ImportFrom; mata el ciclo directo y el indirecto.</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="L182" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — El docstring de `escribir_valor_en_archivo` decia 'reescribe el valor=None' y el patron es `valor=)([^,\n]*)(,)`, que casa con lo que haya: un criterio YA declarado se reescribe por la misma via y el boton de la GUI esta disponible para toda fila. Es DELIBERADO --- corregir un valor adoptado es tan legitimo como declararlo, y obligar a editar el archivo a mano empujaria a saltarse la guardia --- y lo que faltaba era decirlo. Queda escrito ademas lo que la funcion NO toca (etiqueta, justificacion, fuente, sensibilidad, resolucion) y que la GUI lo advierte en su confirmacion.</t>
+          <t>4141fd5 — El docstring de `escribir_valor_en_archivo` decia 'reescribe el valor=None' y el patron es `valor=)([^,\n]*)(,)`, que casa con lo que haya: un criterio YA declarado se reescribe por la misma via y el boton de la GUI esta disponible para toda fila. Es DELIBERADO --- corregir un valor adoptado es tan legitimo como declararlo, y obligar a editar el archivo a mano empujaria a saltarse la guardia --- y lo que faltaba era decirlo. Queda escrito ademas lo que la funcion NO toca (etiqueta, justificacion, fuente, sensibilidad, resolucion) y que la GUI lo advierte en su confirmacion. || REFUTADO Y REABIERTO EN f175fab, y era lo peor cerrado de la sesion. El docstring declaraba «REESCRIBE CUALQUIER VALOR ... es deliberado» y para cuatro criterios --- F_pga, hds5_embocadura_hdpe, diametros_normalizados, D_max_catalogo --- no reescribia: DESTRUIA criterios_adoptados.py dejandolo con SyntaxError y VOLVIA SIN EXCEPCION. El patron se corta en la primera coma y un valor de UNA LINEA con comas quedaba partido. La GUI pintaba «escrito» en verde y, como refresca CRITERIOS en memoria, la corrupcion no aparecia hasta el siguiente arranque. Es el mismo desastre que SIS-F-19 describe para los MULTILINEA, en el hueco que ese test no cubria. Guardia: ast.parse sobre el texto resultante ANTES de escribir, mas dos tests. Y el Tooltip del boton --- lo que lee el USUARIO --- seguia diciendo «Reescribe 'valor=None'»: la correccion habia llegado solo a quien lee el codigo.</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L205" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Comprobado vaciando el valor de los 46 criterios y de todos los datos de sitio: cli.correr devuelve informe sin levantar nada, con 12 bloqueos archivados. Los tres unicos sitios que levantan CriterioPendienteError cuelgan de etapas envueltas por _etapa, de modo que ninguno alcanza el except ErrorProyecto de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md.</t>
+          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Comprobado vaciando el valor de los 46 criterios y de todos los datos de sitio: cli.correr devuelve informe sin levantar nada, con 12 bloqueos archivados. Los tres unicos sitios que levantan CriterioPendienteError cuelgan de etapas envueltas por _etapa, de modo que ninguno alcanza el except ErrorProyecto de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md. || PRECISADO EN f175fab: «[N] imposible» y el censo de lo que corre fuera de `_etapa` eran afirmaciones mas fuertes que el codigo. Sustituidas por lo comprobable.</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="L215" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva.</t>
+          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN f175fab: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia.</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="L219" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — Y EL HALLAZGO SE QUEDABA CORTO, dicho para que no se lea de menos: no era solo que el ejemplo diera las luces sin la salvedad que si lleva el test y con ids del fixture presentados como cruces reales --- es que NO EJECUTABA. Llamaba a `clasificar_puntos` con dos de sus tres argumentos y abortaba en el primer punto con CriterioPendienteError sobre 'umbral_area_quebrada_importante_ha' (reproducido). El bloque Uso nuevo corre y da 71/35/35/None, dice que los ids son del fixture y que la luz no es columna de la Sec. 1.2, y corrige '# detiene los puentes', que describia un efecto que con esas cuatro luces no se produce. Lo fija un test que EXTRAE el bloque del archivo y lo ejecuta, de modo que ejemplo y test no puedan volver a divergir.</t>
+          <t>4141fd5 — Y EL HALLAZGO SE QUEDABA CORTO, dicho para que no se lea de menos: no era solo que el ejemplo diera las luces sin la salvedad que si lleva el test y con ids del fixture presentados como cruces reales --- es que NO EJECUTABA. Llamaba a `clasificar_puntos` con dos de sus tres argumentos y abortaba en el primer punto con CriterioPendienteError sobre 'umbral_area_quebrada_importante_ha' (reproducido). El bloque Uso nuevo corre y da 71/35/35/None, dice que los ids son del fixture y que la luz no es columna de la Sec. 1.2, y corrige '# detiene los puentes', que describia un efecto que con esas cuatro luces no se produce. Lo fija un test que EXTRAE el bloque del archivo y lo ejecuta, de modo que ejemplo y test no puedan volver a divergir. || PRECISADO EN f175fab: la razon escrita al cerrarlo --- «los otros doce bloques Uso son fragmentos a proposito» --- era FALSA; los de M0_carga y M10_espaciamiento corren enteros. Es el mismo defecto que la ficha denuncia, cometido al cerrarla. Hoy la suite EJECUTA los tres que se sostienen solos y un segundo test hace crecer la lista si alguien arregla otro.</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="L238" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — EL BARRIDO QUE LA FICHA PEDIA, HECHO, y el hueco del test cerrado por cambio de diseño. La ficha decia que la tasa entre las no ancladas era DESCONOCIDA: medida, era mala. De 68 referencias no ancladas, 16 llevaban a un sitio que no habla de lo que la fila dice --- entre ellas `e2_volteo()` y `empuje_flotacion()`, nombres que el codigo ya no tiene, y ESPACIAMIENTO_MAX_VECES_ESPESOR apuntando al bloque de `n_s_zapata_en_talud` --- y de las 32 restantes sin identificador, 27 tambien. Todas verificadas LEYENDO la linea de destino y reparadas. EL CAMBIO DE DISEÑO: «de prosa» mezclaba dos poblaciones, la fila que no nombra nada (hueco real) y la que nombra un simbolo que el archivo USA sin definir (verificable). Separadas: `test_toda_fila_que_cita_un_identificador_lo_nombra_en_su_destino`, SIN CUPO. Ademas: `_simbolos_citados` devuelve la cola punteada (`M9.cuantia_de_diseno`) y filtra ids de ficha --- eso solo destapo 4 desviadas ---; el resincronizador aprende a mantener las referencias por mencion; y se retiran 40 etiquetas con rango IMPOSIBLE (`[CN:170-49]`), defecto nunca reportado que nacia de reescribir el inicio conservando el final viejo. RESULTADO: 326 referencias = 299 por simbolo + 25 por mencion + 2 sin identificador (las dos legitimas, a docstring de modulo), 0 rotas. Cupos bajados 82-&gt;27 y 33-&gt;2, cobertura verificable del 99 %.</t>
+          <t>4141fd5 — EL BARRIDO QUE LA FICHA PEDIA, HECHO, y el hueco del test cerrado por cambio de diseño. La ficha decia que la tasa entre las no ancladas era DESCONOCIDA: medida, era mala. De 68 referencias no ancladas, 16 llevaban a un sitio que no habla de lo que la fila dice --- entre ellas `e2_volteo()` y `empuje_flotacion()`, nombres que el codigo ya no tiene, y ESPACIAMIENTO_MAX_VECES_ESPESOR apuntando al bloque de `n_s_zapata_en_talud` --- y de las 32 restantes sin identificador, 27 tambien. Todas verificadas LEYENDO la linea de destino y reparadas. EL CAMBIO DE DISEÑO: «de prosa» mezclaba dos poblaciones, la fila que no nombra nada (hueco real) y la que nombra un simbolo que el archivo USA sin definir (verificable). Separadas: `test_toda_fila_que_cita_un_identificador_lo_nombra_en_su_destino`, SIN CUPO. Ademas: `_simbolos_citados` devuelve la cola punteada (`M9.cuantia_de_diseno`) y filtra ids de ficha --- eso solo destapo 4 desviadas ---; el resincronizador aprende a mantener las referencias por mencion; y se retiran 40 etiquetas con rango IMPOSIBLE (`[CN:170-49]`), defecto nunca reportado que nacia de reescribir el inicio conservando el final viejo. RESULTADO: 326 referencias = 299 por simbolo + 25 por mencion + 2 sin identificador (las dos legitimas, a docstring de modulo), 0 rotas. Cupos bajados 82-&gt;27 y 33-&gt;2, cobertura verificable del 99 %. || PRECISADO EN f175fab tras la refutacion, en tres cosas. (1) LAS CIFRAS ERAN OTRAS: medido con la regla final sobre f56360c, eran 20 rotas de 64 no ancladas (no 16 de 68) y 50 etiquetas con rango imposible (no 40 ni 48). (2) LA GUARDIA NUEVA SE SATISFACIA SOLA: comprobaba el BLOQUE, y seis referencias saboteadas --- una a OTRO ARCHIVO, otra a 2900 lineas de su uso --- pasaban con la suite en verde. Ahora comprueba EL PARRAFO DE LLEGADA y el resincronizador ancla al RENGLON, no al bloque; ademas se descartan los tokens que no son simbolos del proyecto (`py`, cola de un backtick `constantes_normativas.py`, hacia de comodin). (3) UNA REPARACION HABIA CAMBIADO UNA REFERENCIA ROTA POR OTRA: la fila de GAMMA_AGUA_KN_M3 aterrizaba en G_LAUSHEY_ATRIBUCION y la salvaba un comentario que dice que el simbolo NO esta ahi. Reapuntada a constantes_fisicas.py, y la fila corregida ademas de fondo: dejo de ser [N].</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe</t>
+          <t>3ea627c + 7266bfe || S19c: la guardia que S19 le puso en la GUI era VERDE SOBRE LA MENCION del simbolo. `test_la_tabla_de_criterios_muestra_el_valor_efectivo_y_no_lo_recalcula` solo comprobaba que `ca.criterio_efectivo` apareciera como llamada en el AST, de modo que el hallazgo se reabria dejando la llamada en su sitio y leyendo el valor del ARCHIVO: la fila quedaba rotulada «declarado (corrida)» y con «(sin declarar)» en su columna de valor --- contradiciendose en pantalla --- y la suite entera en verde. Ahora se sigue el DATO: que nombre recibe `criterio_efectivo(...).valor` y que ese nombre entre en el `values=` del `insert`. El estado no cambia (sigue Cerrado desde S2); lo que cambia es que ahora esta defendido.</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial.</t>
+          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: `predimensionamiento_cabezal` sigue siendo vacio declarado (valor=None, [A]), de modo que el diferimiento sigue vigente por la misma causa que en S10 y S12. La logica sigue corregida (ESPESOR_DOS_CAPAS_REFUERZO + M9.requiere_refuerzo_dos_capas) y la funcion esta censada en M9_cabezal.FUNCIONES_SIN_CONSUMIDOR con su razon. QUE FALTA, escrito ya en docs/decisiones_diferidas.md: que el proyectista declare el predimensionamiento Y que `diseno_flexion_corte` deje de detenerse en NotImplementedError. Ninguna de las dos es trabajo documental: NO se cierra en F5.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: `predimensionamiento_cabezal` sigue siendo vacio declarado (valor=None, [A]), de modo que el diferimiento sigue vigente por la misma causa que en S10 y S12. La logica sigue corregida (ESPESOR_DOS_CAPAS_REFUERZO + M9.requiere_refuerzo_dos_capas) y la funcion esta censada en M9_cabezal.FUNCIONES_SIN_CONSUMIDOR con su razon. QUE FALTA, escrito ya en docs/decisiones_diferidas.md: que el proyectista declare el predimensionamiento Y que `diseno_flexion_corte` deje de detenerse en NotImplementedError. Ninguna de las dos es trabajo documental: NO se cierra en F5. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA.</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA.</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA.</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: la comparacion que la ficha reclama sigue DECLARADA en 'hds5_embocadura_hdpe' --- la fila alternativa ('Circular CM / Headwall') en `sensibilidad`, y `verificacion_pendiente` diciendo con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila, y es decision, no omision: la adopcion se sostiene en el perfil de pared en la boca --- argumento fisico que la ficha no refuta ---, no en un margen de seguridad. QUE FALTA: el detalle constructivo de la embocadura, que es contenido de planos. NO se cierra en F5.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: la comparacion que la ficha reclama sigue DECLARADA en 'hds5_embocadura_hdpe' --- la fila alternativa ('Circular CM / Headwall') en `sensibilidad`, y `verificacion_pendiente` diciendo con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila, y es decision, no omision: la adopcion se sostiene en el perfil de pared en la boca --- argumento fisico que la ficha no refuta ---, no en un margen de seguridad. QUE FALTA: el detalle constructivo de la embocadura, que es contenido de planos. NO se cierra en F5. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA.</t>
         </is>
       </c>
     </row>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="L177" s="6" t="inlineStr">
         <is>
-          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa. || S19 — REABIERTO Y VUELTO A CERRAR, porque estaba cerrado solo en su letra. La premisa falsa «M5 todavia no existe en el repositorio» se habia retirado de MD.py y sustituido por otra razon --- «la importacion perezosa evita ademas un ciclo de importacion en el arranque» --- que TAMBIEN ES FALSA: M5 importa criterios_adoptados, constantes_normativas, modelos, M2, M8 y tolerancias, y ninguno vuelve a MD. Sustituir una premisa falsa por otra no cierra el hallazgo: le cambia el hecho. Ademas la premisa original sobrevivia VERBATIM en el docstring de tests/test_MD.py, remitiendo a un parrafo de MD que ya no dice eso. Corregidas las dos, con la razon que si se sostiene, y con guardia: test_la_premisa_de_que_M5_no_existe_no_vuelve_como_afirmacion mira los docstrings POR AST y admite la mencion solo cuando el parrafo la declara caducada --- la leccion de FACTOR_MURO_TABLA. || REFUTADO EN f175fab: el guardian que S19 escribio era VACUO en su mitad de ciclo (partia nodo.module por el punto y se quedaba con 'modulos', su segunda clausula era una tautologia, y solo miraba ImportFrom). Un test verde sobre el comentario, que es el precedente FACTOR_MURO_TABLA cometido en el docstring que lo invoca para presumir de no cometerlo. Reescrito como cierre transitivo sobre Import e ImportFrom; mata el ciclo directo y el indirecto.</t>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa. || S19 — REABIERTO Y VUELTO A CERRAR, porque estaba cerrado solo en su letra. La premisa falsa «M5 todavia no existe en el repositorio» se habia retirado de MD.py y sustituido por otra razon --- «la importacion perezosa evita ademas un ciclo de importacion en el arranque» --- que TAMBIEN ES FALSA: M5 importa criterios_adoptados, constantes_normativas, modelos, M2, M8 y tolerancias, y ninguno vuelve a MD. Sustituir una premisa falsa por otra no cierra el hallazgo: le cambia el hecho. Ademas la premisa original sobrevivia VERBATIM en el docstring de tests/test_MD.py, remitiendo a un parrafo de MD que ya no dice eso. Corregidas las dos, con la razon que si se sostiene, y con guardia: test_la_premisa_de_que_M5_no_existe_no_vuelve_como_afirmacion mira los docstrings POR AST y admite la mencion solo cuando el parrafo la declara caducada --- la leccion de FACTOR_MURO_TABLA. || REFUTADO EN 6b70481: el guardian que S19 escribio era VACUO en su mitad de ciclo (partia nodo.module por el punto y se quedaba con 'modulos', su segunda clausula era una tautologia, y solo miraba ImportFrom). Un test verde sobre el comentario, que es el precedente FACTOR_MURO_TABLA cometido en el docstring que lo invoca para presumir de no cometerlo. Reescrito como cierre transitivo sobre Import e ImportFrom; mata el ciclo directo y el indirecto. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="L182" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — El docstring de `escribir_valor_en_archivo` decia 'reescribe el valor=None' y el patron es `valor=)([^,\n]*)(,)`, que casa con lo que haya: un criterio YA declarado se reescribe por la misma via y el boton de la GUI esta disponible para toda fila. Es DELIBERADO --- corregir un valor adoptado es tan legitimo como declararlo, y obligar a editar el archivo a mano empujaria a saltarse la guardia --- y lo que faltaba era decirlo. Queda escrito ademas lo que la funcion NO toca (etiqueta, justificacion, fuente, sensibilidad, resolucion) y que la GUI lo advierte en su confirmacion. || REFUTADO Y REABIERTO EN f175fab, y era lo peor cerrado de la sesion. El docstring declaraba «REESCRIBE CUALQUIER VALOR ... es deliberado» y para cuatro criterios --- F_pga, hds5_embocadura_hdpe, diametros_normalizados, D_max_catalogo --- no reescribia: DESTRUIA criterios_adoptados.py dejandolo con SyntaxError y VOLVIA SIN EXCEPCION. El patron se corta en la primera coma y un valor de UNA LINEA con comas quedaba partido. La GUI pintaba «escrito» en verde y, como refresca CRITERIOS en memoria, la corrupcion no aparecia hasta el siguiente arranque. Es el mismo desastre que SIS-F-19 describe para los MULTILINEA, en el hueco que ese test no cubria. Guardia: ast.parse sobre el texto resultante ANTES de escribir, mas dos tests. Y el Tooltip del boton --- lo que lee el USUARIO --- seguia diciendo «Reescribe 'valor=None'»: la correccion habia llegado solo a quien lee el codigo.</t>
+          <t>4141fd5 — El docstring de `escribir_valor_en_archivo` decia 'reescribe el valor=None' y el patron es `valor=)([^,\n]*)(,)`, que casa con lo que haya: un criterio YA declarado se reescribe por la misma via y el boton de la GUI esta disponible para toda fila. Es DELIBERADO --- corregir un valor adoptado es tan legitimo como declararlo, y obligar a editar el archivo a mano empujaria a saltarse la guardia --- y lo que faltaba era decirlo. Queda escrito ademas lo que la funcion NO toca (etiqueta, justificacion, fuente, sensibilidad, resolucion) y que la GUI lo advierte en su confirmacion. || REFUTADO Y REABIERTO EN 6b70481, y era lo peor cerrado de la sesion. El docstring declaraba «REESCRIBE CUALQUIER VALOR ... es deliberado» y para cuatro criterios --- F_pga, hds5_embocadura_hdpe, diametros_normalizados, D_max_catalogo --- no reescribia: DESTRUIA criterios_adoptados.py dejandolo con SyntaxError y VOLVIA SIN EXCEPCION. El patron se corta en la primera coma y un valor de UNA LINEA con comas quedaba partido. La GUI pintaba «escrito» en verde y, como refresca CRITERIOS en memoria, la corrupcion no aparecia hasta el siguiente arranque. Es el mismo desastre que SIS-F-19 describe para los MULTILINEA, en el hueco que ese test no cubria. Guardia: ast.parse sobre el texto resultante ANTES de escribir, mas dos tests. Y el Tooltip del boton --- lo que lee el USUARIO --- seguia diciendo «Reescribe 'valor=None'»: la correccion habia llegado solo a quien lee el codigo. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L205" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Comprobado vaciando el valor de los 46 criterios y de todos los datos de sitio: cli.correr devuelve informe sin levantar nada, con 12 bloqueos archivados. Los tres unicos sitios que levantan CriterioPendienteError cuelgan de etapas envueltas por _etapa, de modo que ninguno alcanza el except ErrorProyecto de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md. || PRECISADO EN f175fab: «[N] imposible» y el censo de lo que corre fuera de `_etapa` eran afirmaciones mas fuertes que el codigo. Sustituidas por lo comprobable.</t>
+          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Comprobado vaciando el valor de los 46 criterios y de todos los datos de sitio: cli.correr devuelve informe sin levantar nada, con 12 bloqueos archivados. Los tres unicos sitios que levantan CriterioPendienteError cuelgan de etapas envueltas por _etapa, de modo que ninguno alcanza el except ErrorProyecto de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md. || PRECISADO EN 6b70481: «[N] imposible» y el censo de lo que corre fuera de `_etapa` eran afirmaciones mas fuertes que el codigo. Sustituidas por lo comprobable. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="L215" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN f175fab: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia.</t>
+          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN 6b70481: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="L219" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — Y EL HALLAZGO SE QUEDABA CORTO, dicho para que no se lea de menos: no era solo que el ejemplo diera las luces sin la salvedad que si lleva el test y con ids del fixture presentados como cruces reales --- es que NO EJECUTABA. Llamaba a `clasificar_puntos` con dos de sus tres argumentos y abortaba en el primer punto con CriterioPendienteError sobre 'umbral_area_quebrada_importante_ha' (reproducido). El bloque Uso nuevo corre y da 71/35/35/None, dice que los ids son del fixture y que la luz no es columna de la Sec. 1.2, y corrige '# detiene los puentes', que describia un efecto que con esas cuatro luces no se produce. Lo fija un test que EXTRAE el bloque del archivo y lo ejecuta, de modo que ejemplo y test no puedan volver a divergir. || PRECISADO EN f175fab: la razon escrita al cerrarlo --- «los otros doce bloques Uso son fragmentos a proposito» --- era FALSA; los de M0_carga y M10_espaciamiento corren enteros. Es el mismo defecto que la ficha denuncia, cometido al cerrarla. Hoy la suite EJECUTA los tres que se sostienen solos y un segundo test hace crecer la lista si alguien arregla otro.</t>
+          <t>4141fd5 — Y EL HALLAZGO SE QUEDABA CORTO, dicho para que no se lea de menos: no era solo que el ejemplo diera las luces sin la salvedad que si lleva el test y con ids del fixture presentados como cruces reales --- es que NO EJECUTABA. Llamaba a `clasificar_puntos` con dos de sus tres argumentos y abortaba en el primer punto con CriterioPendienteError sobre 'umbral_area_quebrada_importante_ha' (reproducido). El bloque Uso nuevo corre y da 71/35/35/None, dice que los ids son del fixture y que la luz no es columna de la Sec. 1.2, y corrige '# detiene los puentes', que describia un efecto que con esas cuatro luces no se produce. Lo fija un test que EXTRAE el bloque del archivo y lo ejecuta, de modo que ejemplo y test no puedan volver a divergir. || PRECISADO EN 6b70481: la razon escrita al cerrarlo --- «los otros doce bloques Uso son fragmentos a proposito» --- era FALSA; los de M0_carga y M10_espaciamiento corren enteros. Es el mismo defecto que la ficha denuncia, cometido al cerrarla. Hoy la suite EJECUTA los tres que se sostienen solos y un segundo test hace crecer la lista si alguien arregla otro. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
         </is>
       </c>
     </row>
@@ -15595,7 +15595,11 @@
           <t>MEDIA</t>
         </is>
       </c>
-      <c r="E238" s="6" t="n"/>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
           <t>F5</t>
@@ -15631,7 +15635,7 @@
       </c>
       <c r="L238" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — EL BARRIDO QUE LA FICHA PEDIA, HECHO, y el hueco del test cerrado por cambio de diseño. La ficha decia que la tasa entre las no ancladas era DESCONOCIDA: medida, era mala. De 68 referencias no ancladas, 16 llevaban a un sitio que no habla de lo que la fila dice --- entre ellas `e2_volteo()` y `empuje_flotacion()`, nombres que el codigo ya no tiene, y ESPACIAMIENTO_MAX_VECES_ESPESOR apuntando al bloque de `n_s_zapata_en_talud` --- y de las 32 restantes sin identificador, 27 tambien. Todas verificadas LEYENDO la linea de destino y reparadas. EL CAMBIO DE DISEÑO: «de prosa» mezclaba dos poblaciones, la fila que no nombra nada (hueco real) y la que nombra un simbolo que el archivo USA sin definir (verificable). Separadas: `test_toda_fila_que_cita_un_identificador_lo_nombra_en_su_destino`, SIN CUPO. Ademas: `_simbolos_citados` devuelve la cola punteada (`M9.cuantia_de_diseno`) y filtra ids de ficha --- eso solo destapo 4 desviadas ---; el resincronizador aprende a mantener las referencias por mencion; y se retiran 40 etiquetas con rango IMPOSIBLE (`[CN:170-49]`), defecto nunca reportado que nacia de reescribir el inicio conservando el final viejo. RESULTADO: 326 referencias = 299 por simbolo + 25 por mencion + 2 sin identificador (las dos legitimas, a docstring de modulo), 0 rotas. Cupos bajados 82-&gt;27 y 33-&gt;2, cobertura verificable del 99 %. || PRECISADO EN f175fab tras la refutacion, en tres cosas. (1) LAS CIFRAS ERAN OTRAS: medido con la regla final sobre f56360c, eran 20 rotas de 64 no ancladas (no 16 de 68) y 50 etiquetas con rango imposible (no 40 ni 48). (2) LA GUARDIA NUEVA SE SATISFACIA SOLA: comprobaba el BLOQUE, y seis referencias saboteadas --- una a OTRO ARCHIVO, otra a 2900 lineas de su uso --- pasaban con la suite en verde. Ahora comprueba EL PARRAFO DE LLEGADA y el resincronizador ancla al RENGLON, no al bloque; ademas se descartan los tokens que no son simbolos del proyecto (`py`, cola de un backtick `constantes_normativas.py`, hacia de comodin). (3) UNA REPARACION HABIA CAMBIADO UNA REFERENCIA ROTA POR OTRA: la fila de GAMMA_AGUA_KN_M3 aterrizaba en G_LAUSHEY_ATRIBUCION y la salvaba un comentario que dice que el simbolo NO esta ahi. Reapuntada a constantes_fisicas.py, y la fila corregida ademas de fondo: dejo de ser [N].</t>
+          <t>4141fd5 — EL BARRIDO QUE LA FICHA PEDIA, HECHO, y el hueco del test cerrado por cambio de diseño. La ficha decia que la tasa entre las no ancladas era DESCONOCIDA: medida, era mala. De 68 referencias no ancladas, 16 llevaban a un sitio que no habla de lo que la fila dice --- entre ellas `e2_volteo()` y `empuje_flotacion()`, nombres que el codigo ya no tiene, y ESPACIAMIENTO_MAX_VECES_ESPESOR apuntando al bloque de `n_s_zapata_en_talud` --- y de las 32 restantes sin identificador, 27 tambien. Todas verificadas LEYENDO la linea de destino y reparadas. EL CAMBIO DE DISEÑO: «de prosa» mezclaba dos poblaciones, la fila que no nombra nada (hueco real) y la que nombra un simbolo que el archivo USA sin definir (verificable). Separadas: `test_toda_fila_que_cita_un_identificador_lo_nombra_en_su_destino`, SIN CUPO. Ademas: `_simbolos_citados` devuelve la cola punteada (`M9.cuantia_de_diseno`) y filtra ids de ficha --- eso solo destapo 4 desviadas ---; el resincronizador aprende a mantener las referencias por mencion; y se retiran 40 etiquetas con rango IMPOSIBLE (`[CN:170-49]`), defecto nunca reportado que nacia de reescribir el inicio conservando el final viejo. RESULTADO: 326 referencias = 299 por simbolo + 25 por mencion + 2 sin identificador (las dos legitimas, a docstring de modulo), 0 rotas. Cupos bajados 82-&gt;27 y 33-&gt;2, cobertura verificable del 99 %. || PRECISADO EN 6b70481 tras la refutacion, en tres cosas. (1) LAS CIFRAS ERAN OTRAS: medido con la regla final sobre f56360c, eran 20 rotas de 64 no ancladas (no 16 de 68) y 50 etiquetas con rango imposible (no 40 ni 48). (2) LA GUARDIA NUEVA SE SATISFACIA SOLA: comprobaba el BLOQUE, y seis referencias saboteadas --- una a OTRO ARCHIVO, otra a 2900 lineas de su uso --- pasaban con la suite en verde. Ahora comprueba EL PARRAFO DE LLEGADA y el resincronizador ancla al RENGLON, no al bloque; ademas se descartan los tokens que no son simbolos del proyecto (`py`, cola de un backtick `constantes_normativas.py`, hacia de comodin). (3) UNA REPARACION HABIA CAMBIADO UNA REFERENCIA ROTA POR OTRA: la fila de GAMMA_AGUA_KN_M3 aterrizaba en G_LAUSHEY_ATRIBUCION y la salvaba un comentario que dice que el simbolo NO esta ahi. Reapuntada a constantes_fisicas.py, y la fila corregida ademas de fondo: dejo de ser [N]. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -12162,7 +12162,7 @@
       </c>
       <c r="L177" s="6" t="inlineStr">
         <is>
-          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa. || S19 — REABIERTO Y VUELTO A CERRAR, porque estaba cerrado solo en su letra. La premisa falsa «M5 todavia no existe en el repositorio» se habia retirado de MD.py y sustituido por otra razon --- «la importacion perezosa evita ademas un ciclo de importacion en el arranque» --- que TAMBIEN ES FALSA: M5 importa criterios_adoptados, constantes_normativas, modelos, M2, M8 y tolerancias, y ninguno vuelve a MD. Sustituir una premisa falsa por otra no cierra el hallazgo: le cambia el hecho. Ademas la premisa original sobrevivia VERBATIM en el docstring de tests/test_MD.py, remitiendo a un parrafo de MD que ya no dice eso. Corregidas las dos, con la razon que si se sostiene, y con guardia: test_la_premisa_de_que_M5_no_existe_no_vuelve_como_afirmacion mira los docstrings POR AST y admite la mencion solo cuando el parrafo la declara caducada --- la leccion de FACTOR_MURO_TABLA. || REFUTADO EN 6b70481: el guardian que S19 escribio era VACUO en su mitad de ciclo (partia nodo.module por el punto y se quedaba con 'modulos', su segunda clausula era una tautologia, y solo miraba ImportFrom). Un test verde sobre el comentario, que es el precedente FACTOR_MURO_TABLA cometido en el docstring que lo invoca para presumir de no cometerlo. Reescrito como cierre transitivo sobre Import e ImportFrom; mata el ciclo directo y el indirecto. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
+          <t>a227cb9+e3f36df+f1b40b2+9822880 — [C11/F5, de paso] retirada del docstring de MD la premisa «M5 todavia no existe en el repositorio», que era falsa y sostenia la justificacion del Protocol y de la importacion perezosa. || S19 — REABIERTO Y VUELTO A CERRAR, porque estaba cerrado solo en su letra. La premisa falsa «M5 todavia no existe en el repositorio» se habia retirado de MD.py y sustituido por otra razon --- «la importacion perezosa evita ademas un ciclo de importacion en el arranque» --- que TAMBIEN ES FALSA: M5 importa criterios_adoptados, constantes_normativas, modelos, M2, M8 y tolerancias, y ninguno vuelve a MD. Sustituir una premisa falsa por otra no cierra el hallazgo: le cambia el hecho. Ademas la premisa original sobrevivia VERBATIM en el docstring de tests/test_MD.py, remitiendo a un parrafo de MD que ya no dice eso. Corregidas las dos, con la razon que si se sostiene, y con guardia: test_la_premisa_de_que_M5_no_existe_no_vuelve_como_afirmacion mira los docstrings POR AST y admite la mencion solo cuando el parrafo la declara caducada --- la leccion de FACTOR_MURO_TABLA. || REFUTADO EN 6b70481: el guardian que S19 escribio era VACUO en su mitad de ciclo (partia nodo.module por el punto y se quedaba con 'modulos', su segunda clausula era una tautologia, y solo miraba ImportFrom). Un test verde sobre el comentario, que es el precedente FACTOR_MURO_TABLA cometido en el docstring que lo invoca para presumir de no cometerlo. Reescrito como cierre transitivo sobre Import e ImportFrom; mata el ciclo directo y el indirecto. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4.</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="L182" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — El docstring de `escribir_valor_en_archivo` decia 'reescribe el valor=None' y el patron es `valor=)([^,\n]*)(,)`, que casa con lo que haya: un criterio YA declarado se reescribe por la misma via y el boton de la GUI esta disponible para toda fila. Es DELIBERADO --- corregir un valor adoptado es tan legitimo como declararlo, y obligar a editar el archivo a mano empujaria a saltarse la guardia --- y lo que faltaba era decirlo. Queda escrito ademas lo que la funcion NO toca (etiqueta, justificacion, fuente, sensibilidad, resolucion) y que la GUI lo advierte en su confirmacion. || REFUTADO Y REABIERTO EN 6b70481, y era lo peor cerrado de la sesion. El docstring declaraba «REESCRIBE CUALQUIER VALOR ... es deliberado» y para cuatro criterios --- F_pga, hds5_embocadura_hdpe, diametros_normalizados, D_max_catalogo --- no reescribia: DESTRUIA criterios_adoptados.py dejandolo con SyntaxError y VOLVIA SIN EXCEPCION. El patron se corta en la primera coma y un valor de UNA LINEA con comas quedaba partido. La GUI pintaba «escrito» en verde y, como refresca CRITERIOS en memoria, la corrupcion no aparecia hasta el siguiente arranque. Es el mismo desastre que SIS-F-19 describe para los MULTILINEA, en el hueco que ese test no cubria. Guardia: ast.parse sobre el texto resultante ANTES de escribir, mas dos tests. Y el Tooltip del boton --- lo que lee el USUARIO --- seguia diciendo «Reescribe 'valor=None'»: la correccion habia llegado solo a quien lee el codigo. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
+          <t>4141fd5 — El docstring de `escribir_valor_en_archivo` decia 'reescribe el valor=None' y el patron es `valor=)([^,\n]*)(,)`, que casa con lo que haya: un criterio YA declarado se reescribe por la misma via y el boton de la GUI esta disponible para toda fila. Es DELIBERADO --- corregir un valor adoptado es tan legitimo como declararlo, y obligar a editar el archivo a mano empujaria a saltarse la guardia --- y lo que faltaba era decirlo. Queda escrito ademas lo que la funcion NO toca (etiqueta, justificacion, fuente, sensibilidad, resolucion) y que la GUI lo advierte en su confirmacion. || REFUTADO Y REABIERTO EN 6b70481, y era lo peor cerrado de la sesion. El docstring declaraba «REESCRIBE CUALQUIER VALOR ... es deliberado» y para cuatro criterios --- F_pga, hds5_embocadura_hdpe, diametros_normalizados, D_max_catalogo --- no reescribia: DESTRUIA criterios_adoptados.py dejandolo con SyntaxError y VOLVIA SIN EXCEPCION. El patron se corta en la primera coma y un valor de UNA LINEA con comas quedaba partido. La GUI pintaba «escrito» en verde y, como refresca CRITERIOS en memoria, la corrupcion no aparecia hasta el siguiente arranque. Es el mismo desastre que SIS-F-19 describe para los MULTILINEA, en el hueco que ese test no cubria. Guardia: ast.parse sobre el texto resultante ANTES de escribir, mas dos tests. Y el Tooltip del boton --- lo que lee el USUARIO --- seguia diciendo «Reescribe 'valor=None'»: la correccion habia llegado solo a quien lee el codigo. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4.</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="L205" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Comprobado vaciando el valor de los 46 criterios y de todos los datos de sitio: cli.correr devuelve informe sin levantar nada, con 12 bloqueos archivados. Los tres unicos sitios que levantan CriterioPendienteError cuelgan de etapas envueltas por _etapa, de modo que ninguno alcanza el except ErrorProyecto de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md. || PRECISADO EN 6b70481: «[N] imposible» y el censo de lo que corre fuera de `_etapa` eran afirmaciones mas fuertes que el codigo. Sustituidas por lo comprobable. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
+          <t>4141fd5 — CONSERVADO con su razon escrita, y la razon es mas fuerte que 'la otra via es mas rica': la via del `Bloqueo` es la UNICA. Comprobado vaciando el valor de los 46 criterios y de todos los datos de sitio: cli.correr devuelve informe sin levantar nada, con 12 bloqueos archivados. Los tres unicos sitios que levantan CriterioPendienteError cuelgan de etapas envueltas por _etapa, de modo que ninguno alcanza el except ErrorProyecto de la ventana. El docstring afirmaba un estado falso ('Texto que la GUI muestra al usuario') y se reescribio. DEFECTO CONTRA CLAUDE.md CORREGIDO: su clausula decia que la GUI muestra 'falta declarar: &lt;clave&gt;' y la GUI pinta seis columnas por `M11.criterios_bloqueantes`. Ficha en docs/decisiones_diferidas.md. || PRECISADO EN 6b70481: «[N] imposible» y el censo de lo que corre fuera de `_etapa` eran afirmaciones mas fuertes que el codigo. Sustituidas por lo comprobable. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4.</t>
         </is>
       </c>
     </row>
@@ -14363,7 +14363,7 @@
       </c>
       <c r="L215" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN 6b70481: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
+          <t>4141fd5 — La ficha esta obsoleta en LA MITAD de su acusacion --- «no se emite ni al JSON ni al HTML» --- y la otra mitad sigue viva. Al HTML SI llega: `ahogado_por_TW` SI tiene lector de produccion y SI llega a la memoria desde S18 (f865969), dentro del PasoDeMemoria de h_o que emite `M4._pasos_hidraulicos` --- «(manda TW: la salida esta ahogada)» frente a «(manda la aproximacion geometrica)» ---. Se cerro solo, sin que nadie marcara el hallazgo. S19 lo verifica ejecutando las dos ramas, lo escribe en el docstring de `ControlSalida` y lo FIJA con un test sobre el TEXTO RENDERIZADO, no sobre el booleano: hasta ahora el campo asomaba al entregable por una sola frase y nada la protegia. AL JSON NO LLEGA, y eso no se cierra aqui: no llega ninguna pieza del bloque h_o (`grep -n 'h_o' cli.py` esta vacio), ni siquiera los dos flags de condicion de uso. Publicar la etiqueta de la rama sin h_o, TW ni la aproximacion geometrica daria al lector del JSON un veredicto sin los dos numeros que lo producen, que es menos revisable que no publicar nada. Abrir el JSON al bloque h_o ENTERO es una decision propia y no parte de SIS-B-18. Los otros cuatro campos siguen con su decision escrita, como la ficha reconoce. HALLAZGO NUEVO ABIERTO DE PASO: `M9_cabezal.combinaciones()` afirmaba en su docstring que 'M11 la usa' y M11 no la referencia --- corregido, con la razon de por que se conserva. || PRECISADO EN 6b70481: al JSON NO llega, y el cierre anterior daba la ficha por obsoleta entera. Se declara que abrir el JSON al bloque h_o completo es decision propia. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4.</t>
         </is>
       </c>
     </row>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="L219" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — Y EL HALLAZGO SE QUEDABA CORTO, dicho para que no se lea de menos: no era solo que el ejemplo diera las luces sin la salvedad que si lleva el test y con ids del fixture presentados como cruces reales --- es que NO EJECUTABA. Llamaba a `clasificar_puntos` con dos de sus tres argumentos y abortaba en el primer punto con CriterioPendienteError sobre 'umbral_area_quebrada_importante_ha' (reproducido). El bloque Uso nuevo corre y da 71/35/35/None, dice que los ids son del fixture y que la luz no es columna de la Sec. 1.2, y corrige '# detiene los puentes', que describia un efecto que con esas cuatro luces no se produce. Lo fija un test que EXTRAE el bloque del archivo y lo ejecuta, de modo que ejemplo y test no puedan volver a divergir. || PRECISADO EN 6b70481: la razon escrita al cerrarlo --- «los otros doce bloques Uso son fragmentos a proposito» --- era FALSA; los de M0_carga y M10_espaciamiento corren enteros. Es el mismo defecto que la ficha denuncia, cometido al cerrarla. Hoy la suite EJECUTA los tres que se sostienen solos y un segundo test hace crecer la lista si alguien arregla otro. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
+          <t>4141fd5 — Y EL HALLAZGO SE QUEDABA CORTO, dicho para que no se lea de menos: no era solo que el ejemplo diera las luces sin la salvedad que si lleva el test y con ids del fixture presentados como cruces reales --- es que NO EJECUTABA. Llamaba a `clasificar_puntos` con dos de sus tres argumentos y abortaba en el primer punto con CriterioPendienteError sobre 'umbral_area_quebrada_importante_ha' (reproducido). El bloque Uso nuevo corre y da 71/35/35/None, dice que los ids son del fixture y que la luz no es columna de la Sec. 1.2, y corrige '# detiene los puentes', que describia un efecto que con esas cuatro luces no se produce. Lo fija un test que EXTRAE el bloque del archivo y lo ejecuta, de modo que ejemplo y test no puedan volver a divergir. || PRECISADO EN 6b70481: la razon escrita al cerrarlo --- «los otros doce bloques Uso son fragmentos a proposito» --- era FALSA; los de M0_carga y M10_espaciamiento corren enteros. Es el mismo defecto que la ficha denuncia, cometido al cerrarla. Hoy la suite EJECUTA los tres que se sostienen solos y un segundo test hace crecer la lista si alguien arregla otro. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4.</t>
         </is>
       </c>
     </row>
@@ -15635,7 +15635,7 @@
       </c>
       <c r="L238" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — EL BARRIDO QUE LA FICHA PEDIA, HECHO, y el hueco del test cerrado por cambio de diseño. La ficha decia que la tasa entre las no ancladas era DESCONOCIDA: medida, era mala. De 68 referencias no ancladas, 16 llevaban a un sitio que no habla de lo que la fila dice --- entre ellas `e2_volteo()` y `empuje_flotacion()`, nombres que el codigo ya no tiene, y ESPACIAMIENTO_MAX_VECES_ESPESOR apuntando al bloque de `n_s_zapata_en_talud` --- y de las 32 restantes sin identificador, 27 tambien. Todas verificadas LEYENDO la linea de destino y reparadas. EL CAMBIO DE DISEÑO: «de prosa» mezclaba dos poblaciones, la fila que no nombra nada (hueco real) y la que nombra un simbolo que el archivo USA sin definir (verificable). Separadas: `test_toda_fila_que_cita_un_identificador_lo_nombra_en_su_destino`, SIN CUPO. Ademas: `_simbolos_citados` devuelve la cola punteada (`M9.cuantia_de_diseno`) y filtra ids de ficha --- eso solo destapo 4 desviadas ---; el resincronizador aprende a mantener las referencias por mencion; y se retiran 40 etiquetas con rango IMPOSIBLE (`[CN:170-49]`), defecto nunca reportado que nacia de reescribir el inicio conservando el final viejo. RESULTADO: 326 referencias = 299 por simbolo + 25 por mencion + 2 sin identificador (las dos legitimas, a docstring de modulo), 0 rotas. Cupos bajados 82-&gt;27 y 33-&gt;2, cobertura verificable del 99 %. || PRECISADO EN 6b70481 tras la refutacion, en tres cosas. (1) LAS CIFRAS ERAN OTRAS: medido con la regla final sobre f56360c, eran 20 rotas de 64 no ancladas (no 16 de 68) y 50 etiquetas con rango imposible (no 40 ni 48). (2) LA GUARDIA NUEVA SE SATISFACIA SOLA: comprobaba el BLOQUE, y seis referencias saboteadas --- una a OTRO ARCHIVO, otra a 2900 lineas de su uso --- pasaban con la suite en verde. Ahora comprueba EL PARRAFO DE LLEGADA y el resincronizador ancla al RENGLON, no al bloque; ademas se descartan los tokens que no son simbolos del proyecto (`py`, cola de un backtick `constantes_normativas.py`, hacia de comodin). (3) UNA REPARACION HABIA CAMBIADO UNA REFERENCIA ROTA POR OTRA: la fila de GAMMA_AGUA_KN_M3 aterrizaba en G_LAUSHEY_ATRIBUCION y la salvaba un comentario que dice que el simbolo NO esta ahi. Reapuntada a constantes_fisicas.py, y la fila corregida ademas de fondo: dejo de ser [N]. || S19d — SHA CORREGIDO: esta celda citaba `f175fab`, que se escribio ANTES del cherry-pick y quedo huerfano al resetear main; en un clon limpio no existe. `6b70481` es el MISMO arbol (git diff f175fab 6b70481 vacio) y el MISMO mensaje, y SI es ancestro de main (verificado con `git merge-base --is-ancestor`). El mensaje del commit 9c00720 todavia dice «Anotado contra f175fab»: eso vive en el historial y no se reescribe.</t>
+          <t>4141fd5 — EL BARRIDO QUE LA FICHA PEDIA, HECHO, y el hueco del test cerrado por cambio de diseño. La ficha decia que la tasa entre las no ancladas era DESCONOCIDA: medida, era mala. De 68 referencias no ancladas, 16 llevaban a un sitio que no habla de lo que la fila dice --- entre ellas `e2_volteo()` y `empuje_flotacion()`, nombres que el codigo ya no tiene, y ESPACIAMIENTO_MAX_VECES_ESPESOR apuntando al bloque de `n_s_zapata_en_talud` --- y de las 32 restantes sin identificador, 27 tambien. Todas verificadas LEYENDO la linea de destino y reparadas. EL CAMBIO DE DISEÑO: «de prosa» mezclaba dos poblaciones, la fila que no nombra nada (hueco real) y la que nombra un simbolo que el archivo USA sin definir (verificable). Separadas: `test_toda_fila_que_cita_un_identificador_lo_nombra_en_su_destino`, SIN CUPO. Ademas: `_simbolos_citados` devuelve la cola punteada (`M9.cuantia_de_diseno`) y filtra ids de ficha --- eso solo destapo 4 desviadas ---; el resincronizador aprende a mantener las referencias por mencion; y se retiran 40 etiquetas con rango IMPOSIBLE (`[CN:170-49]`), defecto nunca reportado que nacia de reescribir el inicio conservando el final viejo. RESULTADO: 326 referencias = 299 por simbolo + 25 por mencion + 2 sin identificador (las dos legitimas, a docstring de modulo), 0 rotas. Cupos bajados 82-&gt;27 y 33-&gt;2, cobertura verificable del 99 %. || PRECISADO EN 6b70481 tras la refutacion, en tres cosas. (1) LAS CIFRAS ERAN OTRAS: medido con la regla final sobre f56360c, eran 20 rotas de 64 no ancladas (no 16 de 68) y 50 etiquetas con rango imposible (no 40 ni 48). (2) LA GUARDIA NUEVA SE SATISFACIA SOLA: comprobaba el BLOQUE, y seis referencias saboteadas --- una a OTRO ARCHIVO, otra a 2900 lineas de su uso --- pasaban con la suite en verde. Ahora comprueba EL PARRAFO DE LLEGADA y el resincronizador ancla al RENGLON, no al bloque; ademas se descartan los tokens que no son simbolos del proyecto (`py`, cola de un backtick `constantes_normativas.py`, hacia de comodin). (3) UNA REPARACION HABIA CAMBIADO UNA REFERENCIA ROTA POR OTRA: la fila de GAMMA_AGUA_KN_M3 aterrizaba en G_LAUSHEY_ATRIBUCION y la salvaba un comentario que dice que el simbolo NO esta ahi. Reapuntada a constantes_fisicas.py, y la fila corregida ademas de fondo: dejo de ser [N]. || S19d — SHA CORREGIDO. Esta celda citaba el commit de CODIGO de S19b tal como se creo la primera vez: por error estando en `main`, y el texto de la celda se escribio ANTES del cherry-pick que lo llevo a la rama. Al resetear `main` ese commit quedo sin rama, de modo que en un clon limpio NO EXISTE. Su equivalente vivo es 6b70481 --- mismo arbol (`git diff` entre los dos, vacio) y mismo mensaje ---, verificado ancestro de main con `git merge-base --is-ancestor` antes de escribirlo. EL HEX MUERTO NO SE ESCRIBE EN ESTA CELDA, y no es pudor: esta columna es justo lo que lee `verificar_sesion.py`, que no distingue un SHA CITADO de un SHA NOMBRADO de pasada, asi que dejarlo escrito aqui como parte de la explicacion reabre el mismo fallo que la explicacion cierra (probado: 6 fallos se volvieron 20). Regla que queda: en la columna Commit / PR no se escribe un hex que no sea ancestro de main; la arqueologia va al mensaje del commit. Quien necesite el hex muerto lo tiene en el mensaje de 9c00720 («Anotado contra ...») y la correccion entera contada en el de a323bf4.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -7855,12 +7855,12 @@
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S2)</t>
+          <t>Claude Code (fase1, S20)</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe</t>
+          <t>3ea627c + 7266bfe || 3e52483 + 1d4432d — S20 - IMPLEMENTADA. `M5.v2b_sedimentacion` evalua el indicador del HDS-5 3.a ed. num. 5.3.3 'Sedimentation', pag. impresa 5.11 (S_conducto &gt;= S_cauce), con sus dos citas verificadas contra el PDF y su Fundamento F5.V2b. La premisa del diferimiento era falsa: 'la colmatacion no es un calculo con umbral' vale del Manual peruano, no del HDS-5 que este proyecto ya aplica para el control de salida. La mitad [A] -- el acceso de mantenimiento en planos -- dejo de ser un parrafo y es el criterio 'acceso_mantenimiento_v2b', que DETIENE. Once filas, ONCE funciones: `verificaciones_no_evaluadas()` devuelve () y M11 imprime la afirmacion positiva. Queda pendiente el segundo indicador del mismo numeral, que exige el n del cauce natural.</t>
         </is>
       </c>
     </row>
@@ -7975,12 +7975,12 @@
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S2)</t>
+          <t>Claude Code (fase1, S20)</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe</t>
+          <t>3ea627c + 7266bfe || 3e52483 + 1d4432d — S20 - IMPLEMENTADO, no diferido. `M3.tw_seccion_1_3` recorre las CUATRO vias de Sec. 1.3 en orden de precedencia -- TW declarado, columna `cota_TW` (que es el paso 2 resuelto fuera: Tablero 3.1 la rotula 'Calculada (1.3)'), `Q_receptor_m3s` + seccion del receptor (pasos 1 y 2 enteros, Manning trapecial), y los dos escenarios acotados del paso 3 -- y emite el PasoDeMemoria con la via por la que salio el numero. La ficha medida se cierra literalmente: un CSV con `cota_TW` llena ya NO exige --tw. Lo que faltaba y no era esperar: la SECCION del receptor, que no es columna ni la fija norma alguna; entra por el criterio nuevo 'seccion_receptor' [A] con su ventana y su trazabilidad. 'TW_receptor' sigue vacio A PROPOSITO y cambio de papel: es la ultima puerta, la que detiene cuando no hay ni nivel, ni caudal, ni seccion. El defecto se reporto ademas contra la hoja de ruta, en su Sec. 1.3.</t>
         </is>
       </c>
     </row>
@@ -8513,12 +8513,12 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S2)</t>
+          <t>Claude Code (fase1, S20)</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr">
         <is>
-          <t>3ea627c + 7266bfe</t>
+          <t>3ea627c + 7266bfe || 3e52483 + 1d4432d — S20 - Cerrado con SIS-A-13, mismo paquete. V2b ya no 'desaparece en silencio': tiene funcion, numeral, fundamento, cita verificada y fila en la tabla de Fase 5 de cada punto. El riesgo que la ficha nombra -- que los planos omitan el acceso de mantenimiento sin que nada lo recuerde -- queda cerrado por la via mas dura de las dos posibles: el criterio 'acceso_mantenimiento_v2b' detiene la corrida mientras no se declare.</t>
         </is>
       </c>
     </row>

--- a/docs/auditorias/matriz_cruzada_auditorias.xlsx
+++ b/docs/auditorias/matriz_cruzada_auditorias.xlsx
@@ -3911,12 +3911,12 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S19)</t>
+          <t>Claude Code (cierre, I1/I1b)</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: `predimensionamiento_cabezal` sigue siendo vacio declarado (valor=None, [A]), de modo que el diferimiento sigue vigente por la misma causa que en S10 y S12. La logica sigue corregida (ESPESOR_DOS_CAPAS_REFUERZO + M9.requiere_refuerzo_dos_capas) y la funcion esta censada en M9_cabezal.FUNCIONES_SIN_CONSUMIDOR con su razon. QUE FALTA, escrito ya en docs/decisiones_diferidas.md: que el proyectista declare el predimensionamiento Y que `diseno_flexion_corte` deje de detenerse en NotImplementedError. Ninguna de las dos es trabajo documental: NO se cierra en F5. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: `predimensionamiento_cabezal` sigue siendo vacio declarado (valor=None, [A]), de modo que el diferimiento sigue vigente por la misma causa que en S10 y S12. La logica sigue corregida (ESPESOR_DOS_CAPAS_REFUERZO + M9.requiere_refuerzo_dos_capas) y la funcion esta censada en M9_cabezal.FUNCIONES_SIN_CONSUMIDOR con su razon. QUE FALTA, escrito ya en docs/decisiones_diferidas.md: que el proyectista declare el predimensionamiento Y que `diseno_flexion_corte` deje de detenerse en NotImplementedError. Ninguna de las dos es trabajo documental: NO se cierra en F5. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b — I1 — RE-VERIFICADO SIN CAMBIO DE CODIGO: la logica sigue corregida (ESPESOR_DOS_CAPAS_REFUERZO=0.200 + M9.requiere_refuerzo_dos_capas), predimensionamiento_cabezal sigue vacio declarado (valor=None, nivel expediente) y diseno_flexion_corte se detiene en NotImplementedError deliberado y censado. Confirmado por el auditor adversarial en I1b. Veredicto regla 3: NO CIERRA (y no pretende): es contrato de expediente. Sigue Cerrado parcial por la misma causa que S19.</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S19)</t>
+          <t>Claude Code (cierre, I1/I1b)</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: las dos condiciones evaluables lo siguen siendo (H_O_HW_SOBRE_D_MIN y H_O_HW_SOBRE_D_CAUTELA, calculadas en control_salida e impresas en la memoria del punto) y la tercera --- que el barril fluya lleno en la mayor parte de su longitud --- sigue transcrita y DECLARADA como no evaluable en H_O_CONDICION_APLICACION, con M4 diciendolo en el punto de uso. QUE FALTA: el procedimiento de barril parcialmente lleno del Cap. III del HDS-5. Es implementar un metodo hidraulico: NO se cierra en F5. Ficha en docs/decisiones_diferidas.md. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — EVALUADO LO QUE LA FICHA DEJABA POR EVALUAR: el Cap. III del HDS-5 3a ed. SI da el procedimiento de barril parcialmente lleno en forma transcribible, y el paquete de implementacion completo (prosa en 3.12/PDF 94 con la Ec. 3.7; umbrales de 3.24/PDF 106; Secc. 3.5 PDF 116-120; que implementar en M4 y por que M5 no cambia; dorados solo con corrida externa citable, conflicto #7) quedo ESCRITO en el bloque que precede a H_O_CONDICION_APLICACION, sin implementar: toca M4.control_salida, motor validado — es sesion propia con plan mode. Ficha de decisiones_diferidas actualizada. Veredicto regla 3 (auditor adversarial I1b): NO CIERRA y no pretende; el paquete es honesto y no contradice Conflictos. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -6993,12 +6993,12 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S19)</t>
+          <t>Claude Code (cierre, I1/I1b)</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, y la mitad abierta se parte en dos de dificultad distinta, que es lo que faltaba decir. La atribucion sigue corregida (A796/A796M, con A798 para instalacion) y `clases_producto_por_relleno` sigue vacio (verificado: valor=None). (1) La relacion luz/corrugacion de la Tabla 1 de A760 y la Tabla 6 de M 36 SE PUEDE hacer --- las dos fuentes estan en normas/ y S14 dejo comprobado que A760 es legible renderizando su pag. PDF 3 a escala 2.0 --- pero es TRANSCRIPCION DE TABLA, trabajo de la fase de citas y no de esta. (2) El calibre del TMC por altura de cobertura NO se puede hacer en absoluto: ASTM A796/A796M NO ESTA en normas/ (comprobado: las trece fuentes del directorio no la incluyen) y figura en la §15 del plan como ausencia declarada. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — LA MITAD TRANSCRIBIBLE SE CERRO: Tabla 1 de A760 y Table 6 de M 36 transcritas ENTERAS por metodo IMAGEN (ASTM_A760.T1, AASHTO_M36.T6 en src/normativa/tablas.py), con CorrespondenciaDeTablas CORR-TAMANOS-TMC que declara las dos celdas en que difieren (375, 825). VERIFICACION I1b, tres agentes: dos verificador-normativo confirmaron celda a celda (31 filas, 128 X, notas al pie) y el auditor adversarial hallo TRES celdas aritmeticamente anomalas (100-&gt;264, 21in-&gt;500, 750-&gt;2483); el desempate por relectura de digitos a 26-60x en AMBOS PDF dio que lo anomalo esta IMPRESO en las dos ediciones: es propiedad de la fuente, declarada en T_A760_T1.interpretacion.en_contra, NO se reescribe (regla 8). De la verificacion salio ademas la correccion de la Fuente AASHTO_M36: edicion M 36-03 (2007) (la portada; antes decia 2006 sin sosten), paginacion PorCapitulo del rotulo M 36-n, y el hallazgo de que al ejemplar le falta la pagina impresa M 36-5 (PDF 6 en blanco), declarado en su nota. Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial por la mitad (2): ASTM A796/A796M ausente (FUENTES_AUSENTES, gabinete).</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S19)</t>
+          <t>Claude Code (cierre, I1/I1b)</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: la comparacion que la ficha reclama sigue DECLARADA en 'hds5_embocadura_hdpe' --- la fila alternativa ('Circular CM / Headwall') en `sensibilidad`, y `verificacion_pendiente` diciendo con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila, y es decision, no omision: la adopcion se sostiene en el perfil de pared en la boca --- argumento fisico que la ficha no refuta ---, no en un margen de seguridad. QUE FALTA: el detalle constructivo de la embocadura, que es contenido de planos. NO se cierra en F5. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA.</t>
+          <t>4141fd5 — S19 — RAZON PRECISADA, sin cambio de codigo. Verificado hoy: la comparacion que la ficha reclama sigue DECLARADA en 'hds5_embocadura_hdpe' --- la fila alternativa ('Circular CM / Headwall') en `sensibilidad`, y `verificacion_pendiente` diciendo con todas las letras que la fila adoptada da un HW MENOR y que esa es la direccion insegura para V1, V4 y el resguardo. NO se cambia de fila, y es decision, no omision: la adopcion se sostiene en el perfil de pared en la boca --- argumento fisico que la ficha no refuta ---, no en un margen de seguridad. QUE FALTA: el detalle constructivo de la embocadura, que es contenido de planos. NO se cierra en F5. || S19d — SHA AÑADIDO, y la nota de arriba se lee bien: sin cambio de CODIGO, no sin commit. La razon precisada SI esta versionada --- es la ficha de este ID en la Parte III de docs/decisiones_diferidas.md, que nace en 4141fd5 (verificado: `git show 4141fd5:docs/decisiones_diferidas.md` ya trae las cuatro fichas NOR). Se corrige la celda y NO el verificador: relajar la exigencia de SHA para toda nota que diga «sin cambio de codigo» seria un guardian que se pone verde sobre una FRASE en vez de sobre el hecho, que es el modo de fallo de FACTOR_MURO_TABLA. || 183415b + 9902b3c — I1/I1b — DEFECTO NUEVO CONTRA ESTA FICHA, hallado por el auditor adversarial de I1b y verificado a mano: la ficha afirma que la fila del concreto da un HW MENOR 'en el rango de q* de interes', y la comparacion MEDIDA con las constantes del propio criterio y los dominios de M4 da lo contrario en los TRES regimenes vigentes — no sumergida manda K (0.0098&gt;0.0078), sumergida la diferencia 0.0019*q*^2-0.02 es positiva en todo su dominio q*&gt;=4.0 (el cruce q*=3.245 cae FUERA, que es donde la ficha evaluo), y la transicion une dos extremos donde el concreto ya es mayor. La ficha ademas enumera 'c y Y ambos menores' cuando 0.0398&gt;0.0379. La declaracion de verificacion_pendiente de hds5_embocadura_hdpe (que copiaba la ficha) se corrigio en 9902b3c y la linea base de Familia C se regenero solo por ese texto. La adopcion resulta CONSERVADORA EN DIRECCION pero se sigue sosteniendo en el argumento fisico (perfil de pared en la boca), no en ese margen. Veredicto regla 3: NO CIERRA — lo abierto (detalle constructivo de la embocadura, contenido de planos) no cambia. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S19)</t>
+          <t>Claude Code (cierre, I1/I1b)</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — S19 cubre la parte que faltaba DENTRO de la frontera declarada, y la frontera no se mueve. NUEVO: `_estado_criterio` ejercitado en sus tres casos (incluido «declarado (corrida)», el que SIS-A-01 dejo invisible); la leyenda de etiquetas contrastada contra `ca.CRITERIOS` en vez de contra una lista copiada; que `_llenar_tabla_criterios` lea el valor por `ca.criterio_efectivo` y no por una regla propia (SIS-A-01 en forma de guardia); y dos guardias de encabezado contra el arbol --- las cuatro pestanas y las cuatro exportaciones (SIS-A-10, que se habia cerrado a mano y no vigilaba nadie), y que el encabezado no vuelva a afirmar que usa el campo validable. MEDIDO: gui/app.py tiene hoy 1182 lineas y ~595 sentencias ejecutables; la suite ejecuta una fraccion pequeña y el resto se lee del AST. SIGUE ABIERTO, y es lo mismo que S17 declaro: el codigo que CONSTRUYE WIDGETS no se ejecuta en la suite, ni el viejo de gui/app.py ni el nuevo de gui/ventana_normativa.py. No es descuido: con un doble de tkinter seria un espejismo. QUE HARIA FALTA: una suite con Tk real bajo servidor X virtual en CI. Es infraestructura, no un test mas.</t>
+          <t>4141fd5 — S19 cubre la parte que faltaba DENTRO de la frontera declarada, y la frontera no se mueve. NUEVO: `_estado_criterio` ejercitado en sus tres casos (incluido «declarado (corrida)», el que SIS-A-01 dejo invisible); la leyenda de etiquetas contrastada contra `ca.CRITERIOS` en vez de contra una lista copiada; que `_llenar_tabla_criterios` lea el valor por `ca.criterio_efectivo` y no por una regla propia (SIS-A-01 en forma de guardia); y dos guardias de encabezado contra el arbol --- las cuatro pestanas y las cuatro exportaciones (SIS-A-10, que se habia cerrado a mano y no vigilaba nadie), y que el encabezado no vuelva a afirmar que usa el campo validable. MEDIDO: gui/app.py tiene hoy 1182 lineas y ~595 sentencias ejecutables; la suite ejecuta una fraccion pequeña y el resto se lee del AST. SIGUE ABIERTO, y es lo mismo que S17 declaro: el codigo que CONSTRUYE WIDGETS no se ejecuta en la suite, ni el viejo de gui/app.py ni el nuevo de gui/ventana_normativa.py. No es descuido: con un doble de tkinter seria un espejismo. QUE HARIA FALTA: una suite con Tk real bajo servidor X virtual en CI. Es infraestructura, no un test mas. || 183415b + 9902b3c — I1/I1b — EL HUECO NOMBRADO SE CUBRE, MEDIDO: cuarto test de ventana real (test_la_ventana_normativa_se_construye_y_se_cierra_de_verdad + tests/apoyo/gui_smoke_normativa.py): construye la app bajo Tk real, puebla las cuatro pestañas con el CSV de expediente y abre y cierra gui/ventana_normativa.py por el camino del raton — el archivo no se construia NUNCA en la suite. Censo de CLAUDE.md: cuatro tests de ventana, y la tabla de entornos re-medida en I1b. ALCANCE MEDIDO EN I1b (auditor adversarial): el smoke abre la cara TABLA; _pintar_rango, _pintar_catalogo, _pintar_campo y el camino de _declarar siguen sin construirse bajo Tk — declarado en la ficha de decisiones_diferidas. Veredicto regla 3: CIERRA EN PARTE (la ficha de auditoria es mas ancha: _interpretar_valor_declarado, banderas, cli.correr — eso ya lo cubrio S19 dentro de su frontera). Sigue Cerrado parcial: lo abierto es alcance (tres caras) y entorno (CI sin X).</t>
         </is>
       </c>
     </row>
@@ -10087,12 +10087,12 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>Claude Code (fase1, S19)</t>
+          <t>Claude Code (cierre, I1/I1b)</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados.</t>
+          <t>4141fd5 — RAZON ESTRECHADA DE TRES A DOS. `test_M5_verificaciones.py` consume ya CP-3 por la cadena de produccion entera (catalogo de M2 -&gt; Manning de M3 -&gt; umbral de M5) sin fabricar ningun dorado: todos los numeros salen de CP-2, CP-3 o de la constante [N] V_MIN, de modo que el conflicto n.7 no se toca. CP-3 gana ademas su propia `tolerancia_V` declarada, y test_M3 deja de escribirla a mano. Y LA REGLA DEJA DE VIVIR SOLO EN CLAUDE.md: test_guardias_de_la_suite.test_todo_modulo_de_calculo_consume_su_caso_patron la ejecuta, con la lista de exentos DECLARADA (M2, M8, M10 con la fuente que falta segun la §15; M11 por no corresponderle dorado) y fallando tambien si un exento deja de serlo. SIGUEN SIN CASO PATRON M2, M8 y M10, por falta de fuente externa: A796/A796M no esta en normas/, y para M10 lo que falta no es una norma sino el expediente vial. || PRECISADO EN S19c tras refutar los tests nuevos: la guardia que se escribio para cerrar este hallazgo decidia si un modulo consume su caso patron con `"casos_patron" in texto`, una busqueda de subcadena --- o sea que cometia SIS-F-17 al cerrar SIS-F-13 ---. Fallaba en las dos direcciones: un modulo podia perder el import Y el test y quedar verde mientras sobreviviera la palabra en un comentario, y un exento que solo la mencionara disparaba la alarma contraria. Reescrita por AST; el mutante muere. Y los DOS tests de CP-3 se rehicieron: el primero anunciaba vigilar la tolerancia de umbral y no la vigila (margen 7.3e-06 contra TOL 1e-09), y el segundo decia ejercitar la conclusion del fixture evaluando FUERA de sus condiciones (y/D caia a 0.32 desde el 0.75 que la conclusion fija). El segundo se reescribio sobre la mitad que nadie ejercitaba: la salvedad de MAT-O20 --- «con y/D &lt; 0.056 V2 SI se viola a S = 0.001» --- era una afirmacion escrita y no comprobada, y ahora se comprueba con su frontera por los dos lados. || 183415b + 9902b3c — I1/I1b — FICHA RECONCILIADA CON LA GUARDIA: M8 salio del censo SIN_CASO_PATRON en C7 (CP10_FLOTACION_MARCO) y la ficha de decisiones_diferidas aun lo listaba; quedan M2 y M10, cada uno con su fuente concreta, sin fabricar dorados (conflicto #7 respetado, verificado por el auditor adversarial). EN I1b ademas la razon de M2 en la guardia se actualizo por el propio trabajo de I1: la serie del TMC dejo de faltar (ASTM_A760.T1/AASHTO_M36.T6, paso 150 mm real sobre 900) y siguen faltando las series del concreto (M 170M Tablas 1-5 sin transcribir) y del HDPE (M294 ausente). Veredicto regla 3: CIERRA EN PARTE. Sigue Cerrado parcial.</t>
         </is>
       </c>
     </row>
